--- a/producao/pressupostos/PRESSUPOSTO_REAL_AMAZON_FLANEY.xlsx
+++ b/producao/pressupostos/PRESSUPOSTO_REAL_AMAZON_FLANEY.xlsx
@@ -27,7 +27,7 @@
     <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="167" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="18">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -102,6 +102,11 @@
     <font>
       <i val="1"/>
       <color rgb="006B6478"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="006B6478"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -164,7 +169,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -214,6 +219,13 @@
     <xf numFmtId="164" fontId="15" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="13" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
@@ -680,7 +692,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:F56"/>
+  <dimension ref="B1:F63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -791,7 +803,7 @@
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>v1</t>
+          <t>v2</t>
         </is>
       </c>
       <c r="D13" s="8" t="n"/>
@@ -878,7 +890,7 @@
       </c>
       <c r="F18" s="12" t="inlineStr">
         <is>
-          <t>a proposta fecha o valor SEM NOTA; com nota seria +15% (R$ 91.999,99). Imposto está em 0% por isso — trocar a alíquota se for faturar.</t>
+          <t>a proposta fecha o valor SEM NOTA; com nota seria +15% (R$ 91.999,99). Imposto zerado — este é um exercício.</t>
         </is>
       </c>
     </row>
@@ -1407,15 +1419,102 @@
         <v/>
       </c>
     </row>
-    <row r="56">
-      <c r="B56" s="30" t="inlineStr">
+    <row r="56" ht="22" customHeight="1">
+      <c r="B56" s="10" t="inlineStr">
+        <is>
+          <t>5.  DIVISÃO DO RESULTADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="28" customHeight="1">
+      <c r="B57" s="11" t="inlineStr">
+        <is>
+          <t>PARTICIPANTE</t>
+        </is>
+      </c>
+      <c r="C57" s="11" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D57" s="11" t="inlineStr">
+        <is>
+          <t>VALOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" s="12" t="inlineStr">
+        <is>
+          <t>YAD</t>
+        </is>
+      </c>
+      <c r="C58" s="22">
+        <f>1-SUM(C59:C60)</f>
+        <v/>
+      </c>
+      <c r="D58" s="13">
+        <f>C48-SUM(D59:D60)</f>
+        <v/>
+      </c>
+      <c r="F58" s="30" t="inlineStr">
+        <is>
+          <t>leva a diferença de arredondamento</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" s="12" t="inlineStr">
+        <is>
+          <t>Carlos</t>
+        </is>
+      </c>
+      <c r="C59" s="31" t="n">
+        <v>0.3333333333333334</v>
+      </c>
+      <c r="D59" s="13">
+        <f>ROUND($C$48*C59,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" s="12" t="inlineStr">
+        <is>
+          <t>Danilo</t>
+        </is>
+      </c>
+      <c r="C60" s="31" t="n">
+        <v>0.3333333333333334</v>
+      </c>
+      <c r="D60" s="13">
+        <f>ROUND($C$48*C60,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" s="20" t="inlineStr">
+        <is>
+          <t>TOTAL DISTRIBUÍDO</t>
+        </is>
+      </c>
+      <c r="C61" s="32">
+        <f>SUM(C58:C60)</f>
+        <v/>
+      </c>
+      <c r="D61" s="21">
+        <f>SUM(D58:D60)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" s="33" t="inlineStr">
         <is>
           <t>Preencha só a aba SAIDAS — esta aqui é toda fórmula. Célula amarela é campo para digitar.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="16">
     <mergeCell ref="B56:F56"/>
     <mergeCell ref="C12:D12"/>
     <mergeCell ref="C3:F3"/>
@@ -1428,6 +1527,7 @@
     <mergeCell ref="B45:F45"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="C13:D13"/>
+    <mergeCell ref="B63:F63"/>
     <mergeCell ref="B8:F8"/>
     <mergeCell ref="C2:F2"/>
     <mergeCell ref="B9:F9"/>
@@ -1490,7 +1590,7 @@
           <t>EQUIPE</t>
         </is>
       </c>
-      <c r="C2" s="31" t="inlineStr">
+      <c r="C2" s="34" t="inlineStr">
         <is>
           <t>Área nova? Escreva na primeira linha amarela.</t>
         </is>
@@ -1502,7 +1602,7 @@
           <t>LOCAÇÃO DE TERCEIROS</t>
         </is>
       </c>
-      <c r="C3" s="32" t="inlineStr">
+      <c r="C3" s="35" t="inlineStr">
         <is>
           <t>Ela aparece sozinha na listinha da aba SAÍDAS e vira uma linha no RESUMO.</t>
         </is>
@@ -1514,7 +1614,7 @@
           <t>TRANSPORTE E LOGÍSTICA</t>
         </is>
       </c>
-      <c r="C4" s="32" t="inlineStr">
+      <c r="C4" s="35" t="inlineStr">
         <is>
           <t>Não apague área que já tem gasto lançado — o RESUMO perde a linha.</t>
         </is>
@@ -1549,19 +1649,19 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="33" t="n"/>
+      <c r="A9" s="36" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="33" t="n"/>
+      <c r="A10" s="36" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="33" t="n"/>
+      <c r="A11" s="36" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="33" t="n"/>
+      <c r="A12" s="36" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="33" t="n"/>
+      <c r="A13" s="36" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1590,14 +1690,14 @@
   </cols>
   <sheetData>
     <row r="2">
-      <c r="B2" s="34" t="inlineStr">
+      <c r="B2" s="37" t="inlineStr">
         <is>
           <t>SAÍDAS — um gasto por linha</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="35" t="inlineStr">
+      <c r="B3" s="38" t="inlineStr">
         <is>
           <t>Como usar:  1) escreva o gasto numa linha vazia   2) escolha a ÁREA na listinha da célula   3) preencha QTD e VALOR UNITÁRIO — o TOTAL e o RESUMO se viram sozinhos.</t>
         </is>
@@ -1672,7 +1772,7 @@
       <c r="F6" s="13" t="n">
         <v>1000</v>
       </c>
-      <c r="G6" s="36">
+      <c r="G6" s="39">
         <f>IF(OR(E6="",F6=""),"",ROUND(E6*F6,2))</f>
         <v/>
       </c>
@@ -1710,7 +1810,7 @@
       <c r="F7" s="13" t="n">
         <v>800</v>
       </c>
-      <c r="G7" s="36">
+      <c r="G7" s="39">
         <f>IF(OR(E7="",F7=""),"",ROUND(E7*F7,2))</f>
         <v/>
       </c>
@@ -1748,7 +1848,7 @@
       <c r="F8" s="13" t="n">
         <v>800</v>
       </c>
-      <c r="G8" s="36">
+      <c r="G8" s="39">
         <f>IF(OR(E8="",F8=""),"",ROUND(E8*F8,2))</f>
         <v/>
       </c>
@@ -1786,7 +1886,7 @@
       <c r="F9" s="13" t="n">
         <v>1000</v>
       </c>
-      <c r="G9" s="36">
+      <c r="G9" s="39">
         <f>IF(OR(E9="",F9=""),"",ROUND(E9*F9,2))</f>
         <v/>
       </c>
@@ -1824,7 +1924,7 @@
       <c r="F10" s="13" t="n">
         <v>1000</v>
       </c>
-      <c r="G10" s="36">
+      <c r="G10" s="39">
         <f>IF(OR(E10="",F10=""),"",ROUND(E10*F10,2))</f>
         <v/>
       </c>
@@ -1862,7 +1962,7 @@
       <c r="F11" s="13" t="n">
         <v>350</v>
       </c>
-      <c r="G11" s="36">
+      <c r="G11" s="39">
         <f>IF(OR(E11="",F11=""),"",ROUND(E11*F11,2))</f>
         <v/>
       </c>
@@ -1900,7 +2000,7 @@
       <c r="F12" s="13" t="n">
         <v>350</v>
       </c>
-      <c r="G12" s="36">
+      <c r="G12" s="39">
         <f>IF(OR(E12="",F12=""),"",ROUND(E12*F12,2))</f>
         <v/>
       </c>
@@ -1938,7 +2038,7 @@
       <c r="F13" s="13" t="n">
         <v>350</v>
       </c>
-      <c r="G13" s="36">
+      <c r="G13" s="39">
         <f>IF(OR(E13="",F13=""),"",ROUND(E13*F13,2))</f>
         <v/>
       </c>
@@ -1976,7 +2076,7 @@
       <c r="F14" s="13" t="n">
         <v>350</v>
       </c>
-      <c r="G14" s="36">
+      <c r="G14" s="39">
         <f>IF(OR(E14="",F14=""),"",ROUND(E14*F14,2))</f>
         <v/>
       </c>
@@ -2000,19 +2100,19 @@
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>Cinegrafistas — 15 posições</t>
+          <t>Felype</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>10 URSA 12K + 5 Pocket</t>
+          <t>DTV / switcher ou interface com o cliente</t>
         </is>
       </c>
       <c r="E15" s="15" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="F15" s="16" t="n"/>
-      <c r="G15" s="36">
+      <c r="G15" s="39">
         <f>IF(OR(E15="",F15=""),"",ROUND(E15*F15,2))</f>
         <v/>
       </c>
@@ -2024,31 +2124,31 @@
       <c r="I15" s="14" t="n"/>
       <c r="J15" s="12" t="inlineStr">
         <is>
-          <t>ADICIONADO — a proposta NÃO vendeu cinegrafista, só técnico de câmeras. Quem opera as 15 câmeras? Se o Flaney fornece, zerar; se não, é a maior linha do job.</t>
+          <t>1.500/diária quando senta no switcher, zero quando é só interface — definir o papel</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="12" t="inlineStr">
         <is>
-          <t>EQUIPE</t>
+          <t>LOCAÇÃO DE TERCEIROS</t>
         </is>
       </c>
       <c r="C16" s="12" t="inlineStr">
         <is>
-          <t>Felype</t>
+          <t>Megatroper</t>
         </is>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
-          <t>DTV / switcher ou interface com o cliente</t>
+          <t>grua com operador + trilho com maquinista</t>
         </is>
       </c>
       <c r="E16" s="15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F16" s="16" t="n"/>
-      <c r="G16" s="36">
+      <c r="G16" s="39">
         <f>IF(OR(E16="",F16=""),"",ROUND(E16*F16,2))</f>
         <v/>
       </c>
@@ -2060,31 +2160,31 @@
       <c r="I16" s="14" t="n"/>
       <c r="J16" s="12" t="inlineStr">
         <is>
-          <t>1.500/diária quando senta no switcher, zero quando é só interface — definir o papel</t>
+          <t>pacote único · vendido a R$ 7.000 nos opcionais (Cammate 4.000 + Dolly 3.000) · no YAH CHURCH o mesmo pacote custou R$ 5.000</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>LOCAÇÃO DE TERCEIROS</t>
+          <t>TRANSPORTE E LOGÍSTICA</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>Cammate 10 m</t>
+          <t>Unidade móvel — operação</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>opcional, 1 diária</t>
+          <t>caminhão, motorista e combustível</t>
         </is>
       </c>
       <c r="E17" s="15" t="n">
         <v>1</v>
       </c>
       <c r="F17" s="16" t="n"/>
-      <c r="G17" s="36">
+      <c r="G17" s="39">
         <f>IF(OR(E17="",F17=""),"",ROUND(E17*F17,2))</f>
         <v/>
       </c>
@@ -2096,31 +2196,31 @@
       <c r="I17" s="14" t="n"/>
       <c r="J17" s="12" t="inlineStr">
         <is>
-          <t>vendido a R$ 4.000 · a Megatroper cobrou 5.000 por grua + trilho no YAH CHURCH</t>
+          <t>vendido a R$ 4.500 na linha LOGÍSTICA U.M. — falta o custo real de rodar a U.M.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="12" t="inlineStr">
         <is>
-          <t>LOCAÇÃO DE TERCEIROS</t>
+          <t>TRANSPORTE E LOGÍSTICA</t>
         </is>
       </c>
       <c r="C18" s="12" t="inlineStr">
         <is>
-          <t>Dolly Camaleon 10 m</t>
+          <t>Pedágio, combustível e estacionamento</t>
         </is>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>opcional, 1 diária</t>
+          <t>ida e volta</t>
         </is>
       </c>
       <c r="E18" s="15" t="n">
         <v>1</v>
       </c>
       <c r="F18" s="16" t="n"/>
-      <c r="G18" s="36">
+      <c r="G18" s="39">
         <f>IF(OR(E18="",F18=""),"",ROUND(E18*F18,2))</f>
         <v/>
       </c>
@@ -2132,31 +2232,33 @@
       <c r="I18" s="14" t="n"/>
       <c r="J18" s="12" t="inlineStr">
         <is>
-          <t>vendido a R$ 3.000</t>
+          <t>ADICIONADO</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>TRANSPORTE E LOGÍSTICA</t>
+          <t>ALIMENTAÇÃO</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>Unidade móvel — operação</t>
+          <t>Alimentação da equipe</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>caminhão, motorista e combustível</t>
+          <t>11 pessoas × 2 dias</t>
         </is>
       </c>
       <c r="E19" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F19" s="16" t="n"/>
-      <c r="G19" s="36">
+        <v>22</v>
+      </c>
+      <c r="F19" s="13" t="n">
+        <v>100</v>
+      </c>
+      <c r="G19" s="39">
         <f>IF(OR(E19="",F19=""),"",ROUND(E19*F19,2))</f>
         <v/>
       </c>
@@ -2168,69 +2270,65 @@
       <c r="I19" s="14" t="n"/>
       <c r="J19" s="12" t="inlineStr">
         <is>
-          <t>vendido a R$ 4.500 na linha LOGÍSTICA U.M. — falta o custo real de rodar a U.M.</t>
+          <t>ESTIMADO — confirmar se o Flaney ou a Amazon fornecem catering; se fornecerem, zerar</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="12" t="inlineStr">
         <is>
-          <t>TRANSPORTE E LOGÍSTICA</t>
+          <t>EQUIPAMENTO E MÍDIA</t>
         </is>
       </c>
       <c r="C20" s="12" t="inlineStr">
         <is>
-          <t>Pedágio, combustível e estacionamento</t>
+          <t>Sistema, 15 câmeras, óptica e comunicação</t>
         </is>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>ida e volta</t>
+          <t>parque próprio da YAD</t>
         </is>
       </c>
       <c r="E20" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="F20" s="16" t="n"/>
-      <c r="G20" s="36">
+      <c r="F20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="39">
         <f>IF(OR(E20="",F20=""),"",ROUND(E20*F20,2))</f>
         <v/>
       </c>
-      <c r="H20" s="15" t="inlineStr">
-        <is>
-          <t>A PAGAR</t>
-        </is>
-      </c>
+      <c r="H20" s="15" t="inlineStr"/>
       <c r="I20" s="14" t="n"/>
       <c r="J20" s="12" t="inlineStr">
         <is>
-          <t>ADICIONADO</t>
+          <t>R$ 88.335 de equipamento vendido, todo próprio — é daqui que vem a margem do job</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>ALIMENTAÇÃO</t>
+          <t>EQUIPAMENTO E MÍDIA</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>Alimentação da equipe</t>
+          <t>Mídia e backup do material</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>11 pessoas × 2 dias</t>
+          <t>30 cartões + 16 SSD · cópia de segurança</t>
         </is>
       </c>
       <c r="E21" s="15" t="n">
-        <v>22</v>
-      </c>
-      <c r="F21" s="13" t="n">
-        <v>100</v>
-      </c>
-      <c r="G21" s="36">
+        <v>1</v>
+      </c>
+      <c r="F21" s="16" t="n"/>
+      <c r="G21" s="39">
         <f>IF(OR(E21="",F21=""),"",ROUND(E21*F21,2))</f>
         <v/>
       </c>
@@ -2242,7 +2340,7 @@
       <c r="I21" s="14" t="n"/>
       <c r="J21" s="12" t="inlineStr">
         <is>
-          <t>ESTIMADO — confirmar se o Flaney ou a Amazon fornecem catering; se fornecerem, zerar</t>
+          <t>ADICIONADO — mídia é própria, a guarda e a cópia são custo</t>
         </is>
       </c>
     </row>
@@ -2254,12 +2352,12 @@
       </c>
       <c r="C22" s="12" t="inlineStr">
         <is>
-          <t>Sistema, 15 câmeras, óptica e comunicação</t>
+          <t>Ponto eletrônico do apresentador</t>
         </is>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
-          <t>parque próprio da YAD</t>
+          <t>acrescentado a pedido do cliente</t>
         </is>
       </c>
       <c r="E22" s="15" t="n">
@@ -2268,7 +2366,7 @@
       <c r="F22" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="G22" s="36">
+      <c r="G22" s="39">
         <f>IF(OR(E22="",F22=""),"",ROUND(E22*F22,2))</f>
         <v/>
       </c>
@@ -2276,31 +2374,31 @@
       <c r="I22" s="14" t="n"/>
       <c r="J22" s="12" t="inlineStr">
         <is>
-          <t>R$ 88.335 de equipamento vendido, todo próprio — é daqui que vem a margem do job</t>
+          <t>consta nas observações da proposta · kit Hollyland próprio — zerar se for da casa</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>EQUIPAMENTO E MÍDIA</t>
+          <t>PRODUÇÃO E DIVERSOS</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>Mídia e backup do material</t>
+          <t>Consumíveis de set e contingência</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>30 cartões + 16 SSD · cópia de segurança</t>
+          <t>fitas, pilhas, extensões</t>
         </is>
       </c>
       <c r="E23" s="15" t="n">
         <v>1</v>
       </c>
       <c r="F23" s="16" t="n"/>
-      <c r="G23" s="36">
+      <c r="G23" s="39">
         <f>IF(OR(E23="",F23=""),"",ROUND(E23*F23,2))</f>
         <v/>
       </c>
@@ -2312,125 +2410,83 @@
       <c r="I23" s="14" t="n"/>
       <c r="J23" s="12" t="inlineStr">
         <is>
-          <t>ADICIONADO — mídia é própria, a guarda e a cópia são custo</t>
+          <t>ADICIONADO</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="12" t="inlineStr">
         <is>
-          <t>EQUIPAMENTO E MÍDIA</t>
+          <t>COMISSÃO</t>
         </is>
       </c>
       <c r="C24" s="12" t="inlineStr">
         <is>
-          <t>Ponto eletrônico do apresentador</t>
+          <t>Comissão comercial</t>
         </is>
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
-          <t>acrescentado a pedido do cliente</t>
-        </is>
-      </c>
-      <c r="E24" s="15" t="n">
+          <t>% sobre a entrada líquida</t>
+        </is>
+      </c>
+      <c r="E24" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="F24" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" s="36">
+      <c r="F24" s="39">
+        <f>ROUND(RESUMO!$C$26*RESUMO!$F$24,2)</f>
+        <v/>
+      </c>
+      <c r="G24" s="39">
         <f>IF(OR(E24="",F24=""),"",ROUND(E24*F24,2))</f>
         <v/>
       </c>
-      <c r="H24" s="15" t="inlineStr"/>
+      <c r="H24" s="15" t="inlineStr">
+        <is>
+          <t>A PAGAR</t>
+        </is>
+      </c>
       <c r="I24" s="14" t="n"/>
-      <c r="J24" s="12" t="inlineStr">
-        <is>
-          <t>consta nas observações da proposta · kit Hollyland próprio — zerar se for da casa</t>
-        </is>
+      <c r="J24" s="12">
+        <f>TEXT(RESUMO!$F$24,"0.0%")&amp;" da entrada líquida (RESUMO!C26)"</f>
+        <v/>
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="12" t="inlineStr">
-        <is>
-          <t>PRODUÇÃO E DIVERSOS</t>
-        </is>
-      </c>
-      <c r="C25" s="12" t="inlineStr">
-        <is>
-          <t>Consumíveis de set e contingência</t>
-        </is>
-      </c>
-      <c r="D25" s="12" t="inlineStr">
-        <is>
-          <t>fitas, pilhas, extensões</t>
-        </is>
-      </c>
-      <c r="E25" s="15" t="n">
-        <v>1</v>
-      </c>
+      <c r="B25" s="12" t="n"/>
+      <c r="C25" s="12" t="n"/>
+      <c r="D25" s="12" t="n"/>
+      <c r="E25" s="41" t="n"/>
       <c r="F25" s="16" t="n"/>
-      <c r="G25" s="36">
+      <c r="G25" s="39">
         <f>IF(OR(E25="",F25=""),"",ROUND(E25*F25,2))</f>
         <v/>
       </c>
-      <c r="H25" s="15" t="inlineStr">
-        <is>
-          <t>A PAGAR</t>
-        </is>
-      </c>
+      <c r="H25" s="15" t="n"/>
       <c r="I25" s="14" t="n"/>
-      <c r="J25" s="12" t="inlineStr">
-        <is>
-          <t>ADICIONADO</t>
-        </is>
-      </c>
+      <c r="J25" s="12" t="n"/>
     </row>
     <row r="26">
-      <c r="B26" s="12" t="inlineStr">
-        <is>
-          <t>COMISSÃO</t>
-        </is>
-      </c>
-      <c r="C26" s="12" t="inlineStr">
-        <is>
-          <t>Comissão comercial</t>
-        </is>
-      </c>
-      <c r="D26" s="12" t="inlineStr">
-        <is>
-          <t>% sobre a entrada líquida</t>
-        </is>
-      </c>
-      <c r="E26" s="37" t="n">
-        <v>1</v>
-      </c>
-      <c r="F26" s="36">
-        <f>ROUND(RESUMO!$C$26*RESUMO!$F$24,2)</f>
-        <v/>
-      </c>
-      <c r="G26" s="36">
+      <c r="B26" s="12" t="n"/>
+      <c r="C26" s="12" t="n"/>
+      <c r="D26" s="12" t="n"/>
+      <c r="E26" s="41" t="n"/>
+      <c r="F26" s="16" t="n"/>
+      <c r="G26" s="39">
         <f>IF(OR(E26="",F26=""),"",ROUND(E26*F26,2))</f>
         <v/>
       </c>
-      <c r="H26" s="15" t="inlineStr">
-        <is>
-          <t>A PAGAR</t>
-        </is>
-      </c>
+      <c r="H26" s="15" t="n"/>
       <c r="I26" s="14" t="n"/>
-      <c r="J26" s="12">
-        <f>TEXT(RESUMO!$F$24,"0.0%")&amp;" da entrada líquida (RESUMO!C26)"</f>
-        <v/>
-      </c>
+      <c r="J26" s="12" t="n"/>
     </row>
     <row r="27">
       <c r="B27" s="12" t="n"/>
       <c r="C27" s="12" t="n"/>
       <c r="D27" s="12" t="n"/>
-      <c r="E27" s="38" t="n"/>
+      <c r="E27" s="41" t="n"/>
       <c r="F27" s="16" t="n"/>
-      <c r="G27" s="36">
+      <c r="G27" s="39">
         <f>IF(OR(E27="",F27=""),"",ROUND(E27*F27,2))</f>
         <v/>
       </c>
@@ -2442,9 +2498,9 @@
       <c r="B28" s="12" t="n"/>
       <c r="C28" s="12" t="n"/>
       <c r="D28" s="12" t="n"/>
-      <c r="E28" s="38" t="n"/>
+      <c r="E28" s="41" t="n"/>
       <c r="F28" s="16" t="n"/>
-      <c r="G28" s="36">
+      <c r="G28" s="39">
         <f>IF(OR(E28="",F28=""),"",ROUND(E28*F28,2))</f>
         <v/>
       </c>
@@ -2456,9 +2512,9 @@
       <c r="B29" s="12" t="n"/>
       <c r="C29" s="12" t="n"/>
       <c r="D29" s="12" t="n"/>
-      <c r="E29" s="38" t="n"/>
+      <c r="E29" s="41" t="n"/>
       <c r="F29" s="16" t="n"/>
-      <c r="G29" s="36">
+      <c r="G29" s="39">
         <f>IF(OR(E29="",F29=""),"",ROUND(E29*F29,2))</f>
         <v/>
       </c>
@@ -2470,9 +2526,9 @@
       <c r="B30" s="12" t="n"/>
       <c r="C30" s="12" t="n"/>
       <c r="D30" s="12" t="n"/>
-      <c r="E30" s="38" t="n"/>
+      <c r="E30" s="41" t="n"/>
       <c r="F30" s="16" t="n"/>
-      <c r="G30" s="36">
+      <c r="G30" s="39">
         <f>IF(OR(E30="",F30=""),"",ROUND(E30*F30,2))</f>
         <v/>
       </c>
@@ -2484,9 +2540,9 @@
       <c r="B31" s="12" t="n"/>
       <c r="C31" s="12" t="n"/>
       <c r="D31" s="12" t="n"/>
-      <c r="E31" s="38" t="n"/>
+      <c r="E31" s="41" t="n"/>
       <c r="F31" s="16" t="n"/>
-      <c r="G31" s="36">
+      <c r="G31" s="39">
         <f>IF(OR(E31="",F31=""),"",ROUND(E31*F31,2))</f>
         <v/>
       </c>
@@ -2498,9 +2554,9 @@
       <c r="B32" s="12" t="n"/>
       <c r="C32" s="12" t="n"/>
       <c r="D32" s="12" t="n"/>
-      <c r="E32" s="38" t="n"/>
+      <c r="E32" s="41" t="n"/>
       <c r="F32" s="16" t="n"/>
-      <c r="G32" s="36">
+      <c r="G32" s="39">
         <f>IF(OR(E32="",F32=""),"",ROUND(E32*F32,2))</f>
         <v/>
       </c>
@@ -2512,9 +2568,9 @@
       <c r="B33" s="12" t="n"/>
       <c r="C33" s="12" t="n"/>
       <c r="D33" s="12" t="n"/>
-      <c r="E33" s="38" t="n"/>
+      <c r="E33" s="41" t="n"/>
       <c r="F33" s="16" t="n"/>
-      <c r="G33" s="36">
+      <c r="G33" s="39">
         <f>IF(OR(E33="",F33=""),"",ROUND(E33*F33,2))</f>
         <v/>
       </c>
@@ -2526,9 +2582,9 @@
       <c r="B34" s="12" t="n"/>
       <c r="C34" s="12" t="n"/>
       <c r="D34" s="12" t="n"/>
-      <c r="E34" s="38" t="n"/>
+      <c r="E34" s="41" t="n"/>
       <c r="F34" s="16" t="n"/>
-      <c r="G34" s="36">
+      <c r="G34" s="39">
         <f>IF(OR(E34="",F34=""),"",ROUND(E34*F34,2))</f>
         <v/>
       </c>
@@ -2540,9 +2596,9 @@
       <c r="B35" s="12" t="n"/>
       <c r="C35" s="12" t="n"/>
       <c r="D35" s="12" t="n"/>
-      <c r="E35" s="38" t="n"/>
+      <c r="E35" s="41" t="n"/>
       <c r="F35" s="16" t="n"/>
-      <c r="G35" s="36">
+      <c r="G35" s="39">
         <f>IF(OR(E35="",F35=""),"",ROUND(E35*F35,2))</f>
         <v/>
       </c>
@@ -2554,9 +2610,9 @@
       <c r="B36" s="12" t="n"/>
       <c r="C36" s="12" t="n"/>
       <c r="D36" s="12" t="n"/>
-      <c r="E36" s="38" t="n"/>
+      <c r="E36" s="41" t="n"/>
       <c r="F36" s="16" t="n"/>
-      <c r="G36" s="36">
+      <c r="G36" s="39">
         <f>IF(OR(E36="",F36=""),"",ROUND(E36*F36,2))</f>
         <v/>
       </c>
@@ -2568,9 +2624,9 @@
       <c r="B37" s="12" t="n"/>
       <c r="C37" s="12" t="n"/>
       <c r="D37" s="12" t="n"/>
-      <c r="E37" s="38" t="n"/>
+      <c r="E37" s="41" t="n"/>
       <c r="F37" s="16" t="n"/>
-      <c r="G37" s="36">
+      <c r="G37" s="39">
         <f>IF(OR(E37="",F37=""),"",ROUND(E37*F37,2))</f>
         <v/>
       </c>
@@ -2582,9 +2638,9 @@
       <c r="B38" s="12" t="n"/>
       <c r="C38" s="12" t="n"/>
       <c r="D38" s="12" t="n"/>
-      <c r="E38" s="38" t="n"/>
+      <c r="E38" s="41" t="n"/>
       <c r="F38" s="16" t="n"/>
-      <c r="G38" s="36">
+      <c r="G38" s="39">
         <f>IF(OR(E38="",F38=""),"",ROUND(E38*F38,2))</f>
         <v/>
       </c>
@@ -2596,9 +2652,9 @@
       <c r="B39" s="12" t="n"/>
       <c r="C39" s="12" t="n"/>
       <c r="D39" s="12" t="n"/>
-      <c r="E39" s="38" t="n"/>
+      <c r="E39" s="41" t="n"/>
       <c r="F39" s="16" t="n"/>
-      <c r="G39" s="36">
+      <c r="G39" s="39">
         <f>IF(OR(E39="",F39=""),"",ROUND(E39*F39,2))</f>
         <v/>
       </c>
@@ -2610,9 +2666,9 @@
       <c r="B40" s="12" t="n"/>
       <c r="C40" s="12" t="n"/>
       <c r="D40" s="12" t="n"/>
-      <c r="E40" s="38" t="n"/>
+      <c r="E40" s="41" t="n"/>
       <c r="F40" s="16" t="n"/>
-      <c r="G40" s="36">
+      <c r="G40" s="39">
         <f>IF(OR(E40="",F40=""),"",ROUND(E40*F40,2))</f>
         <v/>
       </c>
@@ -2624,9 +2680,9 @@
       <c r="B41" s="12" t="n"/>
       <c r="C41" s="12" t="n"/>
       <c r="D41" s="12" t="n"/>
-      <c r="E41" s="38" t="n"/>
+      <c r="E41" s="41" t="n"/>
       <c r="F41" s="16" t="n"/>
-      <c r="G41" s="36">
+      <c r="G41" s="39">
         <f>IF(OR(E41="",F41=""),"",ROUND(E41*F41,2))</f>
         <v/>
       </c>
@@ -2638,9 +2694,9 @@
       <c r="B42" s="12" t="n"/>
       <c r="C42" s="12" t="n"/>
       <c r="D42" s="12" t="n"/>
-      <c r="E42" s="38" t="n"/>
+      <c r="E42" s="41" t="n"/>
       <c r="F42" s="16" t="n"/>
-      <c r="G42" s="36">
+      <c r="G42" s="39">
         <f>IF(OR(E42="",F42=""),"",ROUND(E42*F42,2))</f>
         <v/>
       </c>
@@ -2652,9 +2708,9 @@
       <c r="B43" s="12" t="n"/>
       <c r="C43" s="12" t="n"/>
       <c r="D43" s="12" t="n"/>
-      <c r="E43" s="38" t="n"/>
+      <c r="E43" s="41" t="n"/>
       <c r="F43" s="16" t="n"/>
-      <c r="G43" s="36">
+      <c r="G43" s="39">
         <f>IF(OR(E43="",F43=""),"",ROUND(E43*F43,2))</f>
         <v/>
       </c>
@@ -2666,9 +2722,9 @@
       <c r="B44" s="12" t="n"/>
       <c r="C44" s="12" t="n"/>
       <c r="D44" s="12" t="n"/>
-      <c r="E44" s="38" t="n"/>
+      <c r="E44" s="41" t="n"/>
       <c r="F44" s="16" t="n"/>
-      <c r="G44" s="36">
+      <c r="G44" s="39">
         <f>IF(OR(E44="",F44=""),"",ROUND(E44*F44,2))</f>
         <v/>
       </c>
@@ -2680,9 +2736,9 @@
       <c r="B45" s="12" t="n"/>
       <c r="C45" s="12" t="n"/>
       <c r="D45" s="12" t="n"/>
-      <c r="E45" s="38" t="n"/>
+      <c r="E45" s="41" t="n"/>
       <c r="F45" s="16" t="n"/>
-      <c r="G45" s="36">
+      <c r="G45" s="39">
         <f>IF(OR(E45="",F45=""),"",ROUND(E45*F45,2))</f>
         <v/>
       </c>
@@ -2694,9 +2750,9 @@
       <c r="B46" s="12" t="n"/>
       <c r="C46" s="12" t="n"/>
       <c r="D46" s="12" t="n"/>
-      <c r="E46" s="38" t="n"/>
+      <c r="E46" s="41" t="n"/>
       <c r="F46" s="16" t="n"/>
-      <c r="G46" s="36">
+      <c r="G46" s="39">
         <f>IF(OR(E46="",F46=""),"",ROUND(E46*F46,2))</f>
         <v/>
       </c>
@@ -2708,9 +2764,9 @@
       <c r="B47" s="12" t="n"/>
       <c r="C47" s="12" t="n"/>
       <c r="D47" s="12" t="n"/>
-      <c r="E47" s="38" t="n"/>
+      <c r="E47" s="41" t="n"/>
       <c r="F47" s="16" t="n"/>
-      <c r="G47" s="36">
+      <c r="G47" s="39">
         <f>IF(OR(E47="",F47=""),"",ROUND(E47*F47,2))</f>
         <v/>
       </c>
@@ -2722,9 +2778,9 @@
       <c r="B48" s="12" t="n"/>
       <c r="C48" s="12" t="n"/>
       <c r="D48" s="12" t="n"/>
-      <c r="E48" s="38" t="n"/>
+      <c r="E48" s="41" t="n"/>
       <c r="F48" s="16" t="n"/>
-      <c r="G48" s="36">
+      <c r="G48" s="39">
         <f>IF(OR(E48="",F48=""),"",ROUND(E48*F48,2))</f>
         <v/>
       </c>
@@ -2736,9 +2792,9 @@
       <c r="B49" s="12" t="n"/>
       <c r="C49" s="12" t="n"/>
       <c r="D49" s="12" t="n"/>
-      <c r="E49" s="38" t="n"/>
+      <c r="E49" s="41" t="n"/>
       <c r="F49" s="16" t="n"/>
-      <c r="G49" s="36">
+      <c r="G49" s="39">
         <f>IF(OR(E49="",F49=""),"",ROUND(E49*F49,2))</f>
         <v/>
       </c>
@@ -2750,9 +2806,9 @@
       <c r="B50" s="12" t="n"/>
       <c r="C50" s="12" t="n"/>
       <c r="D50" s="12" t="n"/>
-      <c r="E50" s="38" t="n"/>
+      <c r="E50" s="41" t="n"/>
       <c r="F50" s="16" t="n"/>
-      <c r="G50" s="36">
+      <c r="G50" s="39">
         <f>IF(OR(E50="",F50=""),"",ROUND(E50*F50,2))</f>
         <v/>
       </c>
@@ -2764,9 +2820,9 @@
       <c r="B51" s="12" t="n"/>
       <c r="C51" s="12" t="n"/>
       <c r="D51" s="12" t="n"/>
-      <c r="E51" s="38" t="n"/>
+      <c r="E51" s="41" t="n"/>
       <c r="F51" s="16" t="n"/>
-      <c r="G51" s="36">
+      <c r="G51" s="39">
         <f>IF(OR(E51="",F51=""),"",ROUND(E51*F51,2))</f>
         <v/>
       </c>
@@ -2778,9 +2834,9 @@
       <c r="B52" s="12" t="n"/>
       <c r="C52" s="12" t="n"/>
       <c r="D52" s="12" t="n"/>
-      <c r="E52" s="38" t="n"/>
+      <c r="E52" s="41" t="n"/>
       <c r="F52" s="16" t="n"/>
-      <c r="G52" s="36">
+      <c r="G52" s="39">
         <f>IF(OR(E52="",F52=""),"",ROUND(E52*F52,2))</f>
         <v/>
       </c>
@@ -2792,9 +2848,9 @@
       <c r="B53" s="12" t="n"/>
       <c r="C53" s="12" t="n"/>
       <c r="D53" s="12" t="n"/>
-      <c r="E53" s="38" t="n"/>
+      <c r="E53" s="41" t="n"/>
       <c r="F53" s="16" t="n"/>
-      <c r="G53" s="36">
+      <c r="G53" s="39">
         <f>IF(OR(E53="",F53=""),"",ROUND(E53*F53,2))</f>
         <v/>
       </c>
@@ -2806,9 +2862,9 @@
       <c r="B54" s="12" t="n"/>
       <c r="C54" s="12" t="n"/>
       <c r="D54" s="12" t="n"/>
-      <c r="E54" s="38" t="n"/>
+      <c r="E54" s="41" t="n"/>
       <c r="F54" s="16" t="n"/>
-      <c r="G54" s="36">
+      <c r="G54" s="39">
         <f>IF(OR(E54="",F54=""),"",ROUND(E54*F54,2))</f>
         <v/>
       </c>
@@ -2820,9 +2876,9 @@
       <c r="B55" s="12" t="n"/>
       <c r="C55" s="12" t="n"/>
       <c r="D55" s="12" t="n"/>
-      <c r="E55" s="38" t="n"/>
+      <c r="E55" s="41" t="n"/>
       <c r="F55" s="16" t="n"/>
-      <c r="G55" s="36">
+      <c r="G55" s="39">
         <f>IF(OR(E55="",F55=""),"",ROUND(E55*F55,2))</f>
         <v/>
       </c>
@@ -2834,9 +2890,9 @@
       <c r="B56" s="12" t="n"/>
       <c r="C56" s="12" t="n"/>
       <c r="D56" s="12" t="n"/>
-      <c r="E56" s="38" t="n"/>
+      <c r="E56" s="41" t="n"/>
       <c r="F56" s="16" t="n"/>
-      <c r="G56" s="36">
+      <c r="G56" s="39">
         <f>IF(OR(E56="",F56=""),"",ROUND(E56*F56,2))</f>
         <v/>
       </c>
@@ -2848,9 +2904,9 @@
       <c r="B57" s="12" t="n"/>
       <c r="C57" s="12" t="n"/>
       <c r="D57" s="12" t="n"/>
-      <c r="E57" s="38" t="n"/>
+      <c r="E57" s="41" t="n"/>
       <c r="F57" s="16" t="n"/>
-      <c r="G57" s="36">
+      <c r="G57" s="39">
         <f>IF(OR(E57="",F57=""),"",ROUND(E57*F57,2))</f>
         <v/>
       </c>
@@ -2862,9 +2918,9 @@
       <c r="B58" s="12" t="n"/>
       <c r="C58" s="12" t="n"/>
       <c r="D58" s="12" t="n"/>
-      <c r="E58" s="38" t="n"/>
+      <c r="E58" s="41" t="n"/>
       <c r="F58" s="16" t="n"/>
-      <c r="G58" s="36">
+      <c r="G58" s="39">
         <f>IF(OR(E58="",F58=""),"",ROUND(E58*F58,2))</f>
         <v/>
       </c>
@@ -2876,9 +2932,9 @@
       <c r="B59" s="12" t="n"/>
       <c r="C59" s="12" t="n"/>
       <c r="D59" s="12" t="n"/>
-      <c r="E59" s="38" t="n"/>
+      <c r="E59" s="41" t="n"/>
       <c r="F59" s="16" t="n"/>
-      <c r="G59" s="36">
+      <c r="G59" s="39">
         <f>IF(OR(E59="",F59=""),"",ROUND(E59*F59,2))</f>
         <v/>
       </c>
@@ -2890,9 +2946,9 @@
       <c r="B60" s="12" t="n"/>
       <c r="C60" s="12" t="n"/>
       <c r="D60" s="12" t="n"/>
-      <c r="E60" s="38" t="n"/>
+      <c r="E60" s="41" t="n"/>
       <c r="F60" s="16" t="n"/>
-      <c r="G60" s="36">
+      <c r="G60" s="39">
         <f>IF(OR(E60="",F60=""),"",ROUND(E60*F60,2))</f>
         <v/>
       </c>
@@ -2904,9 +2960,9 @@
       <c r="B61" s="12" t="n"/>
       <c r="C61" s="12" t="n"/>
       <c r="D61" s="12" t="n"/>
-      <c r="E61" s="38" t="n"/>
+      <c r="E61" s="41" t="n"/>
       <c r="F61" s="16" t="n"/>
-      <c r="G61" s="36">
+      <c r="G61" s="39">
         <f>IF(OR(E61="",F61=""),"",ROUND(E61*F61,2))</f>
         <v/>
       </c>
@@ -2918,9 +2974,9 @@
       <c r="B62" s="12" t="n"/>
       <c r="C62" s="12" t="n"/>
       <c r="D62" s="12" t="n"/>
-      <c r="E62" s="38" t="n"/>
+      <c r="E62" s="41" t="n"/>
       <c r="F62" s="16" t="n"/>
-      <c r="G62" s="36">
+      <c r="G62" s="39">
         <f>IF(OR(E62="",F62=""),"",ROUND(E62*F62,2))</f>
         <v/>
       </c>
@@ -2932,9 +2988,9 @@
       <c r="B63" s="12" t="n"/>
       <c r="C63" s="12" t="n"/>
       <c r="D63" s="12" t="n"/>
-      <c r="E63" s="38" t="n"/>
+      <c r="E63" s="41" t="n"/>
       <c r="F63" s="16" t="n"/>
-      <c r="G63" s="36">
+      <c r="G63" s="39">
         <f>IF(OR(E63="",F63=""),"",ROUND(E63*F63,2))</f>
         <v/>
       </c>
@@ -2946,9 +3002,9 @@
       <c r="B64" s="12" t="n"/>
       <c r="C64" s="12" t="n"/>
       <c r="D64" s="12" t="n"/>
-      <c r="E64" s="38" t="n"/>
+      <c r="E64" s="41" t="n"/>
       <c r="F64" s="16" t="n"/>
-      <c r="G64" s="36">
+      <c r="G64" s="39">
         <f>IF(OR(E64="",F64=""),"",ROUND(E64*F64,2))</f>
         <v/>
       </c>
@@ -2960,9 +3016,9 @@
       <c r="B65" s="12" t="n"/>
       <c r="C65" s="12" t="n"/>
       <c r="D65" s="12" t="n"/>
-      <c r="E65" s="38" t="n"/>
+      <c r="E65" s="41" t="n"/>
       <c r="F65" s="16" t="n"/>
-      <c r="G65" s="36">
+      <c r="G65" s="39">
         <f>IF(OR(E65="",F65=""),"",ROUND(E65*F65,2))</f>
         <v/>
       </c>
@@ -2974,9 +3030,9 @@
       <c r="B66" s="12" t="n"/>
       <c r="C66" s="12" t="n"/>
       <c r="D66" s="12" t="n"/>
-      <c r="E66" s="38" t="n"/>
+      <c r="E66" s="41" t="n"/>
       <c r="F66" s="16" t="n"/>
-      <c r="G66" s="36">
+      <c r="G66" s="39">
         <f>IF(OR(E66="",F66=""),"",ROUND(E66*F66,2))</f>
         <v/>
       </c>
@@ -2988,9 +3044,9 @@
       <c r="B67" s="12" t="n"/>
       <c r="C67" s="12" t="n"/>
       <c r="D67" s="12" t="n"/>
-      <c r="E67" s="38" t="n"/>
+      <c r="E67" s="41" t="n"/>
       <c r="F67" s="16" t="n"/>
-      <c r="G67" s="36">
+      <c r="G67" s="39">
         <f>IF(OR(E67="",F67=""),"",ROUND(E67*F67,2))</f>
         <v/>
       </c>
@@ -3002,9 +3058,9 @@
       <c r="B68" s="12" t="n"/>
       <c r="C68" s="12" t="n"/>
       <c r="D68" s="12" t="n"/>
-      <c r="E68" s="38" t="n"/>
+      <c r="E68" s="41" t="n"/>
       <c r="F68" s="16" t="n"/>
-      <c r="G68" s="36">
+      <c r="G68" s="39">
         <f>IF(OR(E68="",F68=""),"",ROUND(E68*F68,2))</f>
         <v/>
       </c>
@@ -3016,9 +3072,9 @@
       <c r="B69" s="12" t="n"/>
       <c r="C69" s="12" t="n"/>
       <c r="D69" s="12" t="n"/>
-      <c r="E69" s="38" t="n"/>
+      <c r="E69" s="41" t="n"/>
       <c r="F69" s="16" t="n"/>
-      <c r="G69" s="36">
+      <c r="G69" s="39">
         <f>IF(OR(E69="",F69=""),"",ROUND(E69*F69,2))</f>
         <v/>
       </c>
@@ -3030,9 +3086,9 @@
       <c r="B70" s="12" t="n"/>
       <c r="C70" s="12" t="n"/>
       <c r="D70" s="12" t="n"/>
-      <c r="E70" s="38" t="n"/>
+      <c r="E70" s="41" t="n"/>
       <c r="F70" s="16" t="n"/>
-      <c r="G70" s="36">
+      <c r="G70" s="39">
         <f>IF(OR(E70="",F70=""),"",ROUND(E70*F70,2))</f>
         <v/>
       </c>
@@ -3044,9 +3100,9 @@
       <c r="B71" s="12" t="n"/>
       <c r="C71" s="12" t="n"/>
       <c r="D71" s="12" t="n"/>
-      <c r="E71" s="38" t="n"/>
+      <c r="E71" s="41" t="n"/>
       <c r="F71" s="16" t="n"/>
-      <c r="G71" s="36">
+      <c r="G71" s="39">
         <f>IF(OR(E71="",F71=""),"",ROUND(E71*F71,2))</f>
         <v/>
       </c>
@@ -3058,9 +3114,9 @@
       <c r="B72" s="12" t="n"/>
       <c r="C72" s="12" t="n"/>
       <c r="D72" s="12" t="n"/>
-      <c r="E72" s="38" t="n"/>
+      <c r="E72" s="41" t="n"/>
       <c r="F72" s="16" t="n"/>
-      <c r="G72" s="36">
+      <c r="G72" s="39">
         <f>IF(OR(E72="",F72=""),"",ROUND(E72*F72,2))</f>
         <v/>
       </c>
@@ -3072,9 +3128,9 @@
       <c r="B73" s="12" t="n"/>
       <c r="C73" s="12" t="n"/>
       <c r="D73" s="12" t="n"/>
-      <c r="E73" s="38" t="n"/>
+      <c r="E73" s="41" t="n"/>
       <c r="F73" s="16" t="n"/>
-      <c r="G73" s="36">
+      <c r="G73" s="39">
         <f>IF(OR(E73="",F73=""),"",ROUND(E73*F73,2))</f>
         <v/>
       </c>
@@ -3086,9 +3142,9 @@
       <c r="B74" s="12" t="n"/>
       <c r="C74" s="12" t="n"/>
       <c r="D74" s="12" t="n"/>
-      <c r="E74" s="38" t="n"/>
+      <c r="E74" s="41" t="n"/>
       <c r="F74" s="16" t="n"/>
-      <c r="G74" s="36">
+      <c r="G74" s="39">
         <f>IF(OR(E74="",F74=""),"",ROUND(E74*F74,2))</f>
         <v/>
       </c>
@@ -3100,9 +3156,9 @@
       <c r="B75" s="12" t="n"/>
       <c r="C75" s="12" t="n"/>
       <c r="D75" s="12" t="n"/>
-      <c r="E75" s="38" t="n"/>
+      <c r="E75" s="41" t="n"/>
       <c r="F75" s="16" t="n"/>
-      <c r="G75" s="36">
+      <c r="G75" s="39">
         <f>IF(OR(E75="",F75=""),"",ROUND(E75*F75,2))</f>
         <v/>
       </c>
@@ -3114,9 +3170,9 @@
       <c r="B76" s="12" t="n"/>
       <c r="C76" s="12" t="n"/>
       <c r="D76" s="12" t="n"/>
-      <c r="E76" s="38" t="n"/>
+      <c r="E76" s="41" t="n"/>
       <c r="F76" s="16" t="n"/>
-      <c r="G76" s="36">
+      <c r="G76" s="39">
         <f>IF(OR(E76="",F76=""),"",ROUND(E76*F76,2))</f>
         <v/>
       </c>
@@ -3128,9 +3184,9 @@
       <c r="B77" s="12" t="n"/>
       <c r="C77" s="12" t="n"/>
       <c r="D77" s="12" t="n"/>
-      <c r="E77" s="38" t="n"/>
+      <c r="E77" s="41" t="n"/>
       <c r="F77" s="16" t="n"/>
-      <c r="G77" s="36">
+      <c r="G77" s="39">
         <f>IF(OR(E77="",F77=""),"",ROUND(E77*F77,2))</f>
         <v/>
       </c>
@@ -3142,9 +3198,9 @@
       <c r="B78" s="12" t="n"/>
       <c r="C78" s="12" t="n"/>
       <c r="D78" s="12" t="n"/>
-      <c r="E78" s="38" t="n"/>
+      <c r="E78" s="41" t="n"/>
       <c r="F78" s="16" t="n"/>
-      <c r="G78" s="36">
+      <c r="G78" s="39">
         <f>IF(OR(E78="",F78=""),"",ROUND(E78*F78,2))</f>
         <v/>
       </c>
@@ -3156,9 +3212,9 @@
       <c r="B79" s="12" t="n"/>
       <c r="C79" s="12" t="n"/>
       <c r="D79" s="12" t="n"/>
-      <c r="E79" s="38" t="n"/>
+      <c r="E79" s="41" t="n"/>
       <c r="F79" s="16" t="n"/>
-      <c r="G79" s="36">
+      <c r="G79" s="39">
         <f>IF(OR(E79="",F79=""),"",ROUND(E79*F79,2))</f>
         <v/>
       </c>
@@ -3170,9 +3226,9 @@
       <c r="B80" s="12" t="n"/>
       <c r="C80" s="12" t="n"/>
       <c r="D80" s="12" t="n"/>
-      <c r="E80" s="38" t="n"/>
+      <c r="E80" s="41" t="n"/>
       <c r="F80" s="16" t="n"/>
-      <c r="G80" s="36">
+      <c r="G80" s="39">
         <f>IF(OR(E80="",F80=""),"",ROUND(E80*F80,2))</f>
         <v/>
       </c>
@@ -3184,9 +3240,9 @@
       <c r="B81" s="12" t="n"/>
       <c r="C81" s="12" t="n"/>
       <c r="D81" s="12" t="n"/>
-      <c r="E81" s="38" t="n"/>
+      <c r="E81" s="41" t="n"/>
       <c r="F81" s="16" t="n"/>
-      <c r="G81" s="36">
+      <c r="G81" s="39">
         <f>IF(OR(E81="",F81=""),"",ROUND(E81*F81,2))</f>
         <v/>
       </c>
@@ -3198,9 +3254,9 @@
       <c r="B82" s="12" t="n"/>
       <c r="C82" s="12" t="n"/>
       <c r="D82" s="12" t="n"/>
-      <c r="E82" s="38" t="n"/>
+      <c r="E82" s="41" t="n"/>
       <c r="F82" s="16" t="n"/>
-      <c r="G82" s="36">
+      <c r="G82" s="39">
         <f>IF(OR(E82="",F82=""),"",ROUND(E82*F82,2))</f>
         <v/>
       </c>
@@ -3212,9 +3268,9 @@
       <c r="B83" s="12" t="n"/>
       <c r="C83" s="12" t="n"/>
       <c r="D83" s="12" t="n"/>
-      <c r="E83" s="38" t="n"/>
+      <c r="E83" s="41" t="n"/>
       <c r="F83" s="16" t="n"/>
-      <c r="G83" s="36">
+      <c r="G83" s="39">
         <f>IF(OR(E83="",F83=""),"",ROUND(E83*F83,2))</f>
         <v/>
       </c>
@@ -3226,9 +3282,9 @@
       <c r="B84" s="12" t="n"/>
       <c r="C84" s="12" t="n"/>
       <c r="D84" s="12" t="n"/>
-      <c r="E84" s="38" t="n"/>
+      <c r="E84" s="41" t="n"/>
       <c r="F84" s="16" t="n"/>
-      <c r="G84" s="36">
+      <c r="G84" s="39">
         <f>IF(OR(E84="",F84=""),"",ROUND(E84*F84,2))</f>
         <v/>
       </c>
@@ -3240,9 +3296,9 @@
       <c r="B85" s="12" t="n"/>
       <c r="C85" s="12" t="n"/>
       <c r="D85" s="12" t="n"/>
-      <c r="E85" s="38" t="n"/>
+      <c r="E85" s="41" t="n"/>
       <c r="F85" s="16" t="n"/>
-      <c r="G85" s="36">
+      <c r="G85" s="39">
         <f>IF(OR(E85="",F85=""),"",ROUND(E85*F85,2))</f>
         <v/>
       </c>
@@ -3254,9 +3310,9 @@
       <c r="B86" s="12" t="n"/>
       <c r="C86" s="12" t="n"/>
       <c r="D86" s="12" t="n"/>
-      <c r="E86" s="38" t="n"/>
+      <c r="E86" s="41" t="n"/>
       <c r="F86" s="16" t="n"/>
-      <c r="G86" s="36">
+      <c r="G86" s="39">
         <f>IF(OR(E86="",F86=""),"",ROUND(E86*F86,2))</f>
         <v/>
       </c>
@@ -3268,9 +3324,9 @@
       <c r="B87" s="12" t="n"/>
       <c r="C87" s="12" t="n"/>
       <c r="D87" s="12" t="n"/>
-      <c r="E87" s="38" t="n"/>
+      <c r="E87" s="41" t="n"/>
       <c r="F87" s="16" t="n"/>
-      <c r="G87" s="36">
+      <c r="G87" s="39">
         <f>IF(OR(E87="",F87=""),"",ROUND(E87*F87,2))</f>
         <v/>
       </c>
@@ -3282,9 +3338,9 @@
       <c r="B88" s="12" t="n"/>
       <c r="C88" s="12" t="n"/>
       <c r="D88" s="12" t="n"/>
-      <c r="E88" s="38" t="n"/>
+      <c r="E88" s="41" t="n"/>
       <c r="F88" s="16" t="n"/>
-      <c r="G88" s="36">
+      <c r="G88" s="39">
         <f>IF(OR(E88="",F88=""),"",ROUND(E88*F88,2))</f>
         <v/>
       </c>
@@ -3296,9 +3352,9 @@
       <c r="B89" s="12" t="n"/>
       <c r="C89" s="12" t="n"/>
       <c r="D89" s="12" t="n"/>
-      <c r="E89" s="38" t="n"/>
+      <c r="E89" s="41" t="n"/>
       <c r="F89" s="16" t="n"/>
-      <c r="G89" s="36">
+      <c r="G89" s="39">
         <f>IF(OR(E89="",F89=""),"",ROUND(E89*F89,2))</f>
         <v/>
       </c>
@@ -3310,9 +3366,9 @@
       <c r="B90" s="12" t="n"/>
       <c r="C90" s="12" t="n"/>
       <c r="D90" s="12" t="n"/>
-      <c r="E90" s="38" t="n"/>
+      <c r="E90" s="41" t="n"/>
       <c r="F90" s="16" t="n"/>
-      <c r="G90" s="36">
+      <c r="G90" s="39">
         <f>IF(OR(E90="",F90=""),"",ROUND(E90*F90,2))</f>
         <v/>
       </c>
@@ -3324,9 +3380,9 @@
       <c r="B91" s="12" t="n"/>
       <c r="C91" s="12" t="n"/>
       <c r="D91" s="12" t="n"/>
-      <c r="E91" s="38" t="n"/>
+      <c r="E91" s="41" t="n"/>
       <c r="F91" s="16" t="n"/>
-      <c r="G91" s="36">
+      <c r="G91" s="39">
         <f>IF(OR(E91="",F91=""),"",ROUND(E91*F91,2))</f>
         <v/>
       </c>
@@ -3338,9 +3394,9 @@
       <c r="B92" s="12" t="n"/>
       <c r="C92" s="12" t="n"/>
       <c r="D92" s="12" t="n"/>
-      <c r="E92" s="38" t="n"/>
+      <c r="E92" s="41" t="n"/>
       <c r="F92" s="16" t="n"/>
-      <c r="G92" s="36">
+      <c r="G92" s="39">
         <f>IF(OR(E92="",F92=""),"",ROUND(E92*F92,2))</f>
         <v/>
       </c>
@@ -3352,9 +3408,9 @@
       <c r="B93" s="12" t="n"/>
       <c r="C93" s="12" t="n"/>
       <c r="D93" s="12" t="n"/>
-      <c r="E93" s="38" t="n"/>
+      <c r="E93" s="41" t="n"/>
       <c r="F93" s="16" t="n"/>
-      <c r="G93" s="36">
+      <c r="G93" s="39">
         <f>IF(OR(E93="",F93=""),"",ROUND(E93*F93,2))</f>
         <v/>
       </c>
@@ -3366,9 +3422,9 @@
       <c r="B94" s="12" t="n"/>
       <c r="C94" s="12" t="n"/>
       <c r="D94" s="12" t="n"/>
-      <c r="E94" s="38" t="n"/>
+      <c r="E94" s="41" t="n"/>
       <c r="F94" s="16" t="n"/>
-      <c r="G94" s="36">
+      <c r="G94" s="39">
         <f>IF(OR(E94="",F94=""),"",ROUND(E94*F94,2))</f>
         <v/>
       </c>
@@ -3380,9 +3436,9 @@
       <c r="B95" s="12" t="n"/>
       <c r="C95" s="12" t="n"/>
       <c r="D95" s="12" t="n"/>
-      <c r="E95" s="38" t="n"/>
+      <c r="E95" s="41" t="n"/>
       <c r="F95" s="16" t="n"/>
-      <c r="G95" s="36">
+      <c r="G95" s="39">
         <f>IF(OR(E95="",F95=""),"",ROUND(E95*F95,2))</f>
         <v/>
       </c>
@@ -3394,9 +3450,9 @@
       <c r="B96" s="12" t="n"/>
       <c r="C96" s="12" t="n"/>
       <c r="D96" s="12" t="n"/>
-      <c r="E96" s="38" t="n"/>
+      <c r="E96" s="41" t="n"/>
       <c r="F96" s="16" t="n"/>
-      <c r="G96" s="36">
+      <c r="G96" s="39">
         <f>IF(OR(E96="",F96=""),"",ROUND(E96*F96,2))</f>
         <v/>
       </c>
@@ -3408,9 +3464,9 @@
       <c r="B97" s="12" t="n"/>
       <c r="C97" s="12" t="n"/>
       <c r="D97" s="12" t="n"/>
-      <c r="E97" s="38" t="n"/>
+      <c r="E97" s="41" t="n"/>
       <c r="F97" s="16" t="n"/>
-      <c r="G97" s="36">
+      <c r="G97" s="39">
         <f>IF(OR(E97="",F97=""),"",ROUND(E97*F97,2))</f>
         <v/>
       </c>
@@ -3422,9 +3478,9 @@
       <c r="B98" s="12" t="n"/>
       <c r="C98" s="12" t="n"/>
       <c r="D98" s="12" t="n"/>
-      <c r="E98" s="38" t="n"/>
+      <c r="E98" s="41" t="n"/>
       <c r="F98" s="16" t="n"/>
-      <c r="G98" s="36">
+      <c r="G98" s="39">
         <f>IF(OR(E98="",F98=""),"",ROUND(E98*F98,2))</f>
         <v/>
       </c>
@@ -3436,9 +3492,9 @@
       <c r="B99" s="12" t="n"/>
       <c r="C99" s="12" t="n"/>
       <c r="D99" s="12" t="n"/>
-      <c r="E99" s="38" t="n"/>
+      <c r="E99" s="41" t="n"/>
       <c r="F99" s="16" t="n"/>
-      <c r="G99" s="36">
+      <c r="G99" s="39">
         <f>IF(OR(E99="",F99=""),"",ROUND(E99*F99,2))</f>
         <v/>
       </c>
@@ -3450,9 +3506,9 @@
       <c r="B100" s="12" t="n"/>
       <c r="C100" s="12" t="n"/>
       <c r="D100" s="12" t="n"/>
-      <c r="E100" s="38" t="n"/>
+      <c r="E100" s="41" t="n"/>
       <c r="F100" s="16" t="n"/>
-      <c r="G100" s="36">
+      <c r="G100" s="39">
         <f>IF(OR(E100="",F100=""),"",ROUND(E100*F100,2))</f>
         <v/>
       </c>
@@ -3464,9 +3520,9 @@
       <c r="B101" s="12" t="n"/>
       <c r="C101" s="12" t="n"/>
       <c r="D101" s="12" t="n"/>
-      <c r="E101" s="38" t="n"/>
+      <c r="E101" s="41" t="n"/>
       <c r="F101" s="16" t="n"/>
-      <c r="G101" s="36">
+      <c r="G101" s="39">
         <f>IF(OR(E101="",F101=""),"",ROUND(E101*F101,2))</f>
         <v/>
       </c>
@@ -3478,9 +3534,9 @@
       <c r="B102" s="12" t="n"/>
       <c r="C102" s="12" t="n"/>
       <c r="D102" s="12" t="n"/>
-      <c r="E102" s="38" t="n"/>
+      <c r="E102" s="41" t="n"/>
       <c r="F102" s="16" t="n"/>
-      <c r="G102" s="36">
+      <c r="G102" s="39">
         <f>IF(OR(E102="",F102=""),"",ROUND(E102*F102,2))</f>
         <v/>
       </c>
@@ -3492,9 +3548,9 @@
       <c r="B103" s="12" t="n"/>
       <c r="C103" s="12" t="n"/>
       <c r="D103" s="12" t="n"/>
-      <c r="E103" s="38" t="n"/>
+      <c r="E103" s="41" t="n"/>
       <c r="F103" s="16" t="n"/>
-      <c r="G103" s="36">
+      <c r="G103" s="39">
         <f>IF(OR(E103="",F103=""),"",ROUND(E103*F103,2))</f>
         <v/>
       </c>
@@ -3506,9 +3562,9 @@
       <c r="B104" s="12" t="n"/>
       <c r="C104" s="12" t="n"/>
       <c r="D104" s="12" t="n"/>
-      <c r="E104" s="38" t="n"/>
+      <c r="E104" s="41" t="n"/>
       <c r="F104" s="16" t="n"/>
-      <c r="G104" s="36">
+      <c r="G104" s="39">
         <f>IF(OR(E104="",F104=""),"",ROUND(E104*F104,2))</f>
         <v/>
       </c>
@@ -3520,9 +3576,9 @@
       <c r="B105" s="12" t="n"/>
       <c r="C105" s="12" t="n"/>
       <c r="D105" s="12" t="n"/>
-      <c r="E105" s="38" t="n"/>
+      <c r="E105" s="41" t="n"/>
       <c r="F105" s="16" t="n"/>
-      <c r="G105" s="36">
+      <c r="G105" s="39">
         <f>IF(OR(E105="",F105=""),"",ROUND(E105*F105,2))</f>
         <v/>
       </c>
@@ -3534,9 +3590,9 @@
       <c r="B106" s="12" t="n"/>
       <c r="C106" s="12" t="n"/>
       <c r="D106" s="12" t="n"/>
-      <c r="E106" s="38" t="n"/>
+      <c r="E106" s="41" t="n"/>
       <c r="F106" s="16" t="n"/>
-      <c r="G106" s="36">
+      <c r="G106" s="39">
         <f>IF(OR(E106="",F106=""),"",ROUND(E106*F106,2))</f>
         <v/>
       </c>
@@ -3548,9 +3604,9 @@
       <c r="B107" s="12" t="n"/>
       <c r="C107" s="12" t="n"/>
       <c r="D107" s="12" t="n"/>
-      <c r="E107" s="38" t="n"/>
+      <c r="E107" s="41" t="n"/>
       <c r="F107" s="16" t="n"/>
-      <c r="G107" s="36">
+      <c r="G107" s="39">
         <f>IF(OR(E107="",F107=""),"",ROUND(E107*F107,2))</f>
         <v/>
       </c>
@@ -3562,9 +3618,9 @@
       <c r="B108" s="12" t="n"/>
       <c r="C108" s="12" t="n"/>
       <c r="D108" s="12" t="n"/>
-      <c r="E108" s="38" t="n"/>
+      <c r="E108" s="41" t="n"/>
       <c r="F108" s="16" t="n"/>
-      <c r="G108" s="36">
+      <c r="G108" s="39">
         <f>IF(OR(E108="",F108=""),"",ROUND(E108*F108,2))</f>
         <v/>
       </c>
@@ -3576,9 +3632,9 @@
       <c r="B109" s="12" t="n"/>
       <c r="C109" s="12" t="n"/>
       <c r="D109" s="12" t="n"/>
-      <c r="E109" s="38" t="n"/>
+      <c r="E109" s="41" t="n"/>
       <c r="F109" s="16" t="n"/>
-      <c r="G109" s="36">
+      <c r="G109" s="39">
         <f>IF(OR(E109="",F109=""),"",ROUND(E109*F109,2))</f>
         <v/>
       </c>
@@ -3590,9 +3646,9 @@
       <c r="B110" s="12" t="n"/>
       <c r="C110" s="12" t="n"/>
       <c r="D110" s="12" t="n"/>
-      <c r="E110" s="38" t="n"/>
+      <c r="E110" s="41" t="n"/>
       <c r="F110" s="16" t="n"/>
-      <c r="G110" s="36">
+      <c r="G110" s="39">
         <f>IF(OR(E110="",F110=""),"",ROUND(E110*F110,2))</f>
         <v/>
       </c>
@@ -3604,9 +3660,9 @@
       <c r="B111" s="12" t="n"/>
       <c r="C111" s="12" t="n"/>
       <c r="D111" s="12" t="n"/>
-      <c r="E111" s="38" t="n"/>
+      <c r="E111" s="41" t="n"/>
       <c r="F111" s="16" t="n"/>
-      <c r="G111" s="36">
+      <c r="G111" s="39">
         <f>IF(OR(E111="",F111=""),"",ROUND(E111*F111,2))</f>
         <v/>
       </c>
@@ -3618,9 +3674,9 @@
       <c r="B112" s="12" t="n"/>
       <c r="C112" s="12" t="n"/>
       <c r="D112" s="12" t="n"/>
-      <c r="E112" s="38" t="n"/>
+      <c r="E112" s="41" t="n"/>
       <c r="F112" s="16" t="n"/>
-      <c r="G112" s="36">
+      <c r="G112" s="39">
         <f>IF(OR(E112="",F112=""),"",ROUND(E112*F112,2))</f>
         <v/>
       </c>
@@ -3632,9 +3688,9 @@
       <c r="B113" s="12" t="n"/>
       <c r="C113" s="12" t="n"/>
       <c r="D113" s="12" t="n"/>
-      <c r="E113" s="38" t="n"/>
+      <c r="E113" s="41" t="n"/>
       <c r="F113" s="16" t="n"/>
-      <c r="G113" s="36">
+      <c r="G113" s="39">
         <f>IF(OR(E113="",F113=""),"",ROUND(E113*F113,2))</f>
         <v/>
       </c>
@@ -3646,9 +3702,9 @@
       <c r="B114" s="12" t="n"/>
       <c r="C114" s="12" t="n"/>
       <c r="D114" s="12" t="n"/>
-      <c r="E114" s="38" t="n"/>
+      <c r="E114" s="41" t="n"/>
       <c r="F114" s="16" t="n"/>
-      <c r="G114" s="36">
+      <c r="G114" s="39">
         <f>IF(OR(E114="",F114=""),"",ROUND(E114*F114,2))</f>
         <v/>
       </c>
@@ -3660,9 +3716,9 @@
       <c r="B115" s="12" t="n"/>
       <c r="C115" s="12" t="n"/>
       <c r="D115" s="12" t="n"/>
-      <c r="E115" s="38" t="n"/>
+      <c r="E115" s="41" t="n"/>
       <c r="F115" s="16" t="n"/>
-      <c r="G115" s="36">
+      <c r="G115" s="39">
         <f>IF(OR(E115="",F115=""),"",ROUND(E115*F115,2))</f>
         <v/>
       </c>
@@ -3674,9 +3730,9 @@
       <c r="B116" s="12" t="n"/>
       <c r="C116" s="12" t="n"/>
       <c r="D116" s="12" t="n"/>
-      <c r="E116" s="38" t="n"/>
+      <c r="E116" s="41" t="n"/>
       <c r="F116" s="16" t="n"/>
-      <c r="G116" s="36">
+      <c r="G116" s="39">
         <f>IF(OR(E116="",F116=""),"",ROUND(E116*F116,2))</f>
         <v/>
       </c>
@@ -3688,9 +3744,9 @@
       <c r="B117" s="12" t="n"/>
       <c r="C117" s="12" t="n"/>
       <c r="D117" s="12" t="n"/>
-      <c r="E117" s="38" t="n"/>
+      <c r="E117" s="41" t="n"/>
       <c r="F117" s="16" t="n"/>
-      <c r="G117" s="36">
+      <c r="G117" s="39">
         <f>IF(OR(E117="",F117=""),"",ROUND(E117*F117,2))</f>
         <v/>
       </c>
@@ -3702,9 +3758,9 @@
       <c r="B118" s="12" t="n"/>
       <c r="C118" s="12" t="n"/>
       <c r="D118" s="12" t="n"/>
-      <c r="E118" s="38" t="n"/>
+      <c r="E118" s="41" t="n"/>
       <c r="F118" s="16" t="n"/>
-      <c r="G118" s="36">
+      <c r="G118" s="39">
         <f>IF(OR(E118="",F118=""),"",ROUND(E118*F118,2))</f>
         <v/>
       </c>
@@ -3716,9 +3772,9 @@
       <c r="B119" s="12" t="n"/>
       <c r="C119" s="12" t="n"/>
       <c r="D119" s="12" t="n"/>
-      <c r="E119" s="38" t="n"/>
+      <c r="E119" s="41" t="n"/>
       <c r="F119" s="16" t="n"/>
-      <c r="G119" s="36">
+      <c r="G119" s="39">
         <f>IF(OR(E119="",F119=""),"",ROUND(E119*F119,2))</f>
         <v/>
       </c>
@@ -3730,9 +3786,9 @@
       <c r="B120" s="12" t="n"/>
       <c r="C120" s="12" t="n"/>
       <c r="D120" s="12" t="n"/>
-      <c r="E120" s="38" t="n"/>
+      <c r="E120" s="41" t="n"/>
       <c r="F120" s="16" t="n"/>
-      <c r="G120" s="36">
+      <c r="G120" s="39">
         <f>IF(OR(E120="",F120=""),"",ROUND(E120*F120,2))</f>
         <v/>
       </c>
@@ -3744,9 +3800,9 @@
       <c r="B121" s="12" t="n"/>
       <c r="C121" s="12" t="n"/>
       <c r="D121" s="12" t="n"/>
-      <c r="E121" s="38" t="n"/>
+      <c r="E121" s="41" t="n"/>
       <c r="F121" s="16" t="n"/>
-      <c r="G121" s="36">
+      <c r="G121" s="39">
         <f>IF(OR(E121="",F121=""),"",ROUND(E121*F121,2))</f>
         <v/>
       </c>
@@ -3758,9 +3814,9 @@
       <c r="B122" s="12" t="n"/>
       <c r="C122" s="12" t="n"/>
       <c r="D122" s="12" t="n"/>
-      <c r="E122" s="38" t="n"/>
+      <c r="E122" s="41" t="n"/>
       <c r="F122" s="16" t="n"/>
-      <c r="G122" s="36">
+      <c r="G122" s="39">
         <f>IF(OR(E122="",F122=""),"",ROUND(E122*F122,2))</f>
         <v/>
       </c>
@@ -3772,9 +3828,9 @@
       <c r="B123" s="12" t="n"/>
       <c r="C123" s="12" t="n"/>
       <c r="D123" s="12" t="n"/>
-      <c r="E123" s="38" t="n"/>
+      <c r="E123" s="41" t="n"/>
       <c r="F123" s="16" t="n"/>
-      <c r="G123" s="36">
+      <c r="G123" s="39">
         <f>IF(OR(E123="",F123=""),"",ROUND(E123*F123,2))</f>
         <v/>
       </c>
@@ -3786,9 +3842,9 @@
       <c r="B124" s="12" t="n"/>
       <c r="C124" s="12" t="n"/>
       <c r="D124" s="12" t="n"/>
-      <c r="E124" s="38" t="n"/>
+      <c r="E124" s="41" t="n"/>
       <c r="F124" s="16" t="n"/>
-      <c r="G124" s="36">
+      <c r="G124" s="39">
         <f>IF(OR(E124="",F124=""),"",ROUND(E124*F124,2))</f>
         <v/>
       </c>
@@ -3800,9 +3856,9 @@
       <c r="B125" s="12" t="n"/>
       <c r="C125" s="12" t="n"/>
       <c r="D125" s="12" t="n"/>
-      <c r="E125" s="38" t="n"/>
+      <c r="E125" s="41" t="n"/>
       <c r="F125" s="16" t="n"/>
-      <c r="G125" s="36">
+      <c r="G125" s="39">
         <f>IF(OR(E125="",F125=""),"",ROUND(E125*F125,2))</f>
         <v/>
       </c>
@@ -3814,9 +3870,9 @@
       <c r="B126" s="12" t="n"/>
       <c r="C126" s="12" t="n"/>
       <c r="D126" s="12" t="n"/>
-      <c r="E126" s="38" t="n"/>
+      <c r="E126" s="41" t="n"/>
       <c r="F126" s="16" t="n"/>
-      <c r="G126" s="36">
+      <c r="G126" s="39">
         <f>IF(OR(E126="",F126=""),"",ROUND(E126*F126,2))</f>
         <v/>
       </c>
@@ -3828,9 +3884,9 @@
       <c r="B127" s="12" t="n"/>
       <c r="C127" s="12" t="n"/>
       <c r="D127" s="12" t="n"/>
-      <c r="E127" s="38" t="n"/>
+      <c r="E127" s="41" t="n"/>
       <c r="F127" s="16" t="n"/>
-      <c r="G127" s="36">
+      <c r="G127" s="39">
         <f>IF(OR(E127="",F127=""),"",ROUND(E127*F127,2))</f>
         <v/>
       </c>
@@ -3842,9 +3898,9 @@
       <c r="B128" s="12" t="n"/>
       <c r="C128" s="12" t="n"/>
       <c r="D128" s="12" t="n"/>
-      <c r="E128" s="38" t="n"/>
+      <c r="E128" s="41" t="n"/>
       <c r="F128" s="16" t="n"/>
-      <c r="G128" s="36">
+      <c r="G128" s="39">
         <f>IF(OR(E128="",F128=""),"",ROUND(E128*F128,2))</f>
         <v/>
       </c>
@@ -3856,9 +3912,9 @@
       <c r="B129" s="12" t="n"/>
       <c r="C129" s="12" t="n"/>
       <c r="D129" s="12" t="n"/>
-      <c r="E129" s="38" t="n"/>
+      <c r="E129" s="41" t="n"/>
       <c r="F129" s="16" t="n"/>
-      <c r="G129" s="36">
+      <c r="G129" s="39">
         <f>IF(OR(E129="",F129=""),"",ROUND(E129*F129,2))</f>
         <v/>
       </c>
@@ -3870,9 +3926,9 @@
       <c r="B130" s="12" t="n"/>
       <c r="C130" s="12" t="n"/>
       <c r="D130" s="12" t="n"/>
-      <c r="E130" s="38" t="n"/>
+      <c r="E130" s="41" t="n"/>
       <c r="F130" s="16" t="n"/>
-      <c r="G130" s="36">
+      <c r="G130" s="39">
         <f>IF(OR(E130="",F130=""),"",ROUND(E130*F130,2))</f>
         <v/>
       </c>
@@ -3884,9 +3940,9 @@
       <c r="B131" s="12" t="n"/>
       <c r="C131" s="12" t="n"/>
       <c r="D131" s="12" t="n"/>
-      <c r="E131" s="38" t="n"/>
+      <c r="E131" s="41" t="n"/>
       <c r="F131" s="16" t="n"/>
-      <c r="G131" s="36">
+      <c r="G131" s="39">
         <f>IF(OR(E131="",F131=""),"",ROUND(E131*F131,2))</f>
         <v/>
       </c>
@@ -3898,9 +3954,9 @@
       <c r="B132" s="12" t="n"/>
       <c r="C132" s="12" t="n"/>
       <c r="D132" s="12" t="n"/>
-      <c r="E132" s="38" t="n"/>
+      <c r="E132" s="41" t="n"/>
       <c r="F132" s="16" t="n"/>
-      <c r="G132" s="36">
+      <c r="G132" s="39">
         <f>IF(OR(E132="",F132=""),"",ROUND(E132*F132,2))</f>
         <v/>
       </c>
@@ -3912,9 +3968,9 @@
       <c r="B133" s="12" t="n"/>
       <c r="C133" s="12" t="n"/>
       <c r="D133" s="12" t="n"/>
-      <c r="E133" s="38" t="n"/>
+      <c r="E133" s="41" t="n"/>
       <c r="F133" s="16" t="n"/>
-      <c r="G133" s="36">
+      <c r="G133" s="39">
         <f>IF(OR(E133="",F133=""),"",ROUND(E133*F133,2))</f>
         <v/>
       </c>
@@ -3926,9 +3982,9 @@
       <c r="B134" s="12" t="n"/>
       <c r="C134" s="12" t="n"/>
       <c r="D134" s="12" t="n"/>
-      <c r="E134" s="38" t="n"/>
+      <c r="E134" s="41" t="n"/>
       <c r="F134" s="16" t="n"/>
-      <c r="G134" s="36">
+      <c r="G134" s="39">
         <f>IF(OR(E134="",F134=""),"",ROUND(E134*F134,2))</f>
         <v/>
       </c>
@@ -3940,9 +3996,9 @@
       <c r="B135" s="12" t="n"/>
       <c r="C135" s="12" t="n"/>
       <c r="D135" s="12" t="n"/>
-      <c r="E135" s="38" t="n"/>
+      <c r="E135" s="41" t="n"/>
       <c r="F135" s="16" t="n"/>
-      <c r="G135" s="36">
+      <c r="G135" s="39">
         <f>IF(OR(E135="",F135=""),"",ROUND(E135*F135,2))</f>
         <v/>
       </c>
@@ -3954,9 +4010,9 @@
       <c r="B136" s="12" t="n"/>
       <c r="C136" s="12" t="n"/>
       <c r="D136" s="12" t="n"/>
-      <c r="E136" s="38" t="n"/>
+      <c r="E136" s="41" t="n"/>
       <c r="F136" s="16" t="n"/>
-      <c r="G136" s="36">
+      <c r="G136" s="39">
         <f>IF(OR(E136="",F136=""),"",ROUND(E136*F136,2))</f>
         <v/>
       </c>
@@ -3968,9 +4024,9 @@
       <c r="B137" s="12" t="n"/>
       <c r="C137" s="12" t="n"/>
       <c r="D137" s="12" t="n"/>
-      <c r="E137" s="38" t="n"/>
+      <c r="E137" s="41" t="n"/>
       <c r="F137" s="16" t="n"/>
-      <c r="G137" s="36">
+      <c r="G137" s="39">
         <f>IF(OR(E137="",F137=""),"",ROUND(E137*F137,2))</f>
         <v/>
       </c>
@@ -3982,9 +4038,9 @@
       <c r="B138" s="12" t="n"/>
       <c r="C138" s="12" t="n"/>
       <c r="D138" s="12" t="n"/>
-      <c r="E138" s="38" t="n"/>
+      <c r="E138" s="41" t="n"/>
       <c r="F138" s="16" t="n"/>
-      <c r="G138" s="36">
+      <c r="G138" s="39">
         <f>IF(OR(E138="",F138=""),"",ROUND(E138*F138,2))</f>
         <v/>
       </c>
@@ -3996,9 +4052,9 @@
       <c r="B139" s="12" t="n"/>
       <c r="C139" s="12" t="n"/>
       <c r="D139" s="12" t="n"/>
-      <c r="E139" s="38" t="n"/>
+      <c r="E139" s="41" t="n"/>
       <c r="F139" s="16" t="n"/>
-      <c r="G139" s="36">
+      <c r="G139" s="39">
         <f>IF(OR(E139="",F139=""),"",ROUND(E139*F139,2))</f>
         <v/>
       </c>
@@ -4010,9 +4066,9 @@
       <c r="B140" s="12" t="n"/>
       <c r="C140" s="12" t="n"/>
       <c r="D140" s="12" t="n"/>
-      <c r="E140" s="38" t="n"/>
+      <c r="E140" s="41" t="n"/>
       <c r="F140" s="16" t="n"/>
-      <c r="G140" s="36">
+      <c r="G140" s="39">
         <f>IF(OR(E140="",F140=""),"",ROUND(E140*F140,2))</f>
         <v/>
       </c>
@@ -4024,9 +4080,9 @@
       <c r="B141" s="12" t="n"/>
       <c r="C141" s="12" t="n"/>
       <c r="D141" s="12" t="n"/>
-      <c r="E141" s="38" t="n"/>
+      <c r="E141" s="41" t="n"/>
       <c r="F141" s="16" t="n"/>
-      <c r="G141" s="36">
+      <c r="G141" s="39">
         <f>IF(OR(E141="",F141=""),"",ROUND(E141*F141,2))</f>
         <v/>
       </c>
@@ -4038,9 +4094,9 @@
       <c r="B142" s="12" t="n"/>
       <c r="C142" s="12" t="n"/>
       <c r="D142" s="12" t="n"/>
-      <c r="E142" s="38" t="n"/>
+      <c r="E142" s="41" t="n"/>
       <c r="F142" s="16" t="n"/>
-      <c r="G142" s="36">
+      <c r="G142" s="39">
         <f>IF(OR(E142="",F142=""),"",ROUND(E142*F142,2))</f>
         <v/>
       </c>
@@ -4052,9 +4108,9 @@
       <c r="B143" s="12" t="n"/>
       <c r="C143" s="12" t="n"/>
       <c r="D143" s="12" t="n"/>
-      <c r="E143" s="38" t="n"/>
+      <c r="E143" s="41" t="n"/>
       <c r="F143" s="16" t="n"/>
-      <c r="G143" s="36">
+      <c r="G143" s="39">
         <f>IF(OR(E143="",F143=""),"",ROUND(E143*F143,2))</f>
         <v/>
       </c>
@@ -4066,9 +4122,9 @@
       <c r="B144" s="12" t="n"/>
       <c r="C144" s="12" t="n"/>
       <c r="D144" s="12" t="n"/>
-      <c r="E144" s="38" t="n"/>
+      <c r="E144" s="41" t="n"/>
       <c r="F144" s="16" t="n"/>
-      <c r="G144" s="36">
+      <c r="G144" s="39">
         <f>IF(OR(E144="",F144=""),"",ROUND(E144*F144,2))</f>
         <v/>
       </c>
@@ -4080,9 +4136,9 @@
       <c r="B145" s="12" t="n"/>
       <c r="C145" s="12" t="n"/>
       <c r="D145" s="12" t="n"/>
-      <c r="E145" s="38" t="n"/>
+      <c r="E145" s="41" t="n"/>
       <c r="F145" s="16" t="n"/>
-      <c r="G145" s="36">
+      <c r="G145" s="39">
         <f>IF(OR(E145="",F145=""),"",ROUND(E145*F145,2))</f>
         <v/>
       </c>
@@ -4094,9 +4150,9 @@
       <c r="B146" s="12" t="n"/>
       <c r="C146" s="12" t="n"/>
       <c r="D146" s="12" t="n"/>
-      <c r="E146" s="38" t="n"/>
+      <c r="E146" s="41" t="n"/>
       <c r="F146" s="16" t="n"/>
-      <c r="G146" s="36">
+      <c r="G146" s="39">
         <f>IF(OR(E146="",F146=""),"",ROUND(E146*F146,2))</f>
         <v/>
       </c>
@@ -4108,9 +4164,9 @@
       <c r="B147" s="12" t="n"/>
       <c r="C147" s="12" t="n"/>
       <c r="D147" s="12" t="n"/>
-      <c r="E147" s="38" t="n"/>
+      <c r="E147" s="41" t="n"/>
       <c r="F147" s="16" t="n"/>
-      <c r="G147" s="36">
+      <c r="G147" s="39">
         <f>IF(OR(E147="",F147=""),"",ROUND(E147*F147,2))</f>
         <v/>
       </c>
@@ -4122,9 +4178,9 @@
       <c r="B148" s="12" t="n"/>
       <c r="C148" s="12" t="n"/>
       <c r="D148" s="12" t="n"/>
-      <c r="E148" s="38" t="n"/>
+      <c r="E148" s="41" t="n"/>
       <c r="F148" s="16" t="n"/>
-      <c r="G148" s="36">
+      <c r="G148" s="39">
         <f>IF(OR(E148="",F148=""),"",ROUND(E148*F148,2))</f>
         <v/>
       </c>
@@ -4136,9 +4192,9 @@
       <c r="B149" s="12" t="n"/>
       <c r="C149" s="12" t="n"/>
       <c r="D149" s="12" t="n"/>
-      <c r="E149" s="38" t="n"/>
+      <c r="E149" s="41" t="n"/>
       <c r="F149" s="16" t="n"/>
-      <c r="G149" s="36">
+      <c r="G149" s="39">
         <f>IF(OR(E149="",F149=""),"",ROUND(E149*F149,2))</f>
         <v/>
       </c>
@@ -4150,9 +4206,9 @@
       <c r="B150" s="12" t="n"/>
       <c r="C150" s="12" t="n"/>
       <c r="D150" s="12" t="n"/>
-      <c r="E150" s="38" t="n"/>
+      <c r="E150" s="41" t="n"/>
       <c r="F150" s="16" t="n"/>
-      <c r="G150" s="36">
+      <c r="G150" s="39">
         <f>IF(OR(E150="",F150=""),"",ROUND(E150*F150,2))</f>
         <v/>
       </c>
@@ -4164,9 +4220,9 @@
       <c r="B151" s="12" t="n"/>
       <c r="C151" s="12" t="n"/>
       <c r="D151" s="12" t="n"/>
-      <c r="E151" s="38" t="n"/>
+      <c r="E151" s="41" t="n"/>
       <c r="F151" s="16" t="n"/>
-      <c r="G151" s="36">
+      <c r="G151" s="39">
         <f>IF(OR(E151="",F151=""),"",ROUND(E151*F151,2))</f>
         <v/>
       </c>
@@ -4178,9 +4234,9 @@
       <c r="B152" s="12" t="n"/>
       <c r="C152" s="12" t="n"/>
       <c r="D152" s="12" t="n"/>
-      <c r="E152" s="38" t="n"/>
+      <c r="E152" s="41" t="n"/>
       <c r="F152" s="16" t="n"/>
-      <c r="G152" s="36">
+      <c r="G152" s="39">
         <f>IF(OR(E152="",F152=""),"",ROUND(E152*F152,2))</f>
         <v/>
       </c>
@@ -4192,9 +4248,9 @@
       <c r="B153" s="12" t="n"/>
       <c r="C153" s="12" t="n"/>
       <c r="D153" s="12" t="n"/>
-      <c r="E153" s="38" t="n"/>
+      <c r="E153" s="41" t="n"/>
       <c r="F153" s="16" t="n"/>
-      <c r="G153" s="36">
+      <c r="G153" s="39">
         <f>IF(OR(E153="",F153=""),"",ROUND(E153*F153,2))</f>
         <v/>
       </c>
@@ -4206,9 +4262,9 @@
       <c r="B154" s="12" t="n"/>
       <c r="C154" s="12" t="n"/>
       <c r="D154" s="12" t="n"/>
-      <c r="E154" s="38" t="n"/>
+      <c r="E154" s="41" t="n"/>
       <c r="F154" s="16" t="n"/>
-      <c r="G154" s="36">
+      <c r="G154" s="39">
         <f>IF(OR(E154="",F154=""),"",ROUND(E154*F154,2))</f>
         <v/>
       </c>
@@ -4220,9 +4276,9 @@
       <c r="B155" s="12" t="n"/>
       <c r="C155" s="12" t="n"/>
       <c r="D155" s="12" t="n"/>
-      <c r="E155" s="38" t="n"/>
+      <c r="E155" s="41" t="n"/>
       <c r="F155" s="16" t="n"/>
-      <c r="G155" s="36">
+      <c r="G155" s="39">
         <f>IF(OR(E155="",F155=""),"",ROUND(E155*F155,2))</f>
         <v/>
       </c>
@@ -4234,9 +4290,9 @@
       <c r="B156" s="12" t="n"/>
       <c r="C156" s="12" t="n"/>
       <c r="D156" s="12" t="n"/>
-      <c r="E156" s="38" t="n"/>
+      <c r="E156" s="41" t="n"/>
       <c r="F156" s="16" t="n"/>
-      <c r="G156" s="36">
+      <c r="G156" s="39">
         <f>IF(OR(E156="",F156=""),"",ROUND(E156*F156,2))</f>
         <v/>
       </c>
@@ -4248,9 +4304,9 @@
       <c r="B157" s="12" t="n"/>
       <c r="C157" s="12" t="n"/>
       <c r="D157" s="12" t="n"/>
-      <c r="E157" s="38" t="n"/>
+      <c r="E157" s="41" t="n"/>
       <c r="F157" s="16" t="n"/>
-      <c r="G157" s="36">
+      <c r="G157" s="39">
         <f>IF(OR(E157="",F157=""),"",ROUND(E157*F157,2))</f>
         <v/>
       </c>
@@ -4262,9 +4318,9 @@
       <c r="B158" s="12" t="n"/>
       <c r="C158" s="12" t="n"/>
       <c r="D158" s="12" t="n"/>
-      <c r="E158" s="38" t="n"/>
+      <c r="E158" s="41" t="n"/>
       <c r="F158" s="16" t="n"/>
-      <c r="G158" s="36">
+      <c r="G158" s="39">
         <f>IF(OR(E158="",F158=""),"",ROUND(E158*F158,2))</f>
         <v/>
       </c>
@@ -4276,9 +4332,9 @@
       <c r="B159" s="12" t="n"/>
       <c r="C159" s="12" t="n"/>
       <c r="D159" s="12" t="n"/>
-      <c r="E159" s="38" t="n"/>
+      <c r="E159" s="41" t="n"/>
       <c r="F159" s="16" t="n"/>
-      <c r="G159" s="36">
+      <c r="G159" s="39">
         <f>IF(OR(E159="",F159=""),"",ROUND(E159*F159,2))</f>
         <v/>
       </c>
@@ -4290,9 +4346,9 @@
       <c r="B160" s="12" t="n"/>
       <c r="C160" s="12" t="n"/>
       <c r="D160" s="12" t="n"/>
-      <c r="E160" s="38" t="n"/>
+      <c r="E160" s="41" t="n"/>
       <c r="F160" s="16" t="n"/>
-      <c r="G160" s="36">
+      <c r="G160" s="39">
         <f>IF(OR(E160="",F160=""),"",ROUND(E160*F160,2))</f>
         <v/>
       </c>
@@ -4304,9 +4360,9 @@
       <c r="B161" s="12" t="n"/>
       <c r="C161" s="12" t="n"/>
       <c r="D161" s="12" t="n"/>
-      <c r="E161" s="38" t="n"/>
+      <c r="E161" s="41" t="n"/>
       <c r="F161" s="16" t="n"/>
-      <c r="G161" s="36">
+      <c r="G161" s="39">
         <f>IF(OR(E161="",F161=""),"",ROUND(E161*F161,2))</f>
         <v/>
       </c>
@@ -4318,9 +4374,9 @@
       <c r="B162" s="12" t="n"/>
       <c r="C162" s="12" t="n"/>
       <c r="D162" s="12" t="n"/>
-      <c r="E162" s="38" t="n"/>
+      <c r="E162" s="41" t="n"/>
       <c r="F162" s="16" t="n"/>
-      <c r="G162" s="36">
+      <c r="G162" s="39">
         <f>IF(OR(E162="",F162=""),"",ROUND(E162*F162,2))</f>
         <v/>
       </c>
@@ -4332,9 +4388,9 @@
       <c r="B163" s="12" t="n"/>
       <c r="C163" s="12" t="n"/>
       <c r="D163" s="12" t="n"/>
-      <c r="E163" s="38" t="n"/>
+      <c r="E163" s="41" t="n"/>
       <c r="F163" s="16" t="n"/>
-      <c r="G163" s="36">
+      <c r="G163" s="39">
         <f>IF(OR(E163="",F163=""),"",ROUND(E163*F163,2))</f>
         <v/>
       </c>
@@ -4346,9 +4402,9 @@
       <c r="B164" s="12" t="n"/>
       <c r="C164" s="12" t="n"/>
       <c r="D164" s="12" t="n"/>
-      <c r="E164" s="38" t="n"/>
+      <c r="E164" s="41" t="n"/>
       <c r="F164" s="16" t="n"/>
-      <c r="G164" s="36">
+      <c r="G164" s="39">
         <f>IF(OR(E164="",F164=""),"",ROUND(E164*F164,2))</f>
         <v/>
       </c>
@@ -4360,9 +4416,9 @@
       <c r="B165" s="12" t="n"/>
       <c r="C165" s="12" t="n"/>
       <c r="D165" s="12" t="n"/>
-      <c r="E165" s="38" t="n"/>
+      <c r="E165" s="41" t="n"/>
       <c r="F165" s="16" t="n"/>
-      <c r="G165" s="36">
+      <c r="G165" s="39">
         <f>IF(OR(E165="",F165=""),"",ROUND(E165*F165,2))</f>
         <v/>
       </c>
@@ -4374,9 +4430,9 @@
       <c r="B166" s="12" t="n"/>
       <c r="C166" s="12" t="n"/>
       <c r="D166" s="12" t="n"/>
-      <c r="E166" s="38" t="n"/>
+      <c r="E166" s="41" t="n"/>
       <c r="F166" s="16" t="n"/>
-      <c r="G166" s="36">
+      <c r="G166" s="39">
         <f>IF(OR(E166="",F166=""),"",ROUND(E166*F166,2))</f>
         <v/>
       </c>
@@ -4388,9 +4444,9 @@
       <c r="B167" s="12" t="n"/>
       <c r="C167" s="12" t="n"/>
       <c r="D167" s="12" t="n"/>
-      <c r="E167" s="38" t="n"/>
+      <c r="E167" s="41" t="n"/>
       <c r="F167" s="16" t="n"/>
-      <c r="G167" s="36">
+      <c r="G167" s="39">
         <f>IF(OR(E167="",F167=""),"",ROUND(E167*F167,2))</f>
         <v/>
       </c>
@@ -4402,9 +4458,9 @@
       <c r="B168" s="12" t="n"/>
       <c r="C168" s="12" t="n"/>
       <c r="D168" s="12" t="n"/>
-      <c r="E168" s="38" t="n"/>
+      <c r="E168" s="41" t="n"/>
       <c r="F168" s="16" t="n"/>
-      <c r="G168" s="36">
+      <c r="G168" s="39">
         <f>IF(OR(E168="",F168=""),"",ROUND(E168*F168,2))</f>
         <v/>
       </c>
@@ -4416,9 +4472,9 @@
       <c r="B169" s="12" t="n"/>
       <c r="C169" s="12" t="n"/>
       <c r="D169" s="12" t="n"/>
-      <c r="E169" s="38" t="n"/>
+      <c r="E169" s="41" t="n"/>
       <c r="F169" s="16" t="n"/>
-      <c r="G169" s="36">
+      <c r="G169" s="39">
         <f>IF(OR(E169="",F169=""),"",ROUND(E169*F169,2))</f>
         <v/>
       </c>
@@ -4430,9 +4486,9 @@
       <c r="B170" s="12" t="n"/>
       <c r="C170" s="12" t="n"/>
       <c r="D170" s="12" t="n"/>
-      <c r="E170" s="38" t="n"/>
+      <c r="E170" s="41" t="n"/>
       <c r="F170" s="16" t="n"/>
-      <c r="G170" s="36">
+      <c r="G170" s="39">
         <f>IF(OR(E170="",F170=""),"",ROUND(E170*F170,2))</f>
         <v/>
       </c>
@@ -4444,9 +4500,9 @@
       <c r="B171" s="12" t="n"/>
       <c r="C171" s="12" t="n"/>
       <c r="D171" s="12" t="n"/>
-      <c r="E171" s="38" t="n"/>
+      <c r="E171" s="41" t="n"/>
       <c r="F171" s="16" t="n"/>
-      <c r="G171" s="36">
+      <c r="G171" s="39">
         <f>IF(OR(E171="",F171=""),"",ROUND(E171*F171,2))</f>
         <v/>
       </c>
@@ -4458,9 +4514,9 @@
       <c r="B172" s="12" t="n"/>
       <c r="C172" s="12" t="n"/>
       <c r="D172" s="12" t="n"/>
-      <c r="E172" s="38" t="n"/>
+      <c r="E172" s="41" t="n"/>
       <c r="F172" s="16" t="n"/>
-      <c r="G172" s="36">
+      <c r="G172" s="39">
         <f>IF(OR(E172="",F172=""),"",ROUND(E172*F172,2))</f>
         <v/>
       </c>
@@ -4472,9 +4528,9 @@
       <c r="B173" s="12" t="n"/>
       <c r="C173" s="12" t="n"/>
       <c r="D173" s="12" t="n"/>
-      <c r="E173" s="38" t="n"/>
+      <c r="E173" s="41" t="n"/>
       <c r="F173" s="16" t="n"/>
-      <c r="G173" s="36">
+      <c r="G173" s="39">
         <f>IF(OR(E173="",F173=""),"",ROUND(E173*F173,2))</f>
         <v/>
       </c>
@@ -4486,9 +4542,9 @@
       <c r="B174" s="12" t="n"/>
       <c r="C174" s="12" t="n"/>
       <c r="D174" s="12" t="n"/>
-      <c r="E174" s="38" t="n"/>
+      <c r="E174" s="41" t="n"/>
       <c r="F174" s="16" t="n"/>
-      <c r="G174" s="36">
+      <c r="G174" s="39">
         <f>IF(OR(E174="",F174=""),"",ROUND(E174*F174,2))</f>
         <v/>
       </c>
@@ -4500,9 +4556,9 @@
       <c r="B175" s="12" t="n"/>
       <c r="C175" s="12" t="n"/>
       <c r="D175" s="12" t="n"/>
-      <c r="E175" s="38" t="n"/>
+      <c r="E175" s="41" t="n"/>
       <c r="F175" s="16" t="n"/>
-      <c r="G175" s="36">
+      <c r="G175" s="39">
         <f>IF(OR(E175="",F175=""),"",ROUND(E175*F175,2))</f>
         <v/>
       </c>
@@ -4514,9 +4570,9 @@
       <c r="B176" s="12" t="n"/>
       <c r="C176" s="12" t="n"/>
       <c r="D176" s="12" t="n"/>
-      <c r="E176" s="38" t="n"/>
+      <c r="E176" s="41" t="n"/>
       <c r="F176" s="16" t="n"/>
-      <c r="G176" s="36">
+      <c r="G176" s="39">
         <f>IF(OR(E176="",F176=""),"",ROUND(E176*F176,2))</f>
         <v/>
       </c>
@@ -4528,9 +4584,9 @@
       <c r="B177" s="12" t="n"/>
       <c r="C177" s="12" t="n"/>
       <c r="D177" s="12" t="n"/>
-      <c r="E177" s="38" t="n"/>
+      <c r="E177" s="41" t="n"/>
       <c r="F177" s="16" t="n"/>
-      <c r="G177" s="36">
+      <c r="G177" s="39">
         <f>IF(OR(E177="",F177=""),"",ROUND(E177*F177,2))</f>
         <v/>
       </c>
@@ -4542,9 +4598,9 @@
       <c r="B178" s="12" t="n"/>
       <c r="C178" s="12" t="n"/>
       <c r="D178" s="12" t="n"/>
-      <c r="E178" s="38" t="n"/>
+      <c r="E178" s="41" t="n"/>
       <c r="F178" s="16" t="n"/>
-      <c r="G178" s="36">
+      <c r="G178" s="39">
         <f>IF(OR(E178="",F178=""),"",ROUND(E178*F178,2))</f>
         <v/>
       </c>
@@ -4556,9 +4612,9 @@
       <c r="B179" s="12" t="n"/>
       <c r="C179" s="12" t="n"/>
       <c r="D179" s="12" t="n"/>
-      <c r="E179" s="38" t="n"/>
+      <c r="E179" s="41" t="n"/>
       <c r="F179" s="16" t="n"/>
-      <c r="G179" s="36">
+      <c r="G179" s="39">
         <f>IF(OR(E179="",F179=""),"",ROUND(E179*F179,2))</f>
         <v/>
       </c>
@@ -4570,9 +4626,9 @@
       <c r="B180" s="12" t="n"/>
       <c r="C180" s="12" t="n"/>
       <c r="D180" s="12" t="n"/>
-      <c r="E180" s="38" t="n"/>
+      <c r="E180" s="41" t="n"/>
       <c r="F180" s="16" t="n"/>
-      <c r="G180" s="36">
+      <c r="G180" s="39">
         <f>IF(OR(E180="",F180=""),"",ROUND(E180*F180,2))</f>
         <v/>
       </c>
@@ -4584,9 +4640,9 @@
       <c r="B181" s="12" t="n"/>
       <c r="C181" s="12" t="n"/>
       <c r="D181" s="12" t="n"/>
-      <c r="E181" s="38" t="n"/>
+      <c r="E181" s="41" t="n"/>
       <c r="F181" s="16" t="n"/>
-      <c r="G181" s="36">
+      <c r="G181" s="39">
         <f>IF(OR(E181="",F181=""),"",ROUND(E181*F181,2))</f>
         <v/>
       </c>
@@ -4598,9 +4654,9 @@
       <c r="B182" s="12" t="n"/>
       <c r="C182" s="12" t="n"/>
       <c r="D182" s="12" t="n"/>
-      <c r="E182" s="38" t="n"/>
+      <c r="E182" s="41" t="n"/>
       <c r="F182" s="16" t="n"/>
-      <c r="G182" s="36">
+      <c r="G182" s="39">
         <f>IF(OR(E182="",F182=""),"",ROUND(E182*F182,2))</f>
         <v/>
       </c>
@@ -4612,9 +4668,9 @@
       <c r="B183" s="12" t="n"/>
       <c r="C183" s="12" t="n"/>
       <c r="D183" s="12" t="n"/>
-      <c r="E183" s="38" t="n"/>
+      <c r="E183" s="41" t="n"/>
       <c r="F183" s="16" t="n"/>
-      <c r="G183" s="36">
+      <c r="G183" s="39">
         <f>IF(OR(E183="",F183=""),"",ROUND(E183*F183,2))</f>
         <v/>
       </c>
@@ -4626,9 +4682,9 @@
       <c r="B184" s="12" t="n"/>
       <c r="C184" s="12" t="n"/>
       <c r="D184" s="12" t="n"/>
-      <c r="E184" s="38" t="n"/>
+      <c r="E184" s="41" t="n"/>
       <c r="F184" s="16" t="n"/>
-      <c r="G184" s="36">
+      <c r="G184" s="39">
         <f>IF(OR(E184="",F184=""),"",ROUND(E184*F184,2))</f>
         <v/>
       </c>
@@ -4640,9 +4696,9 @@
       <c r="B185" s="12" t="n"/>
       <c r="C185" s="12" t="n"/>
       <c r="D185" s="12" t="n"/>
-      <c r="E185" s="38" t="n"/>
+      <c r="E185" s="41" t="n"/>
       <c r="F185" s="16" t="n"/>
-      <c r="G185" s="36">
+      <c r="G185" s="39">
         <f>IF(OR(E185="",F185=""),"",ROUND(E185*F185,2))</f>
         <v/>
       </c>
@@ -4654,9 +4710,9 @@
       <c r="B186" s="12" t="n"/>
       <c r="C186" s="12" t="n"/>
       <c r="D186" s="12" t="n"/>
-      <c r="E186" s="38" t="n"/>
+      <c r="E186" s="41" t="n"/>
       <c r="F186" s="16" t="n"/>
-      <c r="G186" s="36">
+      <c r="G186" s="39">
         <f>IF(OR(E186="",F186=""),"",ROUND(E186*F186,2))</f>
         <v/>
       </c>
@@ -4668,9 +4724,9 @@
       <c r="B187" s="12" t="n"/>
       <c r="C187" s="12" t="n"/>
       <c r="D187" s="12" t="n"/>
-      <c r="E187" s="38" t="n"/>
+      <c r="E187" s="41" t="n"/>
       <c r="F187" s="16" t="n"/>
-      <c r="G187" s="36">
+      <c r="G187" s="39">
         <f>IF(OR(E187="",F187=""),"",ROUND(E187*F187,2))</f>
         <v/>
       </c>
@@ -4682,9 +4738,9 @@
       <c r="B188" s="12" t="n"/>
       <c r="C188" s="12" t="n"/>
       <c r="D188" s="12" t="n"/>
-      <c r="E188" s="38" t="n"/>
+      <c r="E188" s="41" t="n"/>
       <c r="F188" s="16" t="n"/>
-      <c r="G188" s="36">
+      <c r="G188" s="39">
         <f>IF(OR(E188="",F188=""),"",ROUND(E188*F188,2))</f>
         <v/>
       </c>
@@ -4696,9 +4752,9 @@
       <c r="B189" s="12" t="n"/>
       <c r="C189" s="12" t="n"/>
       <c r="D189" s="12" t="n"/>
-      <c r="E189" s="38" t="n"/>
+      <c r="E189" s="41" t="n"/>
       <c r="F189" s="16" t="n"/>
-      <c r="G189" s="36">
+      <c r="G189" s="39">
         <f>IF(OR(E189="",F189=""),"",ROUND(E189*F189,2))</f>
         <v/>
       </c>
@@ -4710,9 +4766,9 @@
       <c r="B190" s="12" t="n"/>
       <c r="C190" s="12" t="n"/>
       <c r="D190" s="12" t="n"/>
-      <c r="E190" s="38" t="n"/>
+      <c r="E190" s="41" t="n"/>
       <c r="F190" s="16" t="n"/>
-      <c r="G190" s="36">
+      <c r="G190" s="39">
         <f>IF(OR(E190="",F190=""),"",ROUND(E190*F190,2))</f>
         <v/>
       </c>
@@ -4724,9 +4780,9 @@
       <c r="B191" s="12" t="n"/>
       <c r="C191" s="12" t="n"/>
       <c r="D191" s="12" t="n"/>
-      <c r="E191" s="38" t="n"/>
+      <c r="E191" s="41" t="n"/>
       <c r="F191" s="16" t="n"/>
-      <c r="G191" s="36">
+      <c r="G191" s="39">
         <f>IF(OR(E191="",F191=""),"",ROUND(E191*F191,2))</f>
         <v/>
       </c>
@@ -4738,9 +4794,9 @@
       <c r="B192" s="12" t="n"/>
       <c r="C192" s="12" t="n"/>
       <c r="D192" s="12" t="n"/>
-      <c r="E192" s="38" t="n"/>
+      <c r="E192" s="41" t="n"/>
       <c r="F192" s="16" t="n"/>
-      <c r="G192" s="36">
+      <c r="G192" s="39">
         <f>IF(OR(E192="",F192=""),"",ROUND(E192*F192,2))</f>
         <v/>
       </c>
@@ -4752,9 +4808,9 @@
       <c r="B193" s="12" t="n"/>
       <c r="C193" s="12" t="n"/>
       <c r="D193" s="12" t="n"/>
-      <c r="E193" s="38" t="n"/>
+      <c r="E193" s="41" t="n"/>
       <c r="F193" s="16" t="n"/>
-      <c r="G193" s="36">
+      <c r="G193" s="39">
         <f>IF(OR(E193="",F193=""),"",ROUND(E193*F193,2))</f>
         <v/>
       </c>
@@ -4766,9 +4822,9 @@
       <c r="B194" s="12" t="n"/>
       <c r="C194" s="12" t="n"/>
       <c r="D194" s="12" t="n"/>
-      <c r="E194" s="38" t="n"/>
+      <c r="E194" s="41" t="n"/>
       <c r="F194" s="16" t="n"/>
-      <c r="G194" s="36">
+      <c r="G194" s="39">
         <f>IF(OR(E194="",F194=""),"",ROUND(E194*F194,2))</f>
         <v/>
       </c>
@@ -4780,9 +4836,9 @@
       <c r="B195" s="12" t="n"/>
       <c r="C195" s="12" t="n"/>
       <c r="D195" s="12" t="n"/>
-      <c r="E195" s="38" t="n"/>
+      <c r="E195" s="41" t="n"/>
       <c r="F195" s="16" t="n"/>
-      <c r="G195" s="36">
+      <c r="G195" s="39">
         <f>IF(OR(E195="",F195=""),"",ROUND(E195*F195,2))</f>
         <v/>
       </c>
@@ -4794,9 +4850,9 @@
       <c r="B196" s="12" t="n"/>
       <c r="C196" s="12" t="n"/>
       <c r="D196" s="12" t="n"/>
-      <c r="E196" s="38" t="n"/>
+      <c r="E196" s="41" t="n"/>
       <c r="F196" s="16" t="n"/>
-      <c r="G196" s="36">
+      <c r="G196" s="39">
         <f>IF(OR(E196="",F196=""),"",ROUND(E196*F196,2))</f>
         <v/>
       </c>
@@ -4808,9 +4864,9 @@
       <c r="B197" s="12" t="n"/>
       <c r="C197" s="12" t="n"/>
       <c r="D197" s="12" t="n"/>
-      <c r="E197" s="38" t="n"/>
+      <c r="E197" s="41" t="n"/>
       <c r="F197" s="16" t="n"/>
-      <c r="G197" s="36">
+      <c r="G197" s="39">
         <f>IF(OR(E197="",F197=""),"",ROUND(E197*F197,2))</f>
         <v/>
       </c>
@@ -4822,9 +4878,9 @@
       <c r="B198" s="12" t="n"/>
       <c r="C198" s="12" t="n"/>
       <c r="D198" s="12" t="n"/>
-      <c r="E198" s="38" t="n"/>
+      <c r="E198" s="41" t="n"/>
       <c r="F198" s="16" t="n"/>
-      <c r="G198" s="36">
+      <c r="G198" s="39">
         <f>IF(OR(E198="",F198=""),"",ROUND(E198*F198,2))</f>
         <v/>
       </c>
@@ -4836,9 +4892,9 @@
       <c r="B199" s="12" t="n"/>
       <c r="C199" s="12" t="n"/>
       <c r="D199" s="12" t="n"/>
-      <c r="E199" s="38" t="n"/>
+      <c r="E199" s="41" t="n"/>
       <c r="F199" s="16" t="n"/>
-      <c r="G199" s="36">
+      <c r="G199" s="39">
         <f>IF(OR(E199="",F199=""),"",ROUND(E199*F199,2))</f>
         <v/>
       </c>
@@ -4850,9 +4906,9 @@
       <c r="B200" s="12" t="n"/>
       <c r="C200" s="12" t="n"/>
       <c r="D200" s="12" t="n"/>
-      <c r="E200" s="38" t="n"/>
+      <c r="E200" s="41" t="n"/>
       <c r="F200" s="16" t="n"/>
-      <c r="G200" s="36">
+      <c r="G200" s="39">
         <f>IF(OR(E200="",F200=""),"",ROUND(E200*F200,2))</f>
         <v/>
       </c>
@@ -4864,9 +4920,9 @@
       <c r="B201" s="12" t="n"/>
       <c r="C201" s="12" t="n"/>
       <c r="D201" s="12" t="n"/>
-      <c r="E201" s="38" t="n"/>
+      <c r="E201" s="41" t="n"/>
       <c r="F201" s="16" t="n"/>
-      <c r="G201" s="36">
+      <c r="G201" s="39">
         <f>IF(OR(E201="",F201=""),"",ROUND(E201*F201,2))</f>
         <v/>
       </c>
@@ -4878,9 +4934,9 @@
       <c r="B202" s="12" t="n"/>
       <c r="C202" s="12" t="n"/>
       <c r="D202" s="12" t="n"/>
-      <c r="E202" s="38" t="n"/>
+      <c r="E202" s="41" t="n"/>
       <c r="F202" s="16" t="n"/>
-      <c r="G202" s="36">
+      <c r="G202" s="39">
         <f>IF(OR(E202="",F202=""),"",ROUND(E202*F202,2))</f>
         <v/>
       </c>
@@ -4892,9 +4948,9 @@
       <c r="B203" s="12" t="n"/>
       <c r="C203" s="12" t="n"/>
       <c r="D203" s="12" t="n"/>
-      <c r="E203" s="38" t="n"/>
+      <c r="E203" s="41" t="n"/>
       <c r="F203" s="16" t="n"/>
-      <c r="G203" s="36">
+      <c r="G203" s="39">
         <f>IF(OR(E203="",F203=""),"",ROUND(E203*F203,2))</f>
         <v/>
       </c>
@@ -4906,9 +4962,9 @@
       <c r="B204" s="12" t="n"/>
       <c r="C204" s="12" t="n"/>
       <c r="D204" s="12" t="n"/>
-      <c r="E204" s="38" t="n"/>
+      <c r="E204" s="41" t="n"/>
       <c r="F204" s="16" t="n"/>
-      <c r="G204" s="36">
+      <c r="G204" s="39">
         <f>IF(OR(E204="",F204=""),"",ROUND(E204*F204,2))</f>
         <v/>
       </c>
@@ -4920,9 +4976,9 @@
       <c r="B205" s="12" t="n"/>
       <c r="C205" s="12" t="n"/>
       <c r="D205" s="12" t="n"/>
-      <c r="E205" s="38" t="n"/>
+      <c r="E205" s="41" t="n"/>
       <c r="F205" s="16" t="n"/>
-      <c r="G205" s="36">
+      <c r="G205" s="39">
         <f>IF(OR(E205="",F205=""),"",ROUND(E205*F205,2))</f>
         <v/>
       </c>
@@ -4934,9 +4990,9 @@
       <c r="B206" s="12" t="n"/>
       <c r="C206" s="12" t="n"/>
       <c r="D206" s="12" t="n"/>
-      <c r="E206" s="38" t="n"/>
+      <c r="E206" s="41" t="n"/>
       <c r="F206" s="16" t="n"/>
-      <c r="G206" s="36">
+      <c r="G206" s="39">
         <f>IF(OR(E206="",F206=""),"",ROUND(E206*F206,2))</f>
         <v/>
       </c>
@@ -4948,9 +5004,9 @@
       <c r="B207" s="12" t="n"/>
       <c r="C207" s="12" t="n"/>
       <c r="D207" s="12" t="n"/>
-      <c r="E207" s="38" t="n"/>
+      <c r="E207" s="41" t="n"/>
       <c r="F207" s="16" t="n"/>
-      <c r="G207" s="36">
+      <c r="G207" s="39">
         <f>IF(OR(E207="",F207=""),"",ROUND(E207*F207,2))</f>
         <v/>
       </c>
@@ -4962,9 +5018,9 @@
       <c r="B208" s="12" t="n"/>
       <c r="C208" s="12" t="n"/>
       <c r="D208" s="12" t="n"/>
-      <c r="E208" s="38" t="n"/>
+      <c r="E208" s="41" t="n"/>
       <c r="F208" s="16" t="n"/>
-      <c r="G208" s="36">
+      <c r="G208" s="39">
         <f>IF(OR(E208="",F208=""),"",ROUND(E208*F208,2))</f>
         <v/>
       </c>
@@ -4976,9 +5032,9 @@
       <c r="B209" s="12" t="n"/>
       <c r="C209" s="12" t="n"/>
       <c r="D209" s="12" t="n"/>
-      <c r="E209" s="38" t="n"/>
+      <c r="E209" s="41" t="n"/>
       <c r="F209" s="16" t="n"/>
-      <c r="G209" s="36">
+      <c r="G209" s="39">
         <f>IF(OR(E209="",F209=""),"",ROUND(E209*F209,2))</f>
         <v/>
       </c>
@@ -4990,9 +5046,9 @@
       <c r="B210" s="12" t="n"/>
       <c r="C210" s="12" t="n"/>
       <c r="D210" s="12" t="n"/>
-      <c r="E210" s="38" t="n"/>
+      <c r="E210" s="41" t="n"/>
       <c r="F210" s="16" t="n"/>
-      <c r="G210" s="36">
+      <c r="G210" s="39">
         <f>IF(OR(E210="",F210=""),"",ROUND(E210*F210,2))</f>
         <v/>
       </c>
@@ -5004,9 +5060,9 @@
       <c r="B211" s="12" t="n"/>
       <c r="C211" s="12" t="n"/>
       <c r="D211" s="12" t="n"/>
-      <c r="E211" s="38" t="n"/>
+      <c r="E211" s="41" t="n"/>
       <c r="F211" s="16" t="n"/>
-      <c r="G211" s="36">
+      <c r="G211" s="39">
         <f>IF(OR(E211="",F211=""),"",ROUND(E211*F211,2))</f>
         <v/>
       </c>
@@ -5018,9 +5074,9 @@
       <c r="B212" s="12" t="n"/>
       <c r="C212" s="12" t="n"/>
       <c r="D212" s="12" t="n"/>
-      <c r="E212" s="38" t="n"/>
+      <c r="E212" s="41" t="n"/>
       <c r="F212" s="16" t="n"/>
-      <c r="G212" s="36">
+      <c r="G212" s="39">
         <f>IF(OR(E212="",F212=""),"",ROUND(E212*F212,2))</f>
         <v/>
       </c>
@@ -5032,9 +5088,9 @@
       <c r="B213" s="12" t="n"/>
       <c r="C213" s="12" t="n"/>
       <c r="D213" s="12" t="n"/>
-      <c r="E213" s="38" t="n"/>
+      <c r="E213" s="41" t="n"/>
       <c r="F213" s="16" t="n"/>
-      <c r="G213" s="36">
+      <c r="G213" s="39">
         <f>IF(OR(E213="",F213=""),"",ROUND(E213*F213,2))</f>
         <v/>
       </c>
@@ -5046,9 +5102,9 @@
       <c r="B214" s="12" t="n"/>
       <c r="C214" s="12" t="n"/>
       <c r="D214" s="12" t="n"/>
-      <c r="E214" s="38" t="n"/>
+      <c r="E214" s="41" t="n"/>
       <c r="F214" s="16" t="n"/>
-      <c r="G214" s="36">
+      <c r="G214" s="39">
         <f>IF(OR(E214="",F214=""),"",ROUND(E214*F214,2))</f>
         <v/>
       </c>
@@ -5060,9 +5116,9 @@
       <c r="B215" s="12" t="n"/>
       <c r="C215" s="12" t="n"/>
       <c r="D215" s="12" t="n"/>
-      <c r="E215" s="38" t="n"/>
+      <c r="E215" s="41" t="n"/>
       <c r="F215" s="16" t="n"/>
-      <c r="G215" s="36">
+      <c r="G215" s="39">
         <f>IF(OR(E215="",F215=""),"",ROUND(E215*F215,2))</f>
         <v/>
       </c>
@@ -5074,9 +5130,9 @@
       <c r="B216" s="12" t="n"/>
       <c r="C216" s="12" t="n"/>
       <c r="D216" s="12" t="n"/>
-      <c r="E216" s="38" t="n"/>
+      <c r="E216" s="41" t="n"/>
       <c r="F216" s="16" t="n"/>
-      <c r="G216" s="36">
+      <c r="G216" s="39">
         <f>IF(OR(E216="",F216=""),"",ROUND(E216*F216,2))</f>
         <v/>
       </c>
@@ -5088,9 +5144,9 @@
       <c r="B217" s="12" t="n"/>
       <c r="C217" s="12" t="n"/>
       <c r="D217" s="12" t="n"/>
-      <c r="E217" s="38" t="n"/>
+      <c r="E217" s="41" t="n"/>
       <c r="F217" s="16" t="n"/>
-      <c r="G217" s="36">
+      <c r="G217" s="39">
         <f>IF(OR(E217="",F217=""),"",ROUND(E217*F217,2))</f>
         <v/>
       </c>
@@ -5102,9 +5158,9 @@
       <c r="B218" s="12" t="n"/>
       <c r="C218" s="12" t="n"/>
       <c r="D218" s="12" t="n"/>
-      <c r="E218" s="38" t="n"/>
+      <c r="E218" s="41" t="n"/>
       <c r="F218" s="16" t="n"/>
-      <c r="G218" s="36">
+      <c r="G218" s="39">
         <f>IF(OR(E218="",F218=""),"",ROUND(E218*F218,2))</f>
         <v/>
       </c>
@@ -5116,9 +5172,9 @@
       <c r="B219" s="12" t="n"/>
       <c r="C219" s="12" t="n"/>
       <c r="D219" s="12" t="n"/>
-      <c r="E219" s="38" t="n"/>
+      <c r="E219" s="41" t="n"/>
       <c r="F219" s="16" t="n"/>
-      <c r="G219" s="36">
+      <c r="G219" s="39">
         <f>IF(OR(E219="",F219=""),"",ROUND(E219*F219,2))</f>
         <v/>
       </c>
@@ -5130,9 +5186,9 @@
       <c r="B220" s="12" t="n"/>
       <c r="C220" s="12" t="n"/>
       <c r="D220" s="12" t="n"/>
-      <c r="E220" s="38" t="n"/>
+      <c r="E220" s="41" t="n"/>
       <c r="F220" s="16" t="n"/>
-      <c r="G220" s="36">
+      <c r="G220" s="39">
         <f>IF(OR(E220="",F220=""),"",ROUND(E220*F220,2))</f>
         <v/>
       </c>
@@ -5144,9 +5200,9 @@
       <c r="B221" s="12" t="n"/>
       <c r="C221" s="12" t="n"/>
       <c r="D221" s="12" t="n"/>
-      <c r="E221" s="38" t="n"/>
+      <c r="E221" s="41" t="n"/>
       <c r="F221" s="16" t="n"/>
-      <c r="G221" s="36">
+      <c r="G221" s="39">
         <f>IF(OR(E221="",F221=""),"",ROUND(E221*F221,2))</f>
         <v/>
       </c>
@@ -5158,9 +5214,9 @@
       <c r="B222" s="12" t="n"/>
       <c r="C222" s="12" t="n"/>
       <c r="D222" s="12" t="n"/>
-      <c r="E222" s="38" t="n"/>
+      <c r="E222" s="41" t="n"/>
       <c r="F222" s="16" t="n"/>
-      <c r="G222" s="36">
+      <c r="G222" s="39">
         <f>IF(OR(E222="",F222=""),"",ROUND(E222*F222,2))</f>
         <v/>
       </c>
@@ -5172,9 +5228,9 @@
       <c r="B223" s="12" t="n"/>
       <c r="C223" s="12" t="n"/>
       <c r="D223" s="12" t="n"/>
-      <c r="E223" s="38" t="n"/>
+      <c r="E223" s="41" t="n"/>
       <c r="F223" s="16" t="n"/>
-      <c r="G223" s="36">
+      <c r="G223" s="39">
         <f>IF(OR(E223="",F223=""),"",ROUND(E223*F223,2))</f>
         <v/>
       </c>
@@ -5186,9 +5242,9 @@
       <c r="B224" s="12" t="n"/>
       <c r="C224" s="12" t="n"/>
       <c r="D224" s="12" t="n"/>
-      <c r="E224" s="38" t="n"/>
+      <c r="E224" s="41" t="n"/>
       <c r="F224" s="16" t="n"/>
-      <c r="G224" s="36">
+      <c r="G224" s="39">
         <f>IF(OR(E224="",F224=""),"",ROUND(E224*F224,2))</f>
         <v/>
       </c>
@@ -5200,9 +5256,9 @@
       <c r="B225" s="12" t="n"/>
       <c r="C225" s="12" t="n"/>
       <c r="D225" s="12" t="n"/>
-      <c r="E225" s="38" t="n"/>
+      <c r="E225" s="41" t="n"/>
       <c r="F225" s="16" t="n"/>
-      <c r="G225" s="36">
+      <c r="G225" s="39">
         <f>IF(OR(E225="",F225=""),"",ROUND(E225*F225,2))</f>
         <v/>
       </c>
@@ -5214,9 +5270,9 @@
       <c r="B226" s="12" t="n"/>
       <c r="C226" s="12" t="n"/>
       <c r="D226" s="12" t="n"/>
-      <c r="E226" s="38" t="n"/>
+      <c r="E226" s="41" t="n"/>
       <c r="F226" s="16" t="n"/>
-      <c r="G226" s="36">
+      <c r="G226" s="39">
         <f>IF(OR(E226="",F226=""),"",ROUND(E226*F226,2))</f>
         <v/>
       </c>
@@ -5228,9 +5284,9 @@
       <c r="B227" s="12" t="n"/>
       <c r="C227" s="12" t="n"/>
       <c r="D227" s="12" t="n"/>
-      <c r="E227" s="38" t="n"/>
+      <c r="E227" s="41" t="n"/>
       <c r="F227" s="16" t="n"/>
-      <c r="G227" s="36">
+      <c r="G227" s="39">
         <f>IF(OR(E227="",F227=""),"",ROUND(E227*F227,2))</f>
         <v/>
       </c>
@@ -5242,9 +5298,9 @@
       <c r="B228" s="12" t="n"/>
       <c r="C228" s="12" t="n"/>
       <c r="D228" s="12" t="n"/>
-      <c r="E228" s="38" t="n"/>
+      <c r="E228" s="41" t="n"/>
       <c r="F228" s="16" t="n"/>
-      <c r="G228" s="36">
+      <c r="G228" s="39">
         <f>IF(OR(E228="",F228=""),"",ROUND(E228*F228,2))</f>
         <v/>
       </c>
@@ -5256,9 +5312,9 @@
       <c r="B229" s="12" t="n"/>
       <c r="C229" s="12" t="n"/>
       <c r="D229" s="12" t="n"/>
-      <c r="E229" s="38" t="n"/>
+      <c r="E229" s="41" t="n"/>
       <c r="F229" s="16" t="n"/>
-      <c r="G229" s="36">
+      <c r="G229" s="39">
         <f>IF(OR(E229="",F229=""),"",ROUND(E229*F229,2))</f>
         <v/>
       </c>
@@ -5270,9 +5326,9 @@
       <c r="B230" s="12" t="n"/>
       <c r="C230" s="12" t="n"/>
       <c r="D230" s="12" t="n"/>
-      <c r="E230" s="38" t="n"/>
+      <c r="E230" s="41" t="n"/>
       <c r="F230" s="16" t="n"/>
-      <c r="G230" s="36">
+      <c r="G230" s="39">
         <f>IF(OR(E230="",F230=""),"",ROUND(E230*F230,2))</f>
         <v/>
       </c>
@@ -5284,9 +5340,9 @@
       <c r="B231" s="12" t="n"/>
       <c r="C231" s="12" t="n"/>
       <c r="D231" s="12" t="n"/>
-      <c r="E231" s="38" t="n"/>
+      <c r="E231" s="41" t="n"/>
       <c r="F231" s="16" t="n"/>
-      <c r="G231" s="36">
+      <c r="G231" s="39">
         <f>IF(OR(E231="",F231=""),"",ROUND(E231*F231,2))</f>
         <v/>
       </c>
@@ -5298,9 +5354,9 @@
       <c r="B232" s="12" t="n"/>
       <c r="C232" s="12" t="n"/>
       <c r="D232" s="12" t="n"/>
-      <c r="E232" s="38" t="n"/>
+      <c r="E232" s="41" t="n"/>
       <c r="F232" s="16" t="n"/>
-      <c r="G232" s="36">
+      <c r="G232" s="39">
         <f>IF(OR(E232="",F232=""),"",ROUND(E232*F232,2))</f>
         <v/>
       </c>
@@ -5312,9 +5368,9 @@
       <c r="B233" s="12" t="n"/>
       <c r="C233" s="12" t="n"/>
       <c r="D233" s="12" t="n"/>
-      <c r="E233" s="38" t="n"/>
+      <c r="E233" s="41" t="n"/>
       <c r="F233" s="16" t="n"/>
-      <c r="G233" s="36">
+      <c r="G233" s="39">
         <f>IF(OR(E233="",F233=""),"",ROUND(E233*F233,2))</f>
         <v/>
       </c>
@@ -5326,9 +5382,9 @@
       <c r="B234" s="12" t="n"/>
       <c r="C234" s="12" t="n"/>
       <c r="D234" s="12" t="n"/>
-      <c r="E234" s="38" t="n"/>
+      <c r="E234" s="41" t="n"/>
       <c r="F234" s="16" t="n"/>
-      <c r="G234" s="36">
+      <c r="G234" s="39">
         <f>IF(OR(E234="",F234=""),"",ROUND(E234*F234,2))</f>
         <v/>
       </c>
@@ -5340,9 +5396,9 @@
       <c r="B235" s="12" t="n"/>
       <c r="C235" s="12" t="n"/>
       <c r="D235" s="12" t="n"/>
-      <c r="E235" s="38" t="n"/>
+      <c r="E235" s="41" t="n"/>
       <c r="F235" s="16" t="n"/>
-      <c r="G235" s="36">
+      <c r="G235" s="39">
         <f>IF(OR(E235="",F235=""),"",ROUND(E235*F235,2))</f>
         <v/>
       </c>
@@ -5354,9 +5410,9 @@
       <c r="B236" s="12" t="n"/>
       <c r="C236" s="12" t="n"/>
       <c r="D236" s="12" t="n"/>
-      <c r="E236" s="38" t="n"/>
+      <c r="E236" s="41" t="n"/>
       <c r="F236" s="16" t="n"/>
-      <c r="G236" s="36">
+      <c r="G236" s="39">
         <f>IF(OR(E236="",F236=""),"",ROUND(E236*F236,2))</f>
         <v/>
       </c>
@@ -5368,9 +5424,9 @@
       <c r="B237" s="12" t="n"/>
       <c r="C237" s="12" t="n"/>
       <c r="D237" s="12" t="n"/>
-      <c r="E237" s="38" t="n"/>
+      <c r="E237" s="41" t="n"/>
       <c r="F237" s="16" t="n"/>
-      <c r="G237" s="36">
+      <c r="G237" s="39">
         <f>IF(OR(E237="",F237=""),"",ROUND(E237*F237,2))</f>
         <v/>
       </c>
@@ -5382,9 +5438,9 @@
       <c r="B238" s="12" t="n"/>
       <c r="C238" s="12" t="n"/>
       <c r="D238" s="12" t="n"/>
-      <c r="E238" s="38" t="n"/>
+      <c r="E238" s="41" t="n"/>
       <c r="F238" s="16" t="n"/>
-      <c r="G238" s="36">
+      <c r="G238" s="39">
         <f>IF(OR(E238="",F238=""),"",ROUND(E238*F238,2))</f>
         <v/>
       </c>
@@ -5396,9 +5452,9 @@
       <c r="B239" s="12" t="n"/>
       <c r="C239" s="12" t="n"/>
       <c r="D239" s="12" t="n"/>
-      <c r="E239" s="38" t="n"/>
+      <c r="E239" s="41" t="n"/>
       <c r="F239" s="16" t="n"/>
-      <c r="G239" s="36">
+      <c r="G239" s="39">
         <f>IF(OR(E239="",F239=""),"",ROUND(E239*F239,2))</f>
         <v/>
       </c>
@@ -5410,9 +5466,9 @@
       <c r="B240" s="12" t="n"/>
       <c r="C240" s="12" t="n"/>
       <c r="D240" s="12" t="n"/>
-      <c r="E240" s="38" t="n"/>
+      <c r="E240" s="41" t="n"/>
       <c r="F240" s="16" t="n"/>
-      <c r="G240" s="36">
+      <c r="G240" s="39">
         <f>IF(OR(E240="",F240=""),"",ROUND(E240*F240,2))</f>
         <v/>
       </c>
@@ -5424,9 +5480,9 @@
       <c r="B241" s="12" t="n"/>
       <c r="C241" s="12" t="n"/>
       <c r="D241" s="12" t="n"/>
-      <c r="E241" s="38" t="n"/>
+      <c r="E241" s="41" t="n"/>
       <c r="F241" s="16" t="n"/>
-      <c r="G241" s="36">
+      <c r="G241" s="39">
         <f>IF(OR(E241="",F241=""),"",ROUND(E241*F241,2))</f>
         <v/>
       </c>
@@ -5438,9 +5494,9 @@
       <c r="B242" s="12" t="n"/>
       <c r="C242" s="12" t="n"/>
       <c r="D242" s="12" t="n"/>
-      <c r="E242" s="38" t="n"/>
+      <c r="E242" s="41" t="n"/>
       <c r="F242" s="16" t="n"/>
-      <c r="G242" s="36">
+      <c r="G242" s="39">
         <f>IF(OR(E242="",F242=""),"",ROUND(E242*F242,2))</f>
         <v/>
       </c>
@@ -5452,9 +5508,9 @@
       <c r="B243" s="12" t="n"/>
       <c r="C243" s="12" t="n"/>
       <c r="D243" s="12" t="n"/>
-      <c r="E243" s="38" t="n"/>
+      <c r="E243" s="41" t="n"/>
       <c r="F243" s="16" t="n"/>
-      <c r="G243" s="36">
+      <c r="G243" s="39">
         <f>IF(OR(E243="",F243=""),"",ROUND(E243*F243,2))</f>
         <v/>
       </c>
@@ -5466,9 +5522,9 @@
       <c r="B244" s="12" t="n"/>
       <c r="C244" s="12" t="n"/>
       <c r="D244" s="12" t="n"/>
-      <c r="E244" s="38" t="n"/>
+      <c r="E244" s="41" t="n"/>
       <c r="F244" s="16" t="n"/>
-      <c r="G244" s="36">
+      <c r="G244" s="39">
         <f>IF(OR(E244="",F244=""),"",ROUND(E244*F244,2))</f>
         <v/>
       </c>
@@ -5480,9 +5536,9 @@
       <c r="B245" s="12" t="n"/>
       <c r="C245" s="12" t="n"/>
       <c r="D245" s="12" t="n"/>
-      <c r="E245" s="38" t="n"/>
+      <c r="E245" s="41" t="n"/>
       <c r="F245" s="16" t="n"/>
-      <c r="G245" s="36">
+      <c r="G245" s="39">
         <f>IF(OR(E245="",F245=""),"",ROUND(E245*F245,2))</f>
         <v/>
       </c>
@@ -5494,9 +5550,9 @@
       <c r="B246" s="12" t="n"/>
       <c r="C246" s="12" t="n"/>
       <c r="D246" s="12" t="n"/>
-      <c r="E246" s="38" t="n"/>
+      <c r="E246" s="41" t="n"/>
       <c r="F246" s="16" t="n"/>
-      <c r="G246" s="36">
+      <c r="G246" s="39">
         <f>IF(OR(E246="",F246=""),"",ROUND(E246*F246,2))</f>
         <v/>
       </c>
@@ -5508,9 +5564,9 @@
       <c r="B247" s="12" t="n"/>
       <c r="C247" s="12" t="n"/>
       <c r="D247" s="12" t="n"/>
-      <c r="E247" s="38" t="n"/>
+      <c r="E247" s="41" t="n"/>
       <c r="F247" s="16" t="n"/>
-      <c r="G247" s="36">
+      <c r="G247" s="39">
         <f>IF(OR(E247="",F247=""),"",ROUND(E247*F247,2))</f>
         <v/>
       </c>
@@ -5522,9 +5578,9 @@
       <c r="B248" s="12" t="n"/>
       <c r="C248" s="12" t="n"/>
       <c r="D248" s="12" t="n"/>
-      <c r="E248" s="38" t="n"/>
+      <c r="E248" s="41" t="n"/>
       <c r="F248" s="16" t="n"/>
-      <c r="G248" s="36">
+      <c r="G248" s="39">
         <f>IF(OR(E248="",F248=""),"",ROUND(E248*F248,2))</f>
         <v/>
       </c>
@@ -5536,9 +5592,9 @@
       <c r="B249" s="12" t="n"/>
       <c r="C249" s="12" t="n"/>
       <c r="D249" s="12" t="n"/>
-      <c r="E249" s="38" t="n"/>
+      <c r="E249" s="41" t="n"/>
       <c r="F249" s="16" t="n"/>
-      <c r="G249" s="36">
+      <c r="G249" s="39">
         <f>IF(OR(E249="",F249=""),"",ROUND(E249*F249,2))</f>
         <v/>
       </c>
@@ -5550,9 +5606,9 @@
       <c r="B250" s="12" t="n"/>
       <c r="C250" s="12" t="n"/>
       <c r="D250" s="12" t="n"/>
-      <c r="E250" s="38" t="n"/>
+      <c r="E250" s="41" t="n"/>
       <c r="F250" s="16" t="n"/>
-      <c r="G250" s="36">
+      <c r="G250" s="39">
         <f>IF(OR(E250="",F250=""),"",ROUND(E250*F250,2))</f>
         <v/>
       </c>
@@ -5564,9 +5620,9 @@
       <c r="B251" s="12" t="n"/>
       <c r="C251" s="12" t="n"/>
       <c r="D251" s="12" t="n"/>
-      <c r="E251" s="38" t="n"/>
+      <c r="E251" s="41" t="n"/>
       <c r="F251" s="16" t="n"/>
-      <c r="G251" s="36">
+      <c r="G251" s="39">
         <f>IF(OR(E251="",F251=""),"",ROUND(E251*F251,2))</f>
         <v/>
       </c>
@@ -5578,9 +5634,9 @@
       <c r="B252" s="12" t="n"/>
       <c r="C252" s="12" t="n"/>
       <c r="D252" s="12" t="n"/>
-      <c r="E252" s="38" t="n"/>
+      <c r="E252" s="41" t="n"/>
       <c r="F252" s="16" t="n"/>
-      <c r="G252" s="36">
+      <c r="G252" s="39">
         <f>IF(OR(E252="",F252=""),"",ROUND(E252*F252,2))</f>
         <v/>
       </c>
@@ -5592,9 +5648,9 @@
       <c r="B253" s="12" t="n"/>
       <c r="C253" s="12" t="n"/>
       <c r="D253" s="12" t="n"/>
-      <c r="E253" s="38" t="n"/>
+      <c r="E253" s="41" t="n"/>
       <c r="F253" s="16" t="n"/>
-      <c r="G253" s="36">
+      <c r="G253" s="39">
         <f>IF(OR(E253="",F253=""),"",ROUND(E253*F253,2))</f>
         <v/>
       </c>
@@ -5606,9 +5662,9 @@
       <c r="B254" s="12" t="n"/>
       <c r="C254" s="12" t="n"/>
       <c r="D254" s="12" t="n"/>
-      <c r="E254" s="38" t="n"/>
+      <c r="E254" s="41" t="n"/>
       <c r="F254" s="16" t="n"/>
-      <c r="G254" s="36">
+      <c r="G254" s="39">
         <f>IF(OR(E254="",F254=""),"",ROUND(E254*F254,2))</f>
         <v/>
       </c>
@@ -5620,9 +5676,9 @@
       <c r="B255" s="12" t="n"/>
       <c r="C255" s="12" t="n"/>
       <c r="D255" s="12" t="n"/>
-      <c r="E255" s="38" t="n"/>
+      <c r="E255" s="41" t="n"/>
       <c r="F255" s="16" t="n"/>
-      <c r="G255" s="36">
+      <c r="G255" s="39">
         <f>IF(OR(E255="",F255=""),"",ROUND(E255*F255,2))</f>
         <v/>
       </c>
@@ -5634,9 +5690,9 @@
       <c r="B256" s="12" t="n"/>
       <c r="C256" s="12" t="n"/>
       <c r="D256" s="12" t="n"/>
-      <c r="E256" s="38" t="n"/>
+      <c r="E256" s="41" t="n"/>
       <c r="F256" s="16" t="n"/>
-      <c r="G256" s="36">
+      <c r="G256" s="39">
         <f>IF(OR(E256="",F256=""),"",ROUND(E256*F256,2))</f>
         <v/>
       </c>
@@ -5648,9 +5704,9 @@
       <c r="B257" s="12" t="n"/>
       <c r="C257" s="12" t="n"/>
       <c r="D257" s="12" t="n"/>
-      <c r="E257" s="38" t="n"/>
+      <c r="E257" s="41" t="n"/>
       <c r="F257" s="16" t="n"/>
-      <c r="G257" s="36">
+      <c r="G257" s="39">
         <f>IF(OR(E257="",F257=""),"",ROUND(E257*F257,2))</f>
         <v/>
       </c>
@@ -5662,9 +5718,9 @@
       <c r="B258" s="12" t="n"/>
       <c r="C258" s="12" t="n"/>
       <c r="D258" s="12" t="n"/>
-      <c r="E258" s="38" t="n"/>
+      <c r="E258" s="41" t="n"/>
       <c r="F258" s="16" t="n"/>
-      <c r="G258" s="36">
+      <c r="G258" s="39">
         <f>IF(OR(E258="",F258=""),"",ROUND(E258*F258,2))</f>
         <v/>
       </c>
@@ -5676,9 +5732,9 @@
       <c r="B259" s="12" t="n"/>
       <c r="C259" s="12" t="n"/>
       <c r="D259" s="12" t="n"/>
-      <c r="E259" s="38" t="n"/>
+      <c r="E259" s="41" t="n"/>
       <c r="F259" s="16" t="n"/>
-      <c r="G259" s="36">
+      <c r="G259" s="39">
         <f>IF(OR(E259="",F259=""),"",ROUND(E259*F259,2))</f>
         <v/>
       </c>
@@ -5690,9 +5746,9 @@
       <c r="B260" s="12" t="n"/>
       <c r="C260" s="12" t="n"/>
       <c r="D260" s="12" t="n"/>
-      <c r="E260" s="38" t="n"/>
+      <c r="E260" s="41" t="n"/>
       <c r="F260" s="16" t="n"/>
-      <c r="G260" s="36">
+      <c r="G260" s="39">
         <f>IF(OR(E260="",F260=""),"",ROUND(E260*F260,2))</f>
         <v/>
       </c>
@@ -5704,9 +5760,9 @@
       <c r="B261" s="12" t="n"/>
       <c r="C261" s="12" t="n"/>
       <c r="D261" s="12" t="n"/>
-      <c r="E261" s="38" t="n"/>
+      <c r="E261" s="41" t="n"/>
       <c r="F261" s="16" t="n"/>
-      <c r="G261" s="36">
+      <c r="G261" s="39">
         <f>IF(OR(E261="",F261=""),"",ROUND(E261*F261,2))</f>
         <v/>
       </c>
@@ -5718,9 +5774,9 @@
       <c r="B262" s="12" t="n"/>
       <c r="C262" s="12" t="n"/>
       <c r="D262" s="12" t="n"/>
-      <c r="E262" s="38" t="n"/>
+      <c r="E262" s="41" t="n"/>
       <c r="F262" s="16" t="n"/>
-      <c r="G262" s="36">
+      <c r="G262" s="39">
         <f>IF(OR(E262="",F262=""),"",ROUND(E262*F262,2))</f>
         <v/>
       </c>
@@ -5732,9 +5788,9 @@
       <c r="B263" s="12" t="n"/>
       <c r="C263" s="12" t="n"/>
       <c r="D263" s="12" t="n"/>
-      <c r="E263" s="38" t="n"/>
+      <c r="E263" s="41" t="n"/>
       <c r="F263" s="16" t="n"/>
-      <c r="G263" s="36">
+      <c r="G263" s="39">
         <f>IF(OR(E263="",F263=""),"",ROUND(E263*F263,2))</f>
         <v/>
       </c>
@@ -5746,9 +5802,9 @@
       <c r="B264" s="12" t="n"/>
       <c r="C264" s="12" t="n"/>
       <c r="D264" s="12" t="n"/>
-      <c r="E264" s="38" t="n"/>
+      <c r="E264" s="41" t="n"/>
       <c r="F264" s="16" t="n"/>
-      <c r="G264" s="36">
+      <c r="G264" s="39">
         <f>IF(OR(E264="",F264=""),"",ROUND(E264*F264,2))</f>
         <v/>
       </c>
@@ -5760,9 +5816,9 @@
       <c r="B265" s="12" t="n"/>
       <c r="C265" s="12" t="n"/>
       <c r="D265" s="12" t="n"/>
-      <c r="E265" s="38" t="n"/>
+      <c r="E265" s="41" t="n"/>
       <c r="F265" s="16" t="n"/>
-      <c r="G265" s="36">
+      <c r="G265" s="39">
         <f>IF(OR(E265="",F265=""),"",ROUND(E265*F265,2))</f>
         <v/>
       </c>
@@ -5774,9 +5830,9 @@
       <c r="B266" s="12" t="n"/>
       <c r="C266" s="12" t="n"/>
       <c r="D266" s="12" t="n"/>
-      <c r="E266" s="38" t="n"/>
+      <c r="E266" s="41" t="n"/>
       <c r="F266" s="16" t="n"/>
-      <c r="G266" s="36">
+      <c r="G266" s="39">
         <f>IF(OR(E266="",F266=""),"",ROUND(E266*F266,2))</f>
         <v/>
       </c>
@@ -5788,9 +5844,9 @@
       <c r="B267" s="12" t="n"/>
       <c r="C267" s="12" t="n"/>
       <c r="D267" s="12" t="n"/>
-      <c r="E267" s="38" t="n"/>
+      <c r="E267" s="41" t="n"/>
       <c r="F267" s="16" t="n"/>
-      <c r="G267" s="36">
+      <c r="G267" s="39">
         <f>IF(OR(E267="",F267=""),"",ROUND(E267*F267,2))</f>
         <v/>
       </c>
@@ -5802,9 +5858,9 @@
       <c r="B268" s="12" t="n"/>
       <c r="C268" s="12" t="n"/>
       <c r="D268" s="12" t="n"/>
-      <c r="E268" s="38" t="n"/>
+      <c r="E268" s="41" t="n"/>
       <c r="F268" s="16" t="n"/>
-      <c r="G268" s="36">
+      <c r="G268" s="39">
         <f>IF(OR(E268="",F268=""),"",ROUND(E268*F268,2))</f>
         <v/>
       </c>
@@ -5816,9 +5872,9 @@
       <c r="B269" s="12" t="n"/>
       <c r="C269" s="12" t="n"/>
       <c r="D269" s="12" t="n"/>
-      <c r="E269" s="38" t="n"/>
+      <c r="E269" s="41" t="n"/>
       <c r="F269" s="16" t="n"/>
-      <c r="G269" s="36">
+      <c r="G269" s="39">
         <f>IF(OR(E269="",F269=""),"",ROUND(E269*F269,2))</f>
         <v/>
       </c>
@@ -5830,9 +5886,9 @@
       <c r="B270" s="12" t="n"/>
       <c r="C270" s="12" t="n"/>
       <c r="D270" s="12" t="n"/>
-      <c r="E270" s="38" t="n"/>
+      <c r="E270" s="41" t="n"/>
       <c r="F270" s="16" t="n"/>
-      <c r="G270" s="36">
+      <c r="G270" s="39">
         <f>IF(OR(E270="",F270=""),"",ROUND(E270*F270,2))</f>
         <v/>
       </c>
@@ -5844,9 +5900,9 @@
       <c r="B271" s="12" t="n"/>
       <c r="C271" s="12" t="n"/>
       <c r="D271" s="12" t="n"/>
-      <c r="E271" s="38" t="n"/>
+      <c r="E271" s="41" t="n"/>
       <c r="F271" s="16" t="n"/>
-      <c r="G271" s="36">
+      <c r="G271" s="39">
         <f>IF(OR(E271="",F271=""),"",ROUND(E271*F271,2))</f>
         <v/>
       </c>
@@ -5858,9 +5914,9 @@
       <c r="B272" s="12" t="n"/>
       <c r="C272" s="12" t="n"/>
       <c r="D272" s="12" t="n"/>
-      <c r="E272" s="38" t="n"/>
+      <c r="E272" s="41" t="n"/>
       <c r="F272" s="16" t="n"/>
-      <c r="G272" s="36">
+      <c r="G272" s="39">
         <f>IF(OR(E272="",F272=""),"",ROUND(E272*F272,2))</f>
         <v/>
       </c>
@@ -5872,9 +5928,9 @@
       <c r="B273" s="12" t="n"/>
       <c r="C273" s="12" t="n"/>
       <c r="D273" s="12" t="n"/>
-      <c r="E273" s="38" t="n"/>
+      <c r="E273" s="41" t="n"/>
       <c r="F273" s="16" t="n"/>
-      <c r="G273" s="36">
+      <c r="G273" s="39">
         <f>IF(OR(E273="",F273=""),"",ROUND(E273*F273,2))</f>
         <v/>
       </c>
@@ -5886,9 +5942,9 @@
       <c r="B274" s="12" t="n"/>
       <c r="C274" s="12" t="n"/>
       <c r="D274" s="12" t="n"/>
-      <c r="E274" s="38" t="n"/>
+      <c r="E274" s="41" t="n"/>
       <c r="F274" s="16" t="n"/>
-      <c r="G274" s="36">
+      <c r="G274" s="39">
         <f>IF(OR(E274="",F274=""),"",ROUND(E274*F274,2))</f>
         <v/>
       </c>
@@ -5900,9 +5956,9 @@
       <c r="B275" s="12" t="n"/>
       <c r="C275" s="12" t="n"/>
       <c r="D275" s="12" t="n"/>
-      <c r="E275" s="38" t="n"/>
+      <c r="E275" s="41" t="n"/>
       <c r="F275" s="16" t="n"/>
-      <c r="G275" s="36">
+      <c r="G275" s="39">
         <f>IF(OR(E275="",F275=""),"",ROUND(E275*F275,2))</f>
         <v/>
       </c>
@@ -5914,9 +5970,9 @@
       <c r="B276" s="12" t="n"/>
       <c r="C276" s="12" t="n"/>
       <c r="D276" s="12" t="n"/>
-      <c r="E276" s="38" t="n"/>
+      <c r="E276" s="41" t="n"/>
       <c r="F276" s="16" t="n"/>
-      <c r="G276" s="36">
+      <c r="G276" s="39">
         <f>IF(OR(E276="",F276=""),"",ROUND(E276*F276,2))</f>
         <v/>
       </c>
@@ -5928,9 +5984,9 @@
       <c r="B277" s="12" t="n"/>
       <c r="C277" s="12" t="n"/>
       <c r="D277" s="12" t="n"/>
-      <c r="E277" s="38" t="n"/>
+      <c r="E277" s="41" t="n"/>
       <c r="F277" s="16" t="n"/>
-      <c r="G277" s="36">
+      <c r="G277" s="39">
         <f>IF(OR(E277="",F277=""),"",ROUND(E277*F277,2))</f>
         <v/>
       </c>
@@ -5942,9 +5998,9 @@
       <c r="B278" s="12" t="n"/>
       <c r="C278" s="12" t="n"/>
       <c r="D278" s="12" t="n"/>
-      <c r="E278" s="38" t="n"/>
+      <c r="E278" s="41" t="n"/>
       <c r="F278" s="16" t="n"/>
-      <c r="G278" s="36">
+      <c r="G278" s="39">
         <f>IF(OR(E278="",F278=""),"",ROUND(E278*F278,2))</f>
         <v/>
       </c>
@@ -5956,9 +6012,9 @@
       <c r="B279" s="12" t="n"/>
       <c r="C279" s="12" t="n"/>
       <c r="D279" s="12" t="n"/>
-      <c r="E279" s="38" t="n"/>
+      <c r="E279" s="41" t="n"/>
       <c r="F279" s="16" t="n"/>
-      <c r="G279" s="36">
+      <c r="G279" s="39">
         <f>IF(OR(E279="",F279=""),"",ROUND(E279*F279,2))</f>
         <v/>
       </c>
@@ -5970,9 +6026,9 @@
       <c r="B280" s="12" t="n"/>
       <c r="C280" s="12" t="n"/>
       <c r="D280" s="12" t="n"/>
-      <c r="E280" s="38" t="n"/>
+      <c r="E280" s="41" t="n"/>
       <c r="F280" s="16" t="n"/>
-      <c r="G280" s="36">
+      <c r="G280" s="39">
         <f>IF(OR(E280="",F280=""),"",ROUND(E280*F280,2))</f>
         <v/>
       </c>
@@ -5984,9 +6040,9 @@
       <c r="B281" s="12" t="n"/>
       <c r="C281" s="12" t="n"/>
       <c r="D281" s="12" t="n"/>
-      <c r="E281" s="38" t="n"/>
+      <c r="E281" s="41" t="n"/>
       <c r="F281" s="16" t="n"/>
-      <c r="G281" s="36">
+      <c r="G281" s="39">
         <f>IF(OR(E281="",F281=""),"",ROUND(E281*F281,2))</f>
         <v/>
       </c>
@@ -5998,9 +6054,9 @@
       <c r="B282" s="12" t="n"/>
       <c r="C282" s="12" t="n"/>
       <c r="D282" s="12" t="n"/>
-      <c r="E282" s="38" t="n"/>
+      <c r="E282" s="41" t="n"/>
       <c r="F282" s="16" t="n"/>
-      <c r="G282" s="36">
+      <c r="G282" s="39">
         <f>IF(OR(E282="",F282=""),"",ROUND(E282*F282,2))</f>
         <v/>
       </c>
@@ -6012,9 +6068,9 @@
       <c r="B283" s="12" t="n"/>
       <c r="C283" s="12" t="n"/>
       <c r="D283" s="12" t="n"/>
-      <c r="E283" s="38" t="n"/>
+      <c r="E283" s="41" t="n"/>
       <c r="F283" s="16" t="n"/>
-      <c r="G283" s="36">
+      <c r="G283" s="39">
         <f>IF(OR(E283="",F283=""),"",ROUND(E283*F283,2))</f>
         <v/>
       </c>
@@ -6026,9 +6082,9 @@
       <c r="B284" s="12" t="n"/>
       <c r="C284" s="12" t="n"/>
       <c r="D284" s="12" t="n"/>
-      <c r="E284" s="38" t="n"/>
+      <c r="E284" s="41" t="n"/>
       <c r="F284" s="16" t="n"/>
-      <c r="G284" s="36">
+      <c r="G284" s="39">
         <f>IF(OR(E284="",F284=""),"",ROUND(E284*F284,2))</f>
         <v/>
       </c>
@@ -6040,9 +6096,9 @@
       <c r="B285" s="12" t="n"/>
       <c r="C285" s="12" t="n"/>
       <c r="D285" s="12" t="n"/>
-      <c r="E285" s="38" t="n"/>
+      <c r="E285" s="41" t="n"/>
       <c r="F285" s="16" t="n"/>
-      <c r="G285" s="36">
+      <c r="G285" s="39">
         <f>IF(OR(E285="",F285=""),"",ROUND(E285*F285,2))</f>
         <v/>
       </c>
@@ -6054,9 +6110,9 @@
       <c r="B286" s="12" t="n"/>
       <c r="C286" s="12" t="n"/>
       <c r="D286" s="12" t="n"/>
-      <c r="E286" s="38" t="n"/>
+      <c r="E286" s="41" t="n"/>
       <c r="F286" s="16" t="n"/>
-      <c r="G286" s="36">
+      <c r="G286" s="39">
         <f>IF(OR(E286="",F286=""),"",ROUND(E286*F286,2))</f>
         <v/>
       </c>
@@ -6068,9 +6124,9 @@
       <c r="B287" s="12" t="n"/>
       <c r="C287" s="12" t="n"/>
       <c r="D287" s="12" t="n"/>
-      <c r="E287" s="38" t="n"/>
+      <c r="E287" s="41" t="n"/>
       <c r="F287" s="16" t="n"/>
-      <c r="G287" s="36">
+      <c r="G287" s="39">
         <f>IF(OR(E287="",F287=""),"",ROUND(E287*F287,2))</f>
         <v/>
       </c>
@@ -6082,9 +6138,9 @@
       <c r="B288" s="12" t="n"/>
       <c r="C288" s="12" t="n"/>
       <c r="D288" s="12" t="n"/>
-      <c r="E288" s="38" t="n"/>
+      <c r="E288" s="41" t="n"/>
       <c r="F288" s="16" t="n"/>
-      <c r="G288" s="36">
+      <c r="G288" s="39">
         <f>IF(OR(E288="",F288=""),"",ROUND(E288*F288,2))</f>
         <v/>
       </c>
@@ -6096,9 +6152,9 @@
       <c r="B289" s="12" t="n"/>
       <c r="C289" s="12" t="n"/>
       <c r="D289" s="12" t="n"/>
-      <c r="E289" s="38" t="n"/>
+      <c r="E289" s="41" t="n"/>
       <c r="F289" s="16" t="n"/>
-      <c r="G289" s="36">
+      <c r="G289" s="39">
         <f>IF(OR(E289="",F289=""),"",ROUND(E289*F289,2))</f>
         <v/>
       </c>
@@ -6110,9 +6166,9 @@
       <c r="B290" s="12" t="n"/>
       <c r="C290" s="12" t="n"/>
       <c r="D290" s="12" t="n"/>
-      <c r="E290" s="38" t="n"/>
+      <c r="E290" s="41" t="n"/>
       <c r="F290" s="16" t="n"/>
-      <c r="G290" s="36">
+      <c r="G290" s="39">
         <f>IF(OR(E290="",F290=""),"",ROUND(E290*F290,2))</f>
         <v/>
       </c>
@@ -6124,9 +6180,9 @@
       <c r="B291" s="12" t="n"/>
       <c r="C291" s="12" t="n"/>
       <c r="D291" s="12" t="n"/>
-      <c r="E291" s="38" t="n"/>
+      <c r="E291" s="41" t="n"/>
       <c r="F291" s="16" t="n"/>
-      <c r="G291" s="36">
+      <c r="G291" s="39">
         <f>IF(OR(E291="",F291=""),"",ROUND(E291*F291,2))</f>
         <v/>
       </c>
@@ -6138,9 +6194,9 @@
       <c r="B292" s="12" t="n"/>
       <c r="C292" s="12" t="n"/>
       <c r="D292" s="12" t="n"/>
-      <c r="E292" s="38" t="n"/>
+      <c r="E292" s="41" t="n"/>
       <c r="F292" s="16" t="n"/>
-      <c r="G292" s="36">
+      <c r="G292" s="39">
         <f>IF(OR(E292="",F292=""),"",ROUND(E292*F292,2))</f>
         <v/>
       </c>
@@ -6152,9 +6208,9 @@
       <c r="B293" s="12" t="n"/>
       <c r="C293" s="12" t="n"/>
       <c r="D293" s="12" t="n"/>
-      <c r="E293" s="38" t="n"/>
+      <c r="E293" s="41" t="n"/>
       <c r="F293" s="16" t="n"/>
-      <c r="G293" s="36">
+      <c r="G293" s="39">
         <f>IF(OR(E293="",F293=""),"",ROUND(E293*F293,2))</f>
         <v/>
       </c>
@@ -6166,9 +6222,9 @@
       <c r="B294" s="12" t="n"/>
       <c r="C294" s="12" t="n"/>
       <c r="D294" s="12" t="n"/>
-      <c r="E294" s="38" t="n"/>
+      <c r="E294" s="41" t="n"/>
       <c r="F294" s="16" t="n"/>
-      <c r="G294" s="36">
+      <c r="G294" s="39">
         <f>IF(OR(E294="",F294=""),"",ROUND(E294*F294,2))</f>
         <v/>
       </c>
@@ -6180,9 +6236,9 @@
       <c r="B295" s="12" t="n"/>
       <c r="C295" s="12" t="n"/>
       <c r="D295" s="12" t="n"/>
-      <c r="E295" s="38" t="n"/>
+      <c r="E295" s="41" t="n"/>
       <c r="F295" s="16" t="n"/>
-      <c r="G295" s="36">
+      <c r="G295" s="39">
         <f>IF(OR(E295="",F295=""),"",ROUND(E295*F295,2))</f>
         <v/>
       </c>
@@ -6194,9 +6250,9 @@
       <c r="B296" s="12" t="n"/>
       <c r="C296" s="12" t="n"/>
       <c r="D296" s="12" t="n"/>
-      <c r="E296" s="38" t="n"/>
+      <c r="E296" s="41" t="n"/>
       <c r="F296" s="16" t="n"/>
-      <c r="G296" s="36">
+      <c r="G296" s="39">
         <f>IF(OR(E296="",F296=""),"",ROUND(E296*F296,2))</f>
         <v/>
       </c>
@@ -6208,9 +6264,9 @@
       <c r="B297" s="12" t="n"/>
       <c r="C297" s="12" t="n"/>
       <c r="D297" s="12" t="n"/>
-      <c r="E297" s="38" t="n"/>
+      <c r="E297" s="41" t="n"/>
       <c r="F297" s="16" t="n"/>
-      <c r="G297" s="36">
+      <c r="G297" s="39">
         <f>IF(OR(E297="",F297=""),"",ROUND(E297*F297,2))</f>
         <v/>
       </c>
@@ -6222,9 +6278,9 @@
       <c r="B298" s="12" t="n"/>
       <c r="C298" s="12" t="n"/>
       <c r="D298" s="12" t="n"/>
-      <c r="E298" s="38" t="n"/>
+      <c r="E298" s="41" t="n"/>
       <c r="F298" s="16" t="n"/>
-      <c r="G298" s="36">
+      <c r="G298" s="39">
         <f>IF(OR(E298="",F298=""),"",ROUND(E298*F298,2))</f>
         <v/>
       </c>
@@ -6236,9 +6292,9 @@
       <c r="B299" s="12" t="n"/>
       <c r="C299" s="12" t="n"/>
       <c r="D299" s="12" t="n"/>
-      <c r="E299" s="38" t="n"/>
+      <c r="E299" s="41" t="n"/>
       <c r="F299" s="16" t="n"/>
-      <c r="G299" s="36">
+      <c r="G299" s="39">
         <f>IF(OR(E299="",F299=""),"",ROUND(E299*F299,2))</f>
         <v/>
       </c>
@@ -6250,9 +6306,9 @@
       <c r="B300" s="12" t="n"/>
       <c r="C300" s="12" t="n"/>
       <c r="D300" s="12" t="n"/>
-      <c r="E300" s="38" t="n"/>
+      <c r="E300" s="41" t="n"/>
       <c r="F300" s="16" t="n"/>
-      <c r="G300" s="36">
+      <c r="G300" s="39">
         <f>IF(OR(E300="",F300=""),"",ROUND(E300*F300,2))</f>
         <v/>
       </c>
@@ -6264,9 +6320,9 @@
       <c r="B301" s="12" t="n"/>
       <c r="C301" s="12" t="n"/>
       <c r="D301" s="12" t="n"/>
-      <c r="E301" s="38" t="n"/>
+      <c r="E301" s="41" t="n"/>
       <c r="F301" s="16" t="n"/>
-      <c r="G301" s="36">
+      <c r="G301" s="39">
         <f>IF(OR(E301="",F301=""),"",ROUND(E301*F301,2))</f>
         <v/>
       </c>
@@ -6278,9 +6334,9 @@
       <c r="B302" s="12" t="n"/>
       <c r="C302" s="12" t="n"/>
       <c r="D302" s="12" t="n"/>
-      <c r="E302" s="38" t="n"/>
+      <c r="E302" s="41" t="n"/>
       <c r="F302" s="16" t="n"/>
-      <c r="G302" s="36">
+      <c r="G302" s="39">
         <f>IF(OR(E302="",F302=""),"",ROUND(E302*F302,2))</f>
         <v/>
       </c>
@@ -6292,9 +6348,9 @@
       <c r="B303" s="12" t="n"/>
       <c r="C303" s="12" t="n"/>
       <c r="D303" s="12" t="n"/>
-      <c r="E303" s="38" t="n"/>
+      <c r="E303" s="41" t="n"/>
       <c r="F303" s="16" t="n"/>
-      <c r="G303" s="36">
+      <c r="G303" s="39">
         <f>IF(OR(E303="",F303=""),"",ROUND(E303*F303,2))</f>
         <v/>
       </c>
@@ -6306,9 +6362,9 @@
       <c r="B304" s="12" t="n"/>
       <c r="C304" s="12" t="n"/>
       <c r="D304" s="12" t="n"/>
-      <c r="E304" s="38" t="n"/>
+      <c r="E304" s="41" t="n"/>
       <c r="F304" s="16" t="n"/>
-      <c r="G304" s="36">
+      <c r="G304" s="39">
         <f>IF(OR(E304="",F304=""),"",ROUND(E304*F304,2))</f>
         <v/>
       </c>
@@ -6320,9 +6376,9 @@
       <c r="B305" s="12" t="n"/>
       <c r="C305" s="12" t="n"/>
       <c r="D305" s="12" t="n"/>
-      <c r="E305" s="38" t="n"/>
+      <c r="E305" s="41" t="n"/>
       <c r="F305" s="16" t="n"/>
-      <c r="G305" s="36">
+      <c r="G305" s="39">
         <f>IF(OR(E305="",F305=""),"",ROUND(E305*F305,2))</f>
         <v/>
       </c>
@@ -6334,9 +6390,9 @@
       <c r="B306" s="12" t="n"/>
       <c r="C306" s="12" t="n"/>
       <c r="D306" s="12" t="n"/>
-      <c r="E306" s="38" t="n"/>
+      <c r="E306" s="41" t="n"/>
       <c r="F306" s="16" t="n"/>
-      <c r="G306" s="36">
+      <c r="G306" s="39">
         <f>IF(OR(E306="",F306=""),"",ROUND(E306*F306,2))</f>
         <v/>
       </c>
@@ -6348,9 +6404,9 @@
       <c r="B307" s="12" t="n"/>
       <c r="C307" s="12" t="n"/>
       <c r="D307" s="12" t="n"/>
-      <c r="E307" s="38" t="n"/>
+      <c r="E307" s="41" t="n"/>
       <c r="F307" s="16" t="n"/>
-      <c r="G307" s="36">
+      <c r="G307" s="39">
         <f>IF(OR(E307="",F307=""),"",ROUND(E307*F307,2))</f>
         <v/>
       </c>
@@ -6362,9 +6418,9 @@
       <c r="B308" s="12" t="n"/>
       <c r="C308" s="12" t="n"/>
       <c r="D308" s="12" t="n"/>
-      <c r="E308" s="38" t="n"/>
+      <c r="E308" s="41" t="n"/>
       <c r="F308" s="16" t="n"/>
-      <c r="G308" s="36">
+      <c r="G308" s="39">
         <f>IF(OR(E308="",F308=""),"",ROUND(E308*F308,2))</f>
         <v/>
       </c>
@@ -6376,9 +6432,9 @@
       <c r="B309" s="12" t="n"/>
       <c r="C309" s="12" t="n"/>
       <c r="D309" s="12" t="n"/>
-      <c r="E309" s="38" t="n"/>
+      <c r="E309" s="41" t="n"/>
       <c r="F309" s="16" t="n"/>
-      <c r="G309" s="36">
+      <c r="G309" s="39">
         <f>IF(OR(E309="",F309=""),"",ROUND(E309*F309,2))</f>
         <v/>
       </c>
@@ -6390,9 +6446,9 @@
       <c r="B310" s="12" t="n"/>
       <c r="C310" s="12" t="n"/>
       <c r="D310" s="12" t="n"/>
-      <c r="E310" s="38" t="n"/>
+      <c r="E310" s="41" t="n"/>
       <c r="F310" s="16" t="n"/>
-      <c r="G310" s="36">
+      <c r="G310" s="39">
         <f>IF(OR(E310="",F310=""),"",ROUND(E310*F310,2))</f>
         <v/>
       </c>
@@ -6404,9 +6460,9 @@
       <c r="B311" s="12" t="n"/>
       <c r="C311" s="12" t="n"/>
       <c r="D311" s="12" t="n"/>
-      <c r="E311" s="38" t="n"/>
+      <c r="E311" s="41" t="n"/>
       <c r="F311" s="16" t="n"/>
-      <c r="G311" s="36">
+      <c r="G311" s="39">
         <f>IF(OR(E311="",F311=""),"",ROUND(E311*F311,2))</f>
         <v/>
       </c>
@@ -6418,9 +6474,9 @@
       <c r="B312" s="12" t="n"/>
       <c r="C312" s="12" t="n"/>
       <c r="D312" s="12" t="n"/>
-      <c r="E312" s="38" t="n"/>
+      <c r="E312" s="41" t="n"/>
       <c r="F312" s="16" t="n"/>
-      <c r="G312" s="36">
+      <c r="G312" s="39">
         <f>IF(OR(E312="",F312=""),"",ROUND(E312*F312,2))</f>
         <v/>
       </c>
@@ -6432,9 +6488,9 @@
       <c r="B313" s="12" t="n"/>
       <c r="C313" s="12" t="n"/>
       <c r="D313" s="12" t="n"/>
-      <c r="E313" s="38" t="n"/>
+      <c r="E313" s="41" t="n"/>
       <c r="F313" s="16" t="n"/>
-      <c r="G313" s="36">
+      <c r="G313" s="39">
         <f>IF(OR(E313="",F313=""),"",ROUND(E313*F313,2))</f>
         <v/>
       </c>
@@ -6446,9 +6502,9 @@
       <c r="B314" s="12" t="n"/>
       <c r="C314" s="12" t="n"/>
       <c r="D314" s="12" t="n"/>
-      <c r="E314" s="38" t="n"/>
+      <c r="E314" s="41" t="n"/>
       <c r="F314" s="16" t="n"/>
-      <c r="G314" s="36">
+      <c r="G314" s="39">
         <f>IF(OR(E314="",F314=""),"",ROUND(E314*F314,2))</f>
         <v/>
       </c>
@@ -6460,9 +6516,9 @@
       <c r="B315" s="12" t="n"/>
       <c r="C315" s="12" t="n"/>
       <c r="D315" s="12" t="n"/>
-      <c r="E315" s="38" t="n"/>
+      <c r="E315" s="41" t="n"/>
       <c r="F315" s="16" t="n"/>
-      <c r="G315" s="36">
+      <c r="G315" s="39">
         <f>IF(OR(E315="",F315=""),"",ROUND(E315*F315,2))</f>
         <v/>
       </c>
@@ -6474,9 +6530,9 @@
       <c r="B316" s="12" t="n"/>
       <c r="C316" s="12" t="n"/>
       <c r="D316" s="12" t="n"/>
-      <c r="E316" s="38" t="n"/>
+      <c r="E316" s="41" t="n"/>
       <c r="F316" s="16" t="n"/>
-      <c r="G316" s="36">
+      <c r="G316" s="39">
         <f>IF(OR(E316="",F316=""),"",ROUND(E316*F316,2))</f>
         <v/>
       </c>
@@ -6488,9 +6544,9 @@
       <c r="B317" s="12" t="n"/>
       <c r="C317" s="12" t="n"/>
       <c r="D317" s="12" t="n"/>
-      <c r="E317" s="38" t="n"/>
+      <c r="E317" s="41" t="n"/>
       <c r="F317" s="16" t="n"/>
-      <c r="G317" s="36">
+      <c r="G317" s="39">
         <f>IF(OR(E317="",F317=""),"",ROUND(E317*F317,2))</f>
         <v/>
       </c>
@@ -6502,9 +6558,9 @@
       <c r="B318" s="12" t="n"/>
       <c r="C318" s="12" t="n"/>
       <c r="D318" s="12" t="n"/>
-      <c r="E318" s="38" t="n"/>
+      <c r="E318" s="41" t="n"/>
       <c r="F318" s="16" t="n"/>
-      <c r="G318" s="36">
+      <c r="G318" s="39">
         <f>IF(OR(E318="",F318=""),"",ROUND(E318*F318,2))</f>
         <v/>
       </c>
@@ -6516,9 +6572,9 @@
       <c r="B319" s="12" t="n"/>
       <c r="C319" s="12" t="n"/>
       <c r="D319" s="12" t="n"/>
-      <c r="E319" s="38" t="n"/>
+      <c r="E319" s="41" t="n"/>
       <c r="F319" s="16" t="n"/>
-      <c r="G319" s="36">
+      <c r="G319" s="39">
         <f>IF(OR(E319="",F319=""),"",ROUND(E319*F319,2))</f>
         <v/>
       </c>
@@ -6530,9 +6586,9 @@
       <c r="B320" s="12" t="n"/>
       <c r="C320" s="12" t="n"/>
       <c r="D320" s="12" t="n"/>
-      <c r="E320" s="38" t="n"/>
+      <c r="E320" s="41" t="n"/>
       <c r="F320" s="16" t="n"/>
-      <c r="G320" s="36">
+      <c r="G320" s="39">
         <f>IF(OR(E320="",F320=""),"",ROUND(E320*F320,2))</f>
         <v/>
       </c>
@@ -6544,9 +6600,9 @@
       <c r="B321" s="12" t="n"/>
       <c r="C321" s="12" t="n"/>
       <c r="D321" s="12" t="n"/>
-      <c r="E321" s="38" t="n"/>
+      <c r="E321" s="41" t="n"/>
       <c r="F321" s="16" t="n"/>
-      <c r="G321" s="36">
+      <c r="G321" s="39">
         <f>IF(OR(E321="",F321=""),"",ROUND(E321*F321,2))</f>
         <v/>
       </c>
@@ -6558,9 +6614,9 @@
       <c r="B322" s="12" t="n"/>
       <c r="C322" s="12" t="n"/>
       <c r="D322" s="12" t="n"/>
-      <c r="E322" s="38" t="n"/>
+      <c r="E322" s="41" t="n"/>
       <c r="F322" s="16" t="n"/>
-      <c r="G322" s="36">
+      <c r="G322" s="39">
         <f>IF(OR(E322="",F322=""),"",ROUND(E322*F322,2))</f>
         <v/>
       </c>
@@ -6572,9 +6628,9 @@
       <c r="B323" s="12" t="n"/>
       <c r="C323" s="12" t="n"/>
       <c r="D323" s="12" t="n"/>
-      <c r="E323" s="38" t="n"/>
+      <c r="E323" s="41" t="n"/>
       <c r="F323" s="16" t="n"/>
-      <c r="G323" s="36">
+      <c r="G323" s="39">
         <f>IF(OR(E323="",F323=""),"",ROUND(E323*F323,2))</f>
         <v/>
       </c>
@@ -6586,9 +6642,9 @@
       <c r="B324" s="12" t="n"/>
       <c r="C324" s="12" t="n"/>
       <c r="D324" s="12" t="n"/>
-      <c r="E324" s="38" t="n"/>
+      <c r="E324" s="41" t="n"/>
       <c r="F324" s="16" t="n"/>
-      <c r="G324" s="36">
+      <c r="G324" s="39">
         <f>IF(OR(E324="",F324=""),"",ROUND(E324*F324,2))</f>
         <v/>
       </c>
@@ -6600,9 +6656,9 @@
       <c r="B325" s="12" t="n"/>
       <c r="C325" s="12" t="n"/>
       <c r="D325" s="12" t="n"/>
-      <c r="E325" s="38" t="n"/>
+      <c r="E325" s="41" t="n"/>
       <c r="F325" s="16" t="n"/>
-      <c r="G325" s="36">
+      <c r="G325" s="39">
         <f>IF(OR(E325="",F325=""),"",ROUND(E325*F325,2))</f>
         <v/>
       </c>
@@ -6614,9 +6670,9 @@
       <c r="B326" s="12" t="n"/>
       <c r="C326" s="12" t="n"/>
       <c r="D326" s="12" t="n"/>
-      <c r="E326" s="38" t="n"/>
+      <c r="E326" s="41" t="n"/>
       <c r="F326" s="16" t="n"/>
-      <c r="G326" s="36">
+      <c r="G326" s="39">
         <f>IF(OR(E326="",F326=""),"",ROUND(E326*F326,2))</f>
         <v/>
       </c>
@@ -6628,9 +6684,9 @@
       <c r="B327" s="12" t="n"/>
       <c r="C327" s="12" t="n"/>
       <c r="D327" s="12" t="n"/>
-      <c r="E327" s="38" t="n"/>
+      <c r="E327" s="41" t="n"/>
       <c r="F327" s="16" t="n"/>
-      <c r="G327" s="36">
+      <c r="G327" s="39">
         <f>IF(OR(E327="",F327=""),"",ROUND(E327*F327,2))</f>
         <v/>
       </c>
@@ -6642,9 +6698,9 @@
       <c r="B328" s="12" t="n"/>
       <c r="C328" s="12" t="n"/>
       <c r="D328" s="12" t="n"/>
-      <c r="E328" s="38" t="n"/>
+      <c r="E328" s="41" t="n"/>
       <c r="F328" s="16" t="n"/>
-      <c r="G328" s="36">
+      <c r="G328" s="39">
         <f>IF(OR(E328="",F328=""),"",ROUND(E328*F328,2))</f>
         <v/>
       </c>
@@ -6656,9 +6712,9 @@
       <c r="B329" s="12" t="n"/>
       <c r="C329" s="12" t="n"/>
       <c r="D329" s="12" t="n"/>
-      <c r="E329" s="38" t="n"/>
+      <c r="E329" s="41" t="n"/>
       <c r="F329" s="16" t="n"/>
-      <c r="G329" s="36">
+      <c r="G329" s="39">
         <f>IF(OR(E329="",F329=""),"",ROUND(E329*F329,2))</f>
         <v/>
       </c>
@@ -6670,9 +6726,9 @@
       <c r="B330" s="12" t="n"/>
       <c r="C330" s="12" t="n"/>
       <c r="D330" s="12" t="n"/>
-      <c r="E330" s="38" t="n"/>
+      <c r="E330" s="41" t="n"/>
       <c r="F330" s="16" t="n"/>
-      <c r="G330" s="36">
+      <c r="G330" s="39">
         <f>IF(OR(E330="",F330=""),"",ROUND(E330*F330,2))</f>
         <v/>
       </c>
@@ -6684,9 +6740,9 @@
       <c r="B331" s="12" t="n"/>
       <c r="C331" s="12" t="n"/>
       <c r="D331" s="12" t="n"/>
-      <c r="E331" s="38" t="n"/>
+      <c r="E331" s="41" t="n"/>
       <c r="F331" s="16" t="n"/>
-      <c r="G331" s="36">
+      <c r="G331" s="39">
         <f>IF(OR(E331="",F331=""),"",ROUND(E331*F331,2))</f>
         <v/>
       </c>
@@ -6698,9 +6754,9 @@
       <c r="B332" s="12" t="n"/>
       <c r="C332" s="12" t="n"/>
       <c r="D332" s="12" t="n"/>
-      <c r="E332" s="38" t="n"/>
+      <c r="E332" s="41" t="n"/>
       <c r="F332" s="16" t="n"/>
-      <c r="G332" s="36">
+      <c r="G332" s="39">
         <f>IF(OR(E332="",F332=""),"",ROUND(E332*F332,2))</f>
         <v/>
       </c>
@@ -6712,9 +6768,9 @@
       <c r="B333" s="12" t="n"/>
       <c r="C333" s="12" t="n"/>
       <c r="D333" s="12" t="n"/>
-      <c r="E333" s="38" t="n"/>
+      <c r="E333" s="41" t="n"/>
       <c r="F333" s="16" t="n"/>
-      <c r="G333" s="36">
+      <c r="G333" s="39">
         <f>IF(OR(E333="",F333=""),"",ROUND(E333*F333,2))</f>
         <v/>
       </c>
@@ -6726,9 +6782,9 @@
       <c r="B334" s="12" t="n"/>
       <c r="C334" s="12" t="n"/>
       <c r="D334" s="12" t="n"/>
-      <c r="E334" s="38" t="n"/>
+      <c r="E334" s="41" t="n"/>
       <c r="F334" s="16" t="n"/>
-      <c r="G334" s="36">
+      <c r="G334" s="39">
         <f>IF(OR(E334="",F334=""),"",ROUND(E334*F334,2))</f>
         <v/>
       </c>
@@ -6740,9 +6796,9 @@
       <c r="B335" s="12" t="n"/>
       <c r="C335" s="12" t="n"/>
       <c r="D335" s="12" t="n"/>
-      <c r="E335" s="38" t="n"/>
+      <c r="E335" s="41" t="n"/>
       <c r="F335" s="16" t="n"/>
-      <c r="G335" s="36">
+      <c r="G335" s="39">
         <f>IF(OR(E335="",F335=""),"",ROUND(E335*F335,2))</f>
         <v/>
       </c>
@@ -6754,9 +6810,9 @@
       <c r="B336" s="12" t="n"/>
       <c r="C336" s="12" t="n"/>
       <c r="D336" s="12" t="n"/>
-      <c r="E336" s="38" t="n"/>
+      <c r="E336" s="41" t="n"/>
       <c r="F336" s="16" t="n"/>
-      <c r="G336" s="36">
+      <c r="G336" s="39">
         <f>IF(OR(E336="",F336=""),"",ROUND(E336*F336,2))</f>
         <v/>
       </c>
@@ -6768,9 +6824,9 @@
       <c r="B337" s="12" t="n"/>
       <c r="C337" s="12" t="n"/>
       <c r="D337" s="12" t="n"/>
-      <c r="E337" s="38" t="n"/>
+      <c r="E337" s="41" t="n"/>
       <c r="F337" s="16" t="n"/>
-      <c r="G337" s="36">
+      <c r="G337" s="39">
         <f>IF(OR(E337="",F337=""),"",ROUND(E337*F337,2))</f>
         <v/>
       </c>
@@ -6782,9 +6838,9 @@
       <c r="B338" s="12" t="n"/>
       <c r="C338" s="12" t="n"/>
       <c r="D338" s="12" t="n"/>
-      <c r="E338" s="38" t="n"/>
+      <c r="E338" s="41" t="n"/>
       <c r="F338" s="16" t="n"/>
-      <c r="G338" s="36">
+      <c r="G338" s="39">
         <f>IF(OR(E338="",F338=""),"",ROUND(E338*F338,2))</f>
         <v/>
       </c>
@@ -6796,9 +6852,9 @@
       <c r="B339" s="12" t="n"/>
       <c r="C339" s="12" t="n"/>
       <c r="D339" s="12" t="n"/>
-      <c r="E339" s="38" t="n"/>
+      <c r="E339" s="41" t="n"/>
       <c r="F339" s="16" t="n"/>
-      <c r="G339" s="36">
+      <c r="G339" s="39">
         <f>IF(OR(E339="",F339=""),"",ROUND(E339*F339,2))</f>
         <v/>
       </c>
@@ -6810,9 +6866,9 @@
       <c r="B340" s="12" t="n"/>
       <c r="C340" s="12" t="n"/>
       <c r="D340" s="12" t="n"/>
-      <c r="E340" s="38" t="n"/>
+      <c r="E340" s="41" t="n"/>
       <c r="F340" s="16" t="n"/>
-      <c r="G340" s="36">
+      <c r="G340" s="39">
         <f>IF(OR(E340="",F340=""),"",ROUND(E340*F340,2))</f>
         <v/>
       </c>
@@ -6824,9 +6880,9 @@
       <c r="B341" s="12" t="n"/>
       <c r="C341" s="12" t="n"/>
       <c r="D341" s="12" t="n"/>
-      <c r="E341" s="38" t="n"/>
+      <c r="E341" s="41" t="n"/>
       <c r="F341" s="16" t="n"/>
-      <c r="G341" s="36">
+      <c r="G341" s="39">
         <f>IF(OR(E341="",F341=""),"",ROUND(E341*F341,2))</f>
         <v/>
       </c>
@@ -6838,9 +6894,9 @@
       <c r="B342" s="12" t="n"/>
       <c r="C342" s="12" t="n"/>
       <c r="D342" s="12" t="n"/>
-      <c r="E342" s="38" t="n"/>
+      <c r="E342" s="41" t="n"/>
       <c r="F342" s="16" t="n"/>
-      <c r="G342" s="36">
+      <c r="G342" s="39">
         <f>IF(OR(E342="",F342=""),"",ROUND(E342*F342,2))</f>
         <v/>
       </c>
@@ -6852,9 +6908,9 @@
       <c r="B343" s="12" t="n"/>
       <c r="C343" s="12" t="n"/>
       <c r="D343" s="12" t="n"/>
-      <c r="E343" s="38" t="n"/>
+      <c r="E343" s="41" t="n"/>
       <c r="F343" s="16" t="n"/>
-      <c r="G343" s="36">
+      <c r="G343" s="39">
         <f>IF(OR(E343="",F343=""),"",ROUND(E343*F343,2))</f>
         <v/>
       </c>
@@ -6866,9 +6922,9 @@
       <c r="B344" s="12" t="n"/>
       <c r="C344" s="12" t="n"/>
       <c r="D344" s="12" t="n"/>
-      <c r="E344" s="38" t="n"/>
+      <c r="E344" s="41" t="n"/>
       <c r="F344" s="16" t="n"/>
-      <c r="G344" s="36">
+      <c r="G344" s="39">
         <f>IF(OR(E344="",F344=""),"",ROUND(E344*F344,2))</f>
         <v/>
       </c>
@@ -6880,9 +6936,9 @@
       <c r="B345" s="12" t="n"/>
       <c r="C345" s="12" t="n"/>
       <c r="D345" s="12" t="n"/>
-      <c r="E345" s="38" t="n"/>
+      <c r="E345" s="41" t="n"/>
       <c r="F345" s="16" t="n"/>
-      <c r="G345" s="36">
+      <c r="G345" s="39">
         <f>IF(OR(E345="",F345=""),"",ROUND(E345*F345,2))</f>
         <v/>
       </c>
@@ -6894,9 +6950,9 @@
       <c r="B346" s="12" t="n"/>
       <c r="C346" s="12" t="n"/>
       <c r="D346" s="12" t="n"/>
-      <c r="E346" s="38" t="n"/>
+      <c r="E346" s="41" t="n"/>
       <c r="F346" s="16" t="n"/>
-      <c r="G346" s="36">
+      <c r="G346" s="39">
         <f>IF(OR(E346="",F346=""),"",ROUND(E346*F346,2))</f>
         <v/>
       </c>
@@ -6908,9 +6964,9 @@
       <c r="B347" s="12" t="n"/>
       <c r="C347" s="12" t="n"/>
       <c r="D347" s="12" t="n"/>
-      <c r="E347" s="38" t="n"/>
+      <c r="E347" s="41" t="n"/>
       <c r="F347" s="16" t="n"/>
-      <c r="G347" s="36">
+      <c r="G347" s="39">
         <f>IF(OR(E347="",F347=""),"",ROUND(E347*F347,2))</f>
         <v/>
       </c>
@@ -6922,9 +6978,9 @@
       <c r="B348" s="12" t="n"/>
       <c r="C348" s="12" t="n"/>
       <c r="D348" s="12" t="n"/>
-      <c r="E348" s="38" t="n"/>
+      <c r="E348" s="41" t="n"/>
       <c r="F348" s="16" t="n"/>
-      <c r="G348" s="36">
+      <c r="G348" s="39">
         <f>IF(OR(E348="",F348=""),"",ROUND(E348*F348,2))</f>
         <v/>
       </c>
@@ -6936,9 +6992,9 @@
       <c r="B349" s="12" t="n"/>
       <c r="C349" s="12" t="n"/>
       <c r="D349" s="12" t="n"/>
-      <c r="E349" s="38" t="n"/>
+      <c r="E349" s="41" t="n"/>
       <c r="F349" s="16" t="n"/>
-      <c r="G349" s="36">
+      <c r="G349" s="39">
         <f>IF(OR(E349="",F349=""),"",ROUND(E349*F349,2))</f>
         <v/>
       </c>
@@ -6950,9 +7006,9 @@
       <c r="B350" s="12" t="n"/>
       <c r="C350" s="12" t="n"/>
       <c r="D350" s="12" t="n"/>
-      <c r="E350" s="38" t="n"/>
+      <c r="E350" s="41" t="n"/>
       <c r="F350" s="16" t="n"/>
-      <c r="G350" s="36">
+      <c r="G350" s="39">
         <f>IF(OR(E350="",F350=""),"",ROUND(E350*F350,2))</f>
         <v/>
       </c>
@@ -6964,9 +7020,9 @@
       <c r="B351" s="12" t="n"/>
       <c r="C351" s="12" t="n"/>
       <c r="D351" s="12" t="n"/>
-      <c r="E351" s="38" t="n"/>
+      <c r="E351" s="41" t="n"/>
       <c r="F351" s="16" t="n"/>
-      <c r="G351" s="36">
+      <c r="G351" s="39">
         <f>IF(OR(E351="",F351=""),"",ROUND(E351*F351,2))</f>
         <v/>
       </c>
@@ -6978,9 +7034,9 @@
       <c r="B352" s="12" t="n"/>
       <c r="C352" s="12" t="n"/>
       <c r="D352" s="12" t="n"/>
-      <c r="E352" s="38" t="n"/>
+      <c r="E352" s="41" t="n"/>
       <c r="F352" s="16" t="n"/>
-      <c r="G352" s="36">
+      <c r="G352" s="39">
         <f>IF(OR(E352="",F352=""),"",ROUND(E352*F352,2))</f>
         <v/>
       </c>
@@ -6992,9 +7048,9 @@
       <c r="B353" s="12" t="n"/>
       <c r="C353" s="12" t="n"/>
       <c r="D353" s="12" t="n"/>
-      <c r="E353" s="38" t="n"/>
+      <c r="E353" s="41" t="n"/>
       <c r="F353" s="16" t="n"/>
-      <c r="G353" s="36">
+      <c r="G353" s="39">
         <f>IF(OR(E353="",F353=""),"",ROUND(E353*F353,2))</f>
         <v/>
       </c>
@@ -7006,9 +7062,9 @@
       <c r="B354" s="12" t="n"/>
       <c r="C354" s="12" t="n"/>
       <c r="D354" s="12" t="n"/>
-      <c r="E354" s="38" t="n"/>
+      <c r="E354" s="41" t="n"/>
       <c r="F354" s="16" t="n"/>
-      <c r="G354" s="36">
+      <c r="G354" s="39">
         <f>IF(OR(E354="",F354=""),"",ROUND(E354*F354,2))</f>
         <v/>
       </c>
@@ -7020,9 +7076,9 @@
       <c r="B355" s="12" t="n"/>
       <c r="C355" s="12" t="n"/>
       <c r="D355" s="12" t="n"/>
-      <c r="E355" s="38" t="n"/>
+      <c r="E355" s="41" t="n"/>
       <c r="F355" s="16" t="n"/>
-      <c r="G355" s="36">
+      <c r="G355" s="39">
         <f>IF(OR(E355="",F355=""),"",ROUND(E355*F355,2))</f>
         <v/>
       </c>
@@ -7034,9 +7090,9 @@
       <c r="B356" s="12" t="n"/>
       <c r="C356" s="12" t="n"/>
       <c r="D356" s="12" t="n"/>
-      <c r="E356" s="38" t="n"/>
+      <c r="E356" s="41" t="n"/>
       <c r="F356" s="16" t="n"/>
-      <c r="G356" s="36">
+      <c r="G356" s="39">
         <f>IF(OR(E356="",F356=""),"",ROUND(E356*F356,2))</f>
         <v/>
       </c>
@@ -7048,9 +7104,9 @@
       <c r="B357" s="12" t="n"/>
       <c r="C357" s="12" t="n"/>
       <c r="D357" s="12" t="n"/>
-      <c r="E357" s="38" t="n"/>
+      <c r="E357" s="41" t="n"/>
       <c r="F357" s="16" t="n"/>
-      <c r="G357" s="36">
+      <c r="G357" s="39">
         <f>IF(OR(E357="",F357=""),"",ROUND(E357*F357,2))</f>
         <v/>
       </c>
@@ -7062,9 +7118,9 @@
       <c r="B358" s="12" t="n"/>
       <c r="C358" s="12" t="n"/>
       <c r="D358" s="12" t="n"/>
-      <c r="E358" s="38" t="n"/>
+      <c r="E358" s="41" t="n"/>
       <c r="F358" s="16" t="n"/>
-      <c r="G358" s="36">
+      <c r="G358" s="39">
         <f>IF(OR(E358="",F358=""),"",ROUND(E358*F358,2))</f>
         <v/>
       </c>
@@ -7076,9 +7132,9 @@
       <c r="B359" s="12" t="n"/>
       <c r="C359" s="12" t="n"/>
       <c r="D359" s="12" t="n"/>
-      <c r="E359" s="38" t="n"/>
+      <c r="E359" s="41" t="n"/>
       <c r="F359" s="16" t="n"/>
-      <c r="G359" s="36">
+      <c r="G359" s="39">
         <f>IF(OR(E359="",F359=""),"",ROUND(E359*F359,2))</f>
         <v/>
       </c>
@@ -7090,9 +7146,9 @@
       <c r="B360" s="12" t="n"/>
       <c r="C360" s="12" t="n"/>
       <c r="D360" s="12" t="n"/>
-      <c r="E360" s="38" t="n"/>
+      <c r="E360" s="41" t="n"/>
       <c r="F360" s="16" t="n"/>
-      <c r="G360" s="36">
+      <c r="G360" s="39">
         <f>IF(OR(E360="",F360=""),"",ROUND(E360*F360,2))</f>
         <v/>
       </c>
@@ -7104,9 +7160,9 @@
       <c r="B361" s="12" t="n"/>
       <c r="C361" s="12" t="n"/>
       <c r="D361" s="12" t="n"/>
-      <c r="E361" s="38" t="n"/>
+      <c r="E361" s="41" t="n"/>
       <c r="F361" s="16" t="n"/>
-      <c r="G361" s="36">
+      <c r="G361" s="39">
         <f>IF(OR(E361="",F361=""),"",ROUND(E361*F361,2))</f>
         <v/>
       </c>
@@ -7118,9 +7174,9 @@
       <c r="B362" s="12" t="n"/>
       <c r="C362" s="12" t="n"/>
       <c r="D362" s="12" t="n"/>
-      <c r="E362" s="38" t="n"/>
+      <c r="E362" s="41" t="n"/>
       <c r="F362" s="16" t="n"/>
-      <c r="G362" s="36">
+      <c r="G362" s="39">
         <f>IF(OR(E362="",F362=""),"",ROUND(E362*F362,2))</f>
         <v/>
       </c>
@@ -7132,9 +7188,9 @@
       <c r="B363" s="12" t="n"/>
       <c r="C363" s="12" t="n"/>
       <c r="D363" s="12" t="n"/>
-      <c r="E363" s="38" t="n"/>
+      <c r="E363" s="41" t="n"/>
       <c r="F363" s="16" t="n"/>
-      <c r="G363" s="36">
+      <c r="G363" s="39">
         <f>IF(OR(E363="",F363=""),"",ROUND(E363*F363,2))</f>
         <v/>
       </c>
@@ -7146,9 +7202,9 @@
       <c r="B364" s="12" t="n"/>
       <c r="C364" s="12" t="n"/>
       <c r="D364" s="12" t="n"/>
-      <c r="E364" s="38" t="n"/>
+      <c r="E364" s="41" t="n"/>
       <c r="F364" s="16" t="n"/>
-      <c r="G364" s="36">
+      <c r="G364" s="39">
         <f>IF(OR(E364="",F364=""),"",ROUND(E364*F364,2))</f>
         <v/>
       </c>
@@ -7160,9 +7216,9 @@
       <c r="B365" s="12" t="n"/>
       <c r="C365" s="12" t="n"/>
       <c r="D365" s="12" t="n"/>
-      <c r="E365" s="38" t="n"/>
+      <c r="E365" s="41" t="n"/>
       <c r="F365" s="16" t="n"/>
-      <c r="G365" s="36">
+      <c r="G365" s="39">
         <f>IF(OR(E365="",F365=""),"",ROUND(E365*F365,2))</f>
         <v/>
       </c>
@@ -7174,9 +7230,9 @@
       <c r="B366" s="12" t="n"/>
       <c r="C366" s="12" t="n"/>
       <c r="D366" s="12" t="n"/>
-      <c r="E366" s="38" t="n"/>
+      <c r="E366" s="41" t="n"/>
       <c r="F366" s="16" t="n"/>
-      <c r="G366" s="36">
+      <c r="G366" s="39">
         <f>IF(OR(E366="",F366=""),"",ROUND(E366*F366,2))</f>
         <v/>
       </c>
@@ -7188,9 +7244,9 @@
       <c r="B367" s="12" t="n"/>
       <c r="C367" s="12" t="n"/>
       <c r="D367" s="12" t="n"/>
-      <c r="E367" s="38" t="n"/>
+      <c r="E367" s="41" t="n"/>
       <c r="F367" s="16" t="n"/>
-      <c r="G367" s="36">
+      <c r="G367" s="39">
         <f>IF(OR(E367="",F367=""),"",ROUND(E367*F367,2))</f>
         <v/>
       </c>
@@ -7202,9 +7258,9 @@
       <c r="B368" s="12" t="n"/>
       <c r="C368" s="12" t="n"/>
       <c r="D368" s="12" t="n"/>
-      <c r="E368" s="38" t="n"/>
+      <c r="E368" s="41" t="n"/>
       <c r="F368" s="16" t="n"/>
-      <c r="G368" s="36">
+      <c r="G368" s="39">
         <f>IF(OR(E368="",F368=""),"",ROUND(E368*F368,2))</f>
         <v/>
       </c>
@@ -7216,9 +7272,9 @@
       <c r="B369" s="12" t="n"/>
       <c r="C369" s="12" t="n"/>
       <c r="D369" s="12" t="n"/>
-      <c r="E369" s="38" t="n"/>
+      <c r="E369" s="41" t="n"/>
       <c r="F369" s="16" t="n"/>
-      <c r="G369" s="36">
+      <c r="G369" s="39">
         <f>IF(OR(E369="",F369=""),"",ROUND(E369*F369,2))</f>
         <v/>
       </c>
@@ -7230,9 +7286,9 @@
       <c r="B370" s="12" t="n"/>
       <c r="C370" s="12" t="n"/>
       <c r="D370" s="12" t="n"/>
-      <c r="E370" s="38" t="n"/>
+      <c r="E370" s="41" t="n"/>
       <c r="F370" s="16" t="n"/>
-      <c r="G370" s="36">
+      <c r="G370" s="39">
         <f>IF(OR(E370="",F370=""),"",ROUND(E370*F370,2))</f>
         <v/>
       </c>
@@ -7244,9 +7300,9 @@
       <c r="B371" s="12" t="n"/>
       <c r="C371" s="12" t="n"/>
       <c r="D371" s="12" t="n"/>
-      <c r="E371" s="38" t="n"/>
+      <c r="E371" s="41" t="n"/>
       <c r="F371" s="16" t="n"/>
-      <c r="G371" s="36">
+      <c r="G371" s="39">
         <f>IF(OR(E371="",F371=""),"",ROUND(E371*F371,2))</f>
         <v/>
       </c>
@@ -7258,9 +7314,9 @@
       <c r="B372" s="12" t="n"/>
       <c r="C372" s="12" t="n"/>
       <c r="D372" s="12" t="n"/>
-      <c r="E372" s="38" t="n"/>
+      <c r="E372" s="41" t="n"/>
       <c r="F372" s="16" t="n"/>
-      <c r="G372" s="36">
+      <c r="G372" s="39">
         <f>IF(OR(E372="",F372=""),"",ROUND(E372*F372,2))</f>
         <v/>
       </c>
@@ -7272,9 +7328,9 @@
       <c r="B373" s="12" t="n"/>
       <c r="C373" s="12" t="n"/>
       <c r="D373" s="12" t="n"/>
-      <c r="E373" s="38" t="n"/>
+      <c r="E373" s="41" t="n"/>
       <c r="F373" s="16" t="n"/>
-      <c r="G373" s="36">
+      <c r="G373" s="39">
         <f>IF(OR(E373="",F373=""),"",ROUND(E373*F373,2))</f>
         <v/>
       </c>
@@ -7286,9 +7342,9 @@
       <c r="B374" s="12" t="n"/>
       <c r="C374" s="12" t="n"/>
       <c r="D374" s="12" t="n"/>
-      <c r="E374" s="38" t="n"/>
+      <c r="E374" s="41" t="n"/>
       <c r="F374" s="16" t="n"/>
-      <c r="G374" s="36">
+      <c r="G374" s="39">
         <f>IF(OR(E374="",F374=""),"",ROUND(E374*F374,2))</f>
         <v/>
       </c>
@@ -7300,9 +7356,9 @@
       <c r="B375" s="12" t="n"/>
       <c r="C375" s="12" t="n"/>
       <c r="D375" s="12" t="n"/>
-      <c r="E375" s="38" t="n"/>
+      <c r="E375" s="41" t="n"/>
       <c r="F375" s="16" t="n"/>
-      <c r="G375" s="36">
+      <c r="G375" s="39">
         <f>IF(OR(E375="",F375=""),"",ROUND(E375*F375,2))</f>
         <v/>
       </c>
@@ -7314,9 +7370,9 @@
       <c r="B376" s="12" t="n"/>
       <c r="C376" s="12" t="n"/>
       <c r="D376" s="12" t="n"/>
-      <c r="E376" s="38" t="n"/>
+      <c r="E376" s="41" t="n"/>
       <c r="F376" s="16" t="n"/>
-      <c r="G376" s="36">
+      <c r="G376" s="39">
         <f>IF(OR(E376="",F376=""),"",ROUND(E376*F376,2))</f>
         <v/>
       </c>
@@ -7328,9 +7384,9 @@
       <c r="B377" s="12" t="n"/>
       <c r="C377" s="12" t="n"/>
       <c r="D377" s="12" t="n"/>
-      <c r="E377" s="38" t="n"/>
+      <c r="E377" s="41" t="n"/>
       <c r="F377" s="16" t="n"/>
-      <c r="G377" s="36">
+      <c r="G377" s="39">
         <f>IF(OR(E377="",F377=""),"",ROUND(E377*F377,2))</f>
         <v/>
       </c>
@@ -7342,9 +7398,9 @@
       <c r="B378" s="12" t="n"/>
       <c r="C378" s="12" t="n"/>
       <c r="D378" s="12" t="n"/>
-      <c r="E378" s="38" t="n"/>
+      <c r="E378" s="41" t="n"/>
       <c r="F378" s="16" t="n"/>
-      <c r="G378" s="36">
+      <c r="G378" s="39">
         <f>IF(OR(E378="",F378=""),"",ROUND(E378*F378,2))</f>
         <v/>
       </c>
@@ -7356,9 +7412,9 @@
       <c r="B379" s="12" t="n"/>
       <c r="C379" s="12" t="n"/>
       <c r="D379" s="12" t="n"/>
-      <c r="E379" s="38" t="n"/>
+      <c r="E379" s="41" t="n"/>
       <c r="F379" s="16" t="n"/>
-      <c r="G379" s="36">
+      <c r="G379" s="39">
         <f>IF(OR(E379="",F379=""),"",ROUND(E379*F379,2))</f>
         <v/>
       </c>
@@ -7370,9 +7426,9 @@
       <c r="B380" s="12" t="n"/>
       <c r="C380" s="12" t="n"/>
       <c r="D380" s="12" t="n"/>
-      <c r="E380" s="38" t="n"/>
+      <c r="E380" s="41" t="n"/>
       <c r="F380" s="16" t="n"/>
-      <c r="G380" s="36">
+      <c r="G380" s="39">
         <f>IF(OR(E380="",F380=""),"",ROUND(E380*F380,2))</f>
         <v/>
       </c>
@@ -7384,9 +7440,9 @@
       <c r="B381" s="12" t="n"/>
       <c r="C381" s="12" t="n"/>
       <c r="D381" s="12" t="n"/>
-      <c r="E381" s="38" t="n"/>
+      <c r="E381" s="41" t="n"/>
       <c r="F381" s="16" t="n"/>
-      <c r="G381" s="36">
+      <c r="G381" s="39">
         <f>IF(OR(E381="",F381=""),"",ROUND(E381*F381,2))</f>
         <v/>
       </c>
@@ -7398,9 +7454,9 @@
       <c r="B382" s="12" t="n"/>
       <c r="C382" s="12" t="n"/>
       <c r="D382" s="12" t="n"/>
-      <c r="E382" s="38" t="n"/>
+      <c r="E382" s="41" t="n"/>
       <c r="F382" s="16" t="n"/>
-      <c r="G382" s="36">
+      <c r="G382" s="39">
         <f>IF(OR(E382="",F382=""),"",ROUND(E382*F382,2))</f>
         <v/>
       </c>
@@ -7412,9 +7468,9 @@
       <c r="B383" s="12" t="n"/>
       <c r="C383" s="12" t="n"/>
       <c r="D383" s="12" t="n"/>
-      <c r="E383" s="38" t="n"/>
+      <c r="E383" s="41" t="n"/>
       <c r="F383" s="16" t="n"/>
-      <c r="G383" s="36">
+      <c r="G383" s="39">
         <f>IF(OR(E383="",F383=""),"",ROUND(E383*F383,2))</f>
         <v/>
       </c>
@@ -7426,9 +7482,9 @@
       <c r="B384" s="12" t="n"/>
       <c r="C384" s="12" t="n"/>
       <c r="D384" s="12" t="n"/>
-      <c r="E384" s="38" t="n"/>
+      <c r="E384" s="41" t="n"/>
       <c r="F384" s="16" t="n"/>
-      <c r="G384" s="36">
+      <c r="G384" s="39">
         <f>IF(OR(E384="",F384=""),"",ROUND(E384*F384,2))</f>
         <v/>
       </c>
@@ -7440,9 +7496,9 @@
       <c r="B385" s="12" t="n"/>
       <c r="C385" s="12" t="n"/>
       <c r="D385" s="12" t="n"/>
-      <c r="E385" s="38" t="n"/>
+      <c r="E385" s="41" t="n"/>
       <c r="F385" s="16" t="n"/>
-      <c r="G385" s="36">
+      <c r="G385" s="39">
         <f>IF(OR(E385="",F385=""),"",ROUND(E385*F385,2))</f>
         <v/>
       </c>
@@ -7454,9 +7510,9 @@
       <c r="B386" s="12" t="n"/>
       <c r="C386" s="12" t="n"/>
       <c r="D386" s="12" t="n"/>
-      <c r="E386" s="38" t="n"/>
+      <c r="E386" s="41" t="n"/>
       <c r="F386" s="16" t="n"/>
-      <c r="G386" s="36">
+      <c r="G386" s="39">
         <f>IF(OR(E386="",F386=""),"",ROUND(E386*F386,2))</f>
         <v/>
       </c>
@@ -7468,9 +7524,9 @@
       <c r="B387" s="12" t="n"/>
       <c r="C387" s="12" t="n"/>
       <c r="D387" s="12" t="n"/>
-      <c r="E387" s="38" t="n"/>
+      <c r="E387" s="41" t="n"/>
       <c r="F387" s="16" t="n"/>
-      <c r="G387" s="36">
+      <c r="G387" s="39">
         <f>IF(OR(E387="",F387=""),"",ROUND(E387*F387,2))</f>
         <v/>
       </c>
@@ -7482,9 +7538,9 @@
       <c r="B388" s="12" t="n"/>
       <c r="C388" s="12" t="n"/>
       <c r="D388" s="12" t="n"/>
-      <c r="E388" s="38" t="n"/>
+      <c r="E388" s="41" t="n"/>
       <c r="F388" s="16" t="n"/>
-      <c r="G388" s="36">
+      <c r="G388" s="39">
         <f>IF(OR(E388="",F388=""),"",ROUND(E388*F388,2))</f>
         <v/>
       </c>
@@ -7496,9 +7552,9 @@
       <c r="B389" s="12" t="n"/>
       <c r="C389" s="12" t="n"/>
       <c r="D389" s="12" t="n"/>
-      <c r="E389" s="38" t="n"/>
+      <c r="E389" s="41" t="n"/>
       <c r="F389" s="16" t="n"/>
-      <c r="G389" s="36">
+      <c r="G389" s="39">
         <f>IF(OR(E389="",F389=""),"",ROUND(E389*F389,2))</f>
         <v/>
       </c>
@@ -7510,9 +7566,9 @@
       <c r="B390" s="12" t="n"/>
       <c r="C390" s="12" t="n"/>
       <c r="D390" s="12" t="n"/>
-      <c r="E390" s="38" t="n"/>
+      <c r="E390" s="41" t="n"/>
       <c r="F390" s="16" t="n"/>
-      <c r="G390" s="36">
+      <c r="G390" s="39">
         <f>IF(OR(E390="",F390=""),"",ROUND(E390*F390,2))</f>
         <v/>
       </c>
@@ -7524,9 +7580,9 @@
       <c r="B391" s="12" t="n"/>
       <c r="C391" s="12" t="n"/>
       <c r="D391" s="12" t="n"/>
-      <c r="E391" s="38" t="n"/>
+      <c r="E391" s="41" t="n"/>
       <c r="F391" s="16" t="n"/>
-      <c r="G391" s="36">
+      <c r="G391" s="39">
         <f>IF(OR(E391="",F391=""),"",ROUND(E391*F391,2))</f>
         <v/>
       </c>
@@ -7538,9 +7594,9 @@
       <c r="B392" s="12" t="n"/>
       <c r="C392" s="12" t="n"/>
       <c r="D392" s="12" t="n"/>
-      <c r="E392" s="38" t="n"/>
+      <c r="E392" s="41" t="n"/>
       <c r="F392" s="16" t="n"/>
-      <c r="G392" s="36">
+      <c r="G392" s="39">
         <f>IF(OR(E392="",F392=""),"",ROUND(E392*F392,2))</f>
         <v/>
       </c>
@@ -7552,9 +7608,9 @@
       <c r="B393" s="12" t="n"/>
       <c r="C393" s="12" t="n"/>
       <c r="D393" s="12" t="n"/>
-      <c r="E393" s="38" t="n"/>
+      <c r="E393" s="41" t="n"/>
       <c r="F393" s="16" t="n"/>
-      <c r="G393" s="36">
+      <c r="G393" s="39">
         <f>IF(OR(E393="",F393=""),"",ROUND(E393*F393,2))</f>
         <v/>
       </c>
@@ -7566,9 +7622,9 @@
       <c r="B394" s="12" t="n"/>
       <c r="C394" s="12" t="n"/>
       <c r="D394" s="12" t="n"/>
-      <c r="E394" s="38" t="n"/>
+      <c r="E394" s="41" t="n"/>
       <c r="F394" s="16" t="n"/>
-      <c r="G394" s="36">
+      <c r="G394" s="39">
         <f>IF(OR(E394="",F394=""),"",ROUND(E394*F394,2))</f>
         <v/>
       </c>
@@ -7580,9 +7636,9 @@
       <c r="B395" s="12" t="n"/>
       <c r="C395" s="12" t="n"/>
       <c r="D395" s="12" t="n"/>
-      <c r="E395" s="38" t="n"/>
+      <c r="E395" s="41" t="n"/>
       <c r="F395" s="16" t="n"/>
-      <c r="G395" s="36">
+      <c r="G395" s="39">
         <f>IF(OR(E395="",F395=""),"",ROUND(E395*F395,2))</f>
         <v/>
       </c>
@@ -7594,9 +7650,9 @@
       <c r="B396" s="12" t="n"/>
       <c r="C396" s="12" t="n"/>
       <c r="D396" s="12" t="n"/>
-      <c r="E396" s="38" t="n"/>
+      <c r="E396" s="41" t="n"/>
       <c r="F396" s="16" t="n"/>
-      <c r="G396" s="36">
+      <c r="G396" s="39">
         <f>IF(OR(E396="",F396=""),"",ROUND(E396*F396,2))</f>
         <v/>
       </c>
@@ -7608,9 +7664,9 @@
       <c r="B397" s="12" t="n"/>
       <c r="C397" s="12" t="n"/>
       <c r="D397" s="12" t="n"/>
-      <c r="E397" s="38" t="n"/>
+      <c r="E397" s="41" t="n"/>
       <c r="F397" s="16" t="n"/>
-      <c r="G397" s="36">
+      <c r="G397" s="39">
         <f>IF(OR(E397="",F397=""),"",ROUND(E397*F397,2))</f>
         <v/>
       </c>
@@ -7622,9 +7678,9 @@
       <c r="B398" s="12" t="n"/>
       <c r="C398" s="12" t="n"/>
       <c r="D398" s="12" t="n"/>
-      <c r="E398" s="38" t="n"/>
+      <c r="E398" s="41" t="n"/>
       <c r="F398" s="16" t="n"/>
-      <c r="G398" s="36">
+      <c r="G398" s="39">
         <f>IF(OR(E398="",F398=""),"",ROUND(E398*F398,2))</f>
         <v/>
       </c>
@@ -7636,9 +7692,9 @@
       <c r="B399" s="12" t="n"/>
       <c r="C399" s="12" t="n"/>
       <c r="D399" s="12" t="n"/>
-      <c r="E399" s="38" t="n"/>
+      <c r="E399" s="41" t="n"/>
       <c r="F399" s="16" t="n"/>
-      <c r="G399" s="36">
+      <c r="G399" s="39">
         <f>IF(OR(E399="",F399=""),"",ROUND(E399*F399,2))</f>
         <v/>
       </c>
@@ -7650,9 +7706,9 @@
       <c r="B400" s="12" t="n"/>
       <c r="C400" s="12" t="n"/>
       <c r="D400" s="12" t="n"/>
-      <c r="E400" s="38" t="n"/>
+      <c r="E400" s="41" t="n"/>
       <c r="F400" s="16" t="n"/>
-      <c r="G400" s="36">
+      <c r="G400" s="39">
         <f>IF(OR(E400="",F400=""),"",ROUND(E400*F400,2))</f>
         <v/>
       </c>
@@ -7664,9 +7720,9 @@
       <c r="B401" s="12" t="n"/>
       <c r="C401" s="12" t="n"/>
       <c r="D401" s="12" t="n"/>
-      <c r="E401" s="38" t="n"/>
+      <c r="E401" s="41" t="n"/>
       <c r="F401" s="16" t="n"/>
-      <c r="G401" s="36">
+      <c r="G401" s="39">
         <f>IF(OR(E401="",F401=""),"",ROUND(E401*F401,2))</f>
         <v/>
       </c>
@@ -7678,9 +7734,9 @@
       <c r="B402" s="12" t="n"/>
       <c r="C402" s="12" t="n"/>
       <c r="D402" s="12" t="n"/>
-      <c r="E402" s="38" t="n"/>
+      <c r="E402" s="41" t="n"/>
       <c r="F402" s="16" t="n"/>
-      <c r="G402" s="36">
+      <c r="G402" s="39">
         <f>IF(OR(E402="",F402=""),"",ROUND(E402*F402,2))</f>
         <v/>
       </c>
@@ -7692,9 +7748,9 @@
       <c r="B403" s="12" t="n"/>
       <c r="C403" s="12" t="n"/>
       <c r="D403" s="12" t="n"/>
-      <c r="E403" s="38" t="n"/>
+      <c r="E403" s="41" t="n"/>
       <c r="F403" s="16" t="n"/>
-      <c r="G403" s="36">
+      <c r="G403" s="39">
         <f>IF(OR(E403="",F403=""),"",ROUND(E403*F403,2))</f>
         <v/>
       </c>
@@ -7706,9 +7762,9 @@
       <c r="B404" s="12" t="n"/>
       <c r="C404" s="12" t="n"/>
       <c r="D404" s="12" t="n"/>
-      <c r="E404" s="38" t="n"/>
+      <c r="E404" s="41" t="n"/>
       <c r="F404" s="16" t="n"/>
-      <c r="G404" s="36">
+      <c r="G404" s="39">
         <f>IF(OR(E404="",F404=""),"",ROUND(E404*F404,2))</f>
         <v/>
       </c>
@@ -7720,9 +7776,9 @@
       <c r="B405" s="12" t="n"/>
       <c r="C405" s="12" t="n"/>
       <c r="D405" s="12" t="n"/>
-      <c r="E405" s="38" t="n"/>
+      <c r="E405" s="41" t="n"/>
       <c r="F405" s="16" t="n"/>
-      <c r="G405" s="36">
+      <c r="G405" s="39">
         <f>IF(OR(E405="",F405=""),"",ROUND(E405*F405,2))</f>
         <v/>
       </c>
@@ -7734,9 +7790,9 @@
       <c r="B406" s="12" t="n"/>
       <c r="C406" s="12" t="n"/>
       <c r="D406" s="12" t="n"/>
-      <c r="E406" s="38" t="n"/>
+      <c r="E406" s="41" t="n"/>
       <c r="F406" s="16" t="n"/>
-      <c r="G406" s="36">
+      <c r="G406" s="39">
         <f>IF(OR(E406="",F406=""),"",ROUND(E406*F406,2))</f>
         <v/>
       </c>
@@ -7748,9 +7804,9 @@
       <c r="B407" s="12" t="n"/>
       <c r="C407" s="12" t="n"/>
       <c r="D407" s="12" t="n"/>
-      <c r="E407" s="38" t="n"/>
+      <c r="E407" s="41" t="n"/>
       <c r="F407" s="16" t="n"/>
-      <c r="G407" s="36">
+      <c r="G407" s="39">
         <f>IF(OR(E407="",F407=""),"",ROUND(E407*F407,2))</f>
         <v/>
       </c>
@@ -7762,9 +7818,9 @@
       <c r="B408" s="12" t="n"/>
       <c r="C408" s="12" t="n"/>
       <c r="D408" s="12" t="n"/>
-      <c r="E408" s="38" t="n"/>
+      <c r="E408" s="41" t="n"/>
       <c r="F408" s="16" t="n"/>
-      <c r="G408" s="36">
+      <c r="G408" s="39">
         <f>IF(OR(E408="",F408=""),"",ROUND(E408*F408,2))</f>
         <v/>
       </c>
@@ -7776,9 +7832,9 @@
       <c r="B409" s="12" t="n"/>
       <c r="C409" s="12" t="n"/>
       <c r="D409" s="12" t="n"/>
-      <c r="E409" s="38" t="n"/>
+      <c r="E409" s="41" t="n"/>
       <c r="F409" s="16" t="n"/>
-      <c r="G409" s="36">
+      <c r="G409" s="39">
         <f>IF(OR(E409="",F409=""),"",ROUND(E409*F409,2))</f>
         <v/>
       </c>
@@ -7790,9 +7846,9 @@
       <c r="B410" s="12" t="n"/>
       <c r="C410" s="12" t="n"/>
       <c r="D410" s="12" t="n"/>
-      <c r="E410" s="38" t="n"/>
+      <c r="E410" s="41" t="n"/>
       <c r="F410" s="16" t="n"/>
-      <c r="G410" s="36">
+      <c r="G410" s="39">
         <f>IF(OR(E410="",F410=""),"",ROUND(E410*F410,2))</f>
         <v/>
       </c>
@@ -7804,9 +7860,9 @@
       <c r="B411" s="12" t="n"/>
       <c r="C411" s="12" t="n"/>
       <c r="D411" s="12" t="n"/>
-      <c r="E411" s="38" t="n"/>
+      <c r="E411" s="41" t="n"/>
       <c r="F411" s="16" t="n"/>
-      <c r="G411" s="36">
+      <c r="G411" s="39">
         <f>IF(OR(E411="",F411=""),"",ROUND(E411*F411,2))</f>
         <v/>
       </c>
@@ -7818,9 +7874,9 @@
       <c r="B412" s="12" t="n"/>
       <c r="C412" s="12" t="n"/>
       <c r="D412" s="12" t="n"/>
-      <c r="E412" s="38" t="n"/>
+      <c r="E412" s="41" t="n"/>
       <c r="F412" s="16" t="n"/>
-      <c r="G412" s="36">
+      <c r="G412" s="39">
         <f>IF(OR(E412="",F412=""),"",ROUND(E412*F412,2))</f>
         <v/>
       </c>
@@ -7832,9 +7888,9 @@
       <c r="B413" s="12" t="n"/>
       <c r="C413" s="12" t="n"/>
       <c r="D413" s="12" t="n"/>
-      <c r="E413" s="38" t="n"/>
+      <c r="E413" s="41" t="n"/>
       <c r="F413" s="16" t="n"/>
-      <c r="G413" s="36">
+      <c r="G413" s="39">
         <f>IF(OR(E413="",F413=""),"",ROUND(E413*F413,2))</f>
         <v/>
       </c>
@@ -7846,9 +7902,9 @@
       <c r="B414" s="12" t="n"/>
       <c r="C414" s="12" t="n"/>
       <c r="D414" s="12" t="n"/>
-      <c r="E414" s="38" t="n"/>
+      <c r="E414" s="41" t="n"/>
       <c r="F414" s="16" t="n"/>
-      <c r="G414" s="36">
+      <c r="G414" s="39">
         <f>IF(OR(E414="",F414=""),"",ROUND(E414*F414,2))</f>
         <v/>
       </c>
@@ -7860,9 +7916,9 @@
       <c r="B415" s="12" t="n"/>
       <c r="C415" s="12" t="n"/>
       <c r="D415" s="12" t="n"/>
-      <c r="E415" s="38" t="n"/>
+      <c r="E415" s="41" t="n"/>
       <c r="F415" s="16" t="n"/>
-      <c r="G415" s="36">
+      <c r="G415" s="39">
         <f>IF(OR(E415="",F415=""),"",ROUND(E415*F415,2))</f>
         <v/>
       </c>
@@ -7874,9 +7930,9 @@
       <c r="B416" s="12" t="n"/>
       <c r="C416" s="12" t="n"/>
       <c r="D416" s="12" t="n"/>
-      <c r="E416" s="38" t="n"/>
+      <c r="E416" s="41" t="n"/>
       <c r="F416" s="16" t="n"/>
-      <c r="G416" s="36">
+      <c r="G416" s="39">
         <f>IF(OR(E416="",F416=""),"",ROUND(E416*F416,2))</f>
         <v/>
       </c>
@@ -7888,9 +7944,9 @@
       <c r="B417" s="12" t="n"/>
       <c r="C417" s="12" t="n"/>
       <c r="D417" s="12" t="n"/>
-      <c r="E417" s="38" t="n"/>
+      <c r="E417" s="41" t="n"/>
       <c r="F417" s="16" t="n"/>
-      <c r="G417" s="36">
+      <c r="G417" s="39">
         <f>IF(OR(E417="",F417=""),"",ROUND(E417*F417,2))</f>
         <v/>
       </c>
@@ -7902,9 +7958,9 @@
       <c r="B418" s="12" t="n"/>
       <c r="C418" s="12" t="n"/>
       <c r="D418" s="12" t="n"/>
-      <c r="E418" s="38" t="n"/>
+      <c r="E418" s="41" t="n"/>
       <c r="F418" s="16" t="n"/>
-      <c r="G418" s="36">
+      <c r="G418" s="39">
         <f>IF(OR(E418="",F418=""),"",ROUND(E418*F418,2))</f>
         <v/>
       </c>
@@ -7916,9 +7972,9 @@
       <c r="B419" s="12" t="n"/>
       <c r="C419" s="12" t="n"/>
       <c r="D419" s="12" t="n"/>
-      <c r="E419" s="38" t="n"/>
+      <c r="E419" s="41" t="n"/>
       <c r="F419" s="16" t="n"/>
-      <c r="G419" s="36">
+      <c r="G419" s="39">
         <f>IF(OR(E419="",F419=""),"",ROUND(E419*F419,2))</f>
         <v/>
       </c>
@@ -7930,9 +7986,9 @@
       <c r="B420" s="12" t="n"/>
       <c r="C420" s="12" t="n"/>
       <c r="D420" s="12" t="n"/>
-      <c r="E420" s="38" t="n"/>
+      <c r="E420" s="41" t="n"/>
       <c r="F420" s="16" t="n"/>
-      <c r="G420" s="36">
+      <c r="G420" s="39">
         <f>IF(OR(E420="",F420=""),"",ROUND(E420*F420,2))</f>
         <v/>
       </c>
@@ -7944,9 +8000,9 @@
       <c r="B421" s="12" t="n"/>
       <c r="C421" s="12" t="n"/>
       <c r="D421" s="12" t="n"/>
-      <c r="E421" s="38" t="n"/>
+      <c r="E421" s="41" t="n"/>
       <c r="F421" s="16" t="n"/>
-      <c r="G421" s="36">
+      <c r="G421" s="39">
         <f>IF(OR(E421="",F421=""),"",ROUND(E421*F421,2))</f>
         <v/>
       </c>
@@ -7958,9 +8014,9 @@
       <c r="B422" s="12" t="n"/>
       <c r="C422" s="12" t="n"/>
       <c r="D422" s="12" t="n"/>
-      <c r="E422" s="38" t="n"/>
+      <c r="E422" s="41" t="n"/>
       <c r="F422" s="16" t="n"/>
-      <c r="G422" s="36">
+      <c r="G422" s="39">
         <f>IF(OR(E422="",F422=""),"",ROUND(E422*F422,2))</f>
         <v/>
       </c>
@@ -7972,9 +8028,9 @@
       <c r="B423" s="12" t="n"/>
       <c r="C423" s="12" t="n"/>
       <c r="D423" s="12" t="n"/>
-      <c r="E423" s="38" t="n"/>
+      <c r="E423" s="41" t="n"/>
       <c r="F423" s="16" t="n"/>
-      <c r="G423" s="36">
+      <c r="G423" s="39">
         <f>IF(OR(E423="",F423=""),"",ROUND(E423*F423,2))</f>
         <v/>
       </c>
@@ -7986,9 +8042,9 @@
       <c r="B424" s="12" t="n"/>
       <c r="C424" s="12" t="n"/>
       <c r="D424" s="12" t="n"/>
-      <c r="E424" s="38" t="n"/>
+      <c r="E424" s="41" t="n"/>
       <c r="F424" s="16" t="n"/>
-      <c r="G424" s="36">
+      <c r="G424" s="39">
         <f>IF(OR(E424="",F424=""),"",ROUND(E424*F424,2))</f>
         <v/>
       </c>
@@ -8000,9 +8056,9 @@
       <c r="B425" s="12" t="n"/>
       <c r="C425" s="12" t="n"/>
       <c r="D425" s="12" t="n"/>
-      <c r="E425" s="38" t="n"/>
+      <c r="E425" s="41" t="n"/>
       <c r="F425" s="16" t="n"/>
-      <c r="G425" s="36">
+      <c r="G425" s="39">
         <f>IF(OR(E425="",F425=""),"",ROUND(E425*F425,2))</f>
         <v/>
       </c>
@@ -8014,9 +8070,9 @@
       <c r="B426" s="12" t="n"/>
       <c r="C426" s="12" t="n"/>
       <c r="D426" s="12" t="n"/>
-      <c r="E426" s="38" t="n"/>
+      <c r="E426" s="41" t="n"/>
       <c r="F426" s="16" t="n"/>
-      <c r="G426" s="36">
+      <c r="G426" s="39">
         <f>IF(OR(E426="",F426=""),"",ROUND(E426*F426,2))</f>
         <v/>
       </c>
@@ -8028,9 +8084,9 @@
       <c r="B427" s="12" t="n"/>
       <c r="C427" s="12" t="n"/>
       <c r="D427" s="12" t="n"/>
-      <c r="E427" s="38" t="n"/>
+      <c r="E427" s="41" t="n"/>
       <c r="F427" s="16" t="n"/>
-      <c r="G427" s="36">
+      <c r="G427" s="39">
         <f>IF(OR(E427="",F427=""),"",ROUND(E427*F427,2))</f>
         <v/>
       </c>
@@ -8042,9 +8098,9 @@
       <c r="B428" s="12" t="n"/>
       <c r="C428" s="12" t="n"/>
       <c r="D428" s="12" t="n"/>
-      <c r="E428" s="38" t="n"/>
+      <c r="E428" s="41" t="n"/>
       <c r="F428" s="16" t="n"/>
-      <c r="G428" s="36">
+      <c r="G428" s="39">
         <f>IF(OR(E428="",F428=""),"",ROUND(E428*F428,2))</f>
         <v/>
       </c>
@@ -8056,9 +8112,9 @@
       <c r="B429" s="12" t="n"/>
       <c r="C429" s="12" t="n"/>
       <c r="D429" s="12" t="n"/>
-      <c r="E429" s="38" t="n"/>
+      <c r="E429" s="41" t="n"/>
       <c r="F429" s="16" t="n"/>
-      <c r="G429" s="36">
+      <c r="G429" s="39">
         <f>IF(OR(E429="",F429=""),"",ROUND(E429*F429,2))</f>
         <v/>
       </c>
@@ -8070,9 +8126,9 @@
       <c r="B430" s="12" t="n"/>
       <c r="C430" s="12" t="n"/>
       <c r="D430" s="12" t="n"/>
-      <c r="E430" s="38" t="n"/>
+      <c r="E430" s="41" t="n"/>
       <c r="F430" s="16" t="n"/>
-      <c r="G430" s="36">
+      <c r="G430" s="39">
         <f>IF(OR(E430="",F430=""),"",ROUND(E430*F430,2))</f>
         <v/>
       </c>
@@ -8084,9 +8140,9 @@
       <c r="B431" s="12" t="n"/>
       <c r="C431" s="12" t="n"/>
       <c r="D431" s="12" t="n"/>
-      <c r="E431" s="38" t="n"/>
+      <c r="E431" s="41" t="n"/>
       <c r="F431" s="16" t="n"/>
-      <c r="G431" s="36">
+      <c r="G431" s="39">
         <f>IF(OR(E431="",F431=""),"",ROUND(E431*F431,2))</f>
         <v/>
       </c>
@@ -8098,9 +8154,9 @@
       <c r="B432" s="12" t="n"/>
       <c r="C432" s="12" t="n"/>
       <c r="D432" s="12" t="n"/>
-      <c r="E432" s="38" t="n"/>
+      <c r="E432" s="41" t="n"/>
       <c r="F432" s="16" t="n"/>
-      <c r="G432" s="36">
+      <c r="G432" s="39">
         <f>IF(OR(E432="",F432=""),"",ROUND(E432*F432,2))</f>
         <v/>
       </c>
@@ -8112,9 +8168,9 @@
       <c r="B433" s="12" t="n"/>
       <c r="C433" s="12" t="n"/>
       <c r="D433" s="12" t="n"/>
-      <c r="E433" s="38" t="n"/>
+      <c r="E433" s="41" t="n"/>
       <c r="F433" s="16" t="n"/>
-      <c r="G433" s="36">
+      <c r="G433" s="39">
         <f>IF(OR(E433="",F433=""),"",ROUND(E433*F433,2))</f>
         <v/>
       </c>
@@ -8126,9 +8182,9 @@
       <c r="B434" s="12" t="n"/>
       <c r="C434" s="12" t="n"/>
       <c r="D434" s="12" t="n"/>
-      <c r="E434" s="38" t="n"/>
+      <c r="E434" s="41" t="n"/>
       <c r="F434" s="16" t="n"/>
-      <c r="G434" s="36">
+      <c r="G434" s="39">
         <f>IF(OR(E434="",F434=""),"",ROUND(E434*F434,2))</f>
         <v/>
       </c>
@@ -8140,9 +8196,9 @@
       <c r="B435" s="12" t="n"/>
       <c r="C435" s="12" t="n"/>
       <c r="D435" s="12" t="n"/>
-      <c r="E435" s="38" t="n"/>
+      <c r="E435" s="41" t="n"/>
       <c r="F435" s="16" t="n"/>
-      <c r="G435" s="36">
+      <c r="G435" s="39">
         <f>IF(OR(E435="",F435=""),"",ROUND(E435*F435,2))</f>
         <v/>
       </c>
@@ -8154,9 +8210,9 @@
       <c r="B436" s="12" t="n"/>
       <c r="C436" s="12" t="n"/>
       <c r="D436" s="12" t="n"/>
-      <c r="E436" s="38" t="n"/>
+      <c r="E436" s="41" t="n"/>
       <c r="F436" s="16" t="n"/>
-      <c r="G436" s="36">
+      <c r="G436" s="39">
         <f>IF(OR(E436="",F436=""),"",ROUND(E436*F436,2))</f>
         <v/>
       </c>
@@ -8168,9 +8224,9 @@
       <c r="B437" s="12" t="n"/>
       <c r="C437" s="12" t="n"/>
       <c r="D437" s="12" t="n"/>
-      <c r="E437" s="38" t="n"/>
+      <c r="E437" s="41" t="n"/>
       <c r="F437" s="16" t="n"/>
-      <c r="G437" s="36">
+      <c r="G437" s="39">
         <f>IF(OR(E437="",F437=""),"",ROUND(E437*F437,2))</f>
         <v/>
       </c>
@@ -8182,9 +8238,9 @@
       <c r="B438" s="12" t="n"/>
       <c r="C438" s="12" t="n"/>
       <c r="D438" s="12" t="n"/>
-      <c r="E438" s="38" t="n"/>
+      <c r="E438" s="41" t="n"/>
       <c r="F438" s="16" t="n"/>
-      <c r="G438" s="36">
+      <c r="G438" s="39">
         <f>IF(OR(E438="",F438=""),"",ROUND(E438*F438,2))</f>
         <v/>
       </c>
@@ -8196,9 +8252,9 @@
       <c r="B439" s="12" t="n"/>
       <c r="C439" s="12" t="n"/>
       <c r="D439" s="12" t="n"/>
-      <c r="E439" s="38" t="n"/>
+      <c r="E439" s="41" t="n"/>
       <c r="F439" s="16" t="n"/>
-      <c r="G439" s="36">
+      <c r="G439" s="39">
         <f>IF(OR(E439="",F439=""),"",ROUND(E439*F439,2))</f>
         <v/>
       </c>
@@ -8210,9 +8266,9 @@
       <c r="B440" s="12" t="n"/>
       <c r="C440" s="12" t="n"/>
       <c r="D440" s="12" t="n"/>
-      <c r="E440" s="38" t="n"/>
+      <c r="E440" s="41" t="n"/>
       <c r="F440" s="16" t="n"/>
-      <c r="G440" s="36">
+      <c r="G440" s="39">
         <f>IF(OR(E440="",F440=""),"",ROUND(E440*F440,2))</f>
         <v/>
       </c>
@@ -8224,9 +8280,9 @@
       <c r="B441" s="12" t="n"/>
       <c r="C441" s="12" t="n"/>
       <c r="D441" s="12" t="n"/>
-      <c r="E441" s="38" t="n"/>
+      <c r="E441" s="41" t="n"/>
       <c r="F441" s="16" t="n"/>
-      <c r="G441" s="36">
+      <c r="G441" s="39">
         <f>IF(OR(E441="",F441=""),"",ROUND(E441*F441,2))</f>
         <v/>
       </c>
@@ -8238,9 +8294,9 @@
       <c r="B442" s="12" t="n"/>
       <c r="C442" s="12" t="n"/>
       <c r="D442" s="12" t="n"/>
-      <c r="E442" s="38" t="n"/>
+      <c r="E442" s="41" t="n"/>
       <c r="F442" s="16" t="n"/>
-      <c r="G442" s="36">
+      <c r="G442" s="39">
         <f>IF(OR(E442="",F442=""),"",ROUND(E442*F442,2))</f>
         <v/>
       </c>
@@ -8252,9 +8308,9 @@
       <c r="B443" s="12" t="n"/>
       <c r="C443" s="12" t="n"/>
       <c r="D443" s="12" t="n"/>
-      <c r="E443" s="38" t="n"/>
+      <c r="E443" s="41" t="n"/>
       <c r="F443" s="16" t="n"/>
-      <c r="G443" s="36">
+      <c r="G443" s="39">
         <f>IF(OR(E443="",F443=""),"",ROUND(E443*F443,2))</f>
         <v/>
       </c>
@@ -8266,9 +8322,9 @@
       <c r="B444" s="12" t="n"/>
       <c r="C444" s="12" t="n"/>
       <c r="D444" s="12" t="n"/>
-      <c r="E444" s="38" t="n"/>
+      <c r="E444" s="41" t="n"/>
       <c r="F444" s="16" t="n"/>
-      <c r="G444" s="36">
+      <c r="G444" s="39">
         <f>IF(OR(E444="",F444=""),"",ROUND(E444*F444,2))</f>
         <v/>
       </c>
@@ -8280,9 +8336,9 @@
       <c r="B445" s="12" t="n"/>
       <c r="C445" s="12" t="n"/>
       <c r="D445" s="12" t="n"/>
-      <c r="E445" s="38" t="n"/>
+      <c r="E445" s="41" t="n"/>
       <c r="F445" s="16" t="n"/>
-      <c r="G445" s="36">
+      <c r="G445" s="39">
         <f>IF(OR(E445="",F445=""),"",ROUND(E445*F445,2))</f>
         <v/>
       </c>
@@ -8294,9 +8350,9 @@
       <c r="B446" s="12" t="n"/>
       <c r="C446" s="12" t="n"/>
       <c r="D446" s="12" t="n"/>
-      <c r="E446" s="38" t="n"/>
+      <c r="E446" s="41" t="n"/>
       <c r="F446" s="16" t="n"/>
-      <c r="G446" s="36">
+      <c r="G446" s="39">
         <f>IF(OR(E446="",F446=""),"",ROUND(E446*F446,2))</f>
         <v/>
       </c>
@@ -8308,9 +8364,9 @@
       <c r="B447" s="12" t="n"/>
       <c r="C447" s="12" t="n"/>
       <c r="D447" s="12" t="n"/>
-      <c r="E447" s="38" t="n"/>
+      <c r="E447" s="41" t="n"/>
       <c r="F447" s="16" t="n"/>
-      <c r="G447" s="36">
+      <c r="G447" s="39">
         <f>IF(OR(E447="",F447=""),"",ROUND(E447*F447,2))</f>
         <v/>
       </c>
@@ -8322,9 +8378,9 @@
       <c r="B448" s="12" t="n"/>
       <c r="C448" s="12" t="n"/>
       <c r="D448" s="12" t="n"/>
-      <c r="E448" s="38" t="n"/>
+      <c r="E448" s="41" t="n"/>
       <c r="F448" s="16" t="n"/>
-      <c r="G448" s="36">
+      <c r="G448" s="39">
         <f>IF(OR(E448="",F448=""),"",ROUND(E448*F448,2))</f>
         <v/>
       </c>
@@ -8336,9 +8392,9 @@
       <c r="B449" s="12" t="n"/>
       <c r="C449" s="12" t="n"/>
       <c r="D449" s="12" t="n"/>
-      <c r="E449" s="38" t="n"/>
+      <c r="E449" s="41" t="n"/>
       <c r="F449" s="16" t="n"/>
-      <c r="G449" s="36">
+      <c r="G449" s="39">
         <f>IF(OR(E449="",F449=""),"",ROUND(E449*F449,2))</f>
         <v/>
       </c>
@@ -8350,9 +8406,9 @@
       <c r="B450" s="12" t="n"/>
       <c r="C450" s="12" t="n"/>
       <c r="D450" s="12" t="n"/>
-      <c r="E450" s="38" t="n"/>
+      <c r="E450" s="41" t="n"/>
       <c r="F450" s="16" t="n"/>
-      <c r="G450" s="36">
+      <c r="G450" s="39">
         <f>IF(OR(E450="",F450=""),"",ROUND(E450*F450,2))</f>
         <v/>
       </c>
@@ -8364,9 +8420,9 @@
       <c r="B451" s="12" t="n"/>
       <c r="C451" s="12" t="n"/>
       <c r="D451" s="12" t="n"/>
-      <c r="E451" s="38" t="n"/>
+      <c r="E451" s="41" t="n"/>
       <c r="F451" s="16" t="n"/>
-      <c r="G451" s="36">
+      <c r="G451" s="39">
         <f>IF(OR(E451="",F451=""),"",ROUND(E451*F451,2))</f>
         <v/>
       </c>
@@ -8378,9 +8434,9 @@
       <c r="B452" s="12" t="n"/>
       <c r="C452" s="12" t="n"/>
       <c r="D452" s="12" t="n"/>
-      <c r="E452" s="38" t="n"/>
+      <c r="E452" s="41" t="n"/>
       <c r="F452" s="16" t="n"/>
-      <c r="G452" s="36">
+      <c r="G452" s="39">
         <f>IF(OR(E452="",F452=""),"",ROUND(E452*F452,2))</f>
         <v/>
       </c>
@@ -8392,9 +8448,9 @@
       <c r="B453" s="12" t="n"/>
       <c r="C453" s="12" t="n"/>
       <c r="D453" s="12" t="n"/>
-      <c r="E453" s="38" t="n"/>
+      <c r="E453" s="41" t="n"/>
       <c r="F453" s="16" t="n"/>
-      <c r="G453" s="36">
+      <c r="G453" s="39">
         <f>IF(OR(E453="",F453=""),"",ROUND(E453*F453,2))</f>
         <v/>
       </c>
@@ -8406,9 +8462,9 @@
       <c r="B454" s="12" t="n"/>
       <c r="C454" s="12" t="n"/>
       <c r="D454" s="12" t="n"/>
-      <c r="E454" s="38" t="n"/>
+      <c r="E454" s="41" t="n"/>
       <c r="F454" s="16" t="n"/>
-      <c r="G454" s="36">
+      <c r="G454" s="39">
         <f>IF(OR(E454="",F454=""),"",ROUND(E454*F454,2))</f>
         <v/>
       </c>
@@ -8420,9 +8476,9 @@
       <c r="B455" s="12" t="n"/>
       <c r="C455" s="12" t="n"/>
       <c r="D455" s="12" t="n"/>
-      <c r="E455" s="38" t="n"/>
+      <c r="E455" s="41" t="n"/>
       <c r="F455" s="16" t="n"/>
-      <c r="G455" s="36">
+      <c r="G455" s="39">
         <f>IF(OR(E455="",F455=""),"",ROUND(E455*F455,2))</f>
         <v/>
       </c>
@@ -8434,9 +8490,9 @@
       <c r="B456" s="12" t="n"/>
       <c r="C456" s="12" t="n"/>
       <c r="D456" s="12" t="n"/>
-      <c r="E456" s="38" t="n"/>
+      <c r="E456" s="41" t="n"/>
       <c r="F456" s="16" t="n"/>
-      <c r="G456" s="36">
+      <c r="G456" s="39">
         <f>IF(OR(E456="",F456=""),"",ROUND(E456*F456,2))</f>
         <v/>
       </c>
@@ -8448,9 +8504,9 @@
       <c r="B457" s="12" t="n"/>
       <c r="C457" s="12" t="n"/>
       <c r="D457" s="12" t="n"/>
-      <c r="E457" s="38" t="n"/>
+      <c r="E457" s="41" t="n"/>
       <c r="F457" s="16" t="n"/>
-      <c r="G457" s="36">
+      <c r="G457" s="39">
         <f>IF(OR(E457="",F457=""),"",ROUND(E457*F457,2))</f>
         <v/>
       </c>
@@ -8462,9 +8518,9 @@
       <c r="B458" s="12" t="n"/>
       <c r="C458" s="12" t="n"/>
       <c r="D458" s="12" t="n"/>
-      <c r="E458" s="38" t="n"/>
+      <c r="E458" s="41" t="n"/>
       <c r="F458" s="16" t="n"/>
-      <c r="G458" s="36">
+      <c r="G458" s="39">
         <f>IF(OR(E458="",F458=""),"",ROUND(E458*F458,2))</f>
         <v/>
       </c>
@@ -8476,9 +8532,9 @@
       <c r="B459" s="12" t="n"/>
       <c r="C459" s="12" t="n"/>
       <c r="D459" s="12" t="n"/>
-      <c r="E459" s="38" t="n"/>
+      <c r="E459" s="41" t="n"/>
       <c r="F459" s="16" t="n"/>
-      <c r="G459" s="36">
+      <c r="G459" s="39">
         <f>IF(OR(E459="",F459=""),"",ROUND(E459*F459,2))</f>
         <v/>
       </c>
@@ -8490,9 +8546,9 @@
       <c r="B460" s="12" t="n"/>
       <c r="C460" s="12" t="n"/>
       <c r="D460" s="12" t="n"/>
-      <c r="E460" s="38" t="n"/>
+      <c r="E460" s="41" t="n"/>
       <c r="F460" s="16" t="n"/>
-      <c r="G460" s="36">
+      <c r="G460" s="39">
         <f>IF(OR(E460="",F460=""),"",ROUND(E460*F460,2))</f>
         <v/>
       </c>
@@ -8504,9 +8560,9 @@
       <c r="B461" s="12" t="n"/>
       <c r="C461" s="12" t="n"/>
       <c r="D461" s="12" t="n"/>
-      <c r="E461" s="38" t="n"/>
+      <c r="E461" s="41" t="n"/>
       <c r="F461" s="16" t="n"/>
-      <c r="G461" s="36">
+      <c r="G461" s="39">
         <f>IF(OR(E461="",F461=""),"",ROUND(E461*F461,2))</f>
         <v/>
       </c>
@@ -8518,9 +8574,9 @@
       <c r="B462" s="12" t="n"/>
       <c r="C462" s="12" t="n"/>
       <c r="D462" s="12" t="n"/>
-      <c r="E462" s="38" t="n"/>
+      <c r="E462" s="41" t="n"/>
       <c r="F462" s="16" t="n"/>
-      <c r="G462" s="36">
+      <c r="G462" s="39">
         <f>IF(OR(E462="",F462=""),"",ROUND(E462*F462,2))</f>
         <v/>
       </c>
@@ -8532,9 +8588,9 @@
       <c r="B463" s="12" t="n"/>
       <c r="C463" s="12" t="n"/>
       <c r="D463" s="12" t="n"/>
-      <c r="E463" s="38" t="n"/>
+      <c r="E463" s="41" t="n"/>
       <c r="F463" s="16" t="n"/>
-      <c r="G463" s="36">
+      <c r="G463" s="39">
         <f>IF(OR(E463="",F463=""),"",ROUND(E463*F463,2))</f>
         <v/>
       </c>
@@ -8546,9 +8602,9 @@
       <c r="B464" s="12" t="n"/>
       <c r="C464" s="12" t="n"/>
       <c r="D464" s="12" t="n"/>
-      <c r="E464" s="38" t="n"/>
+      <c r="E464" s="41" t="n"/>
       <c r="F464" s="16" t="n"/>
-      <c r="G464" s="36">
+      <c r="G464" s="39">
         <f>IF(OR(E464="",F464=""),"",ROUND(E464*F464,2))</f>
         <v/>
       </c>
@@ -8560,9 +8616,9 @@
       <c r="B465" s="12" t="n"/>
       <c r="C465" s="12" t="n"/>
       <c r="D465" s="12" t="n"/>
-      <c r="E465" s="38" t="n"/>
+      <c r="E465" s="41" t="n"/>
       <c r="F465" s="16" t="n"/>
-      <c r="G465" s="36">
+      <c r="G465" s="39">
         <f>IF(OR(E465="",F465=""),"",ROUND(E465*F465,2))</f>
         <v/>
       </c>
@@ -8574,9 +8630,9 @@
       <c r="B466" s="12" t="n"/>
       <c r="C466" s="12" t="n"/>
       <c r="D466" s="12" t="n"/>
-      <c r="E466" s="38" t="n"/>
+      <c r="E466" s="41" t="n"/>
       <c r="F466" s="16" t="n"/>
-      <c r="G466" s="36">
+      <c r="G466" s="39">
         <f>IF(OR(E466="",F466=""),"",ROUND(E466*F466,2))</f>
         <v/>
       </c>
@@ -8588,9 +8644,9 @@
       <c r="B467" s="12" t="n"/>
       <c r="C467" s="12" t="n"/>
       <c r="D467" s="12" t="n"/>
-      <c r="E467" s="38" t="n"/>
+      <c r="E467" s="41" t="n"/>
       <c r="F467" s="16" t="n"/>
-      <c r="G467" s="36">
+      <c r="G467" s="39">
         <f>IF(OR(E467="",F467=""),"",ROUND(E467*F467,2))</f>
         <v/>
       </c>
@@ -8602,9 +8658,9 @@
       <c r="B468" s="12" t="n"/>
       <c r="C468" s="12" t="n"/>
       <c r="D468" s="12" t="n"/>
-      <c r="E468" s="38" t="n"/>
+      <c r="E468" s="41" t="n"/>
       <c r="F468" s="16" t="n"/>
-      <c r="G468" s="36">
+      <c r="G468" s="39">
         <f>IF(OR(E468="",F468=""),"",ROUND(E468*F468,2))</f>
         <v/>
       </c>
@@ -8616,9 +8672,9 @@
       <c r="B469" s="12" t="n"/>
       <c r="C469" s="12" t="n"/>
       <c r="D469" s="12" t="n"/>
-      <c r="E469" s="38" t="n"/>
+      <c r="E469" s="41" t="n"/>
       <c r="F469" s="16" t="n"/>
-      <c r="G469" s="36">
+      <c r="G469" s="39">
         <f>IF(OR(E469="",F469=""),"",ROUND(E469*F469,2))</f>
         <v/>
       </c>
@@ -8630,9 +8686,9 @@
       <c r="B470" s="12" t="n"/>
       <c r="C470" s="12" t="n"/>
       <c r="D470" s="12" t="n"/>
-      <c r="E470" s="38" t="n"/>
+      <c r="E470" s="41" t="n"/>
       <c r="F470" s="16" t="n"/>
-      <c r="G470" s="36">
+      <c r="G470" s="39">
         <f>IF(OR(E470="",F470=""),"",ROUND(E470*F470,2))</f>
         <v/>
       </c>
@@ -8644,9 +8700,9 @@
       <c r="B471" s="12" t="n"/>
       <c r="C471" s="12" t="n"/>
       <c r="D471" s="12" t="n"/>
-      <c r="E471" s="38" t="n"/>
+      <c r="E471" s="41" t="n"/>
       <c r="F471" s="16" t="n"/>
-      <c r="G471" s="36">
+      <c r="G471" s="39">
         <f>IF(OR(E471="",F471=""),"",ROUND(E471*F471,2))</f>
         <v/>
       </c>
@@ -8658,9 +8714,9 @@
       <c r="B472" s="12" t="n"/>
       <c r="C472" s="12" t="n"/>
       <c r="D472" s="12" t="n"/>
-      <c r="E472" s="38" t="n"/>
+      <c r="E472" s="41" t="n"/>
       <c r="F472" s="16" t="n"/>
-      <c r="G472" s="36">
+      <c r="G472" s="39">
         <f>IF(OR(E472="",F472=""),"",ROUND(E472*F472,2))</f>
         <v/>
       </c>
@@ -8672,9 +8728,9 @@
       <c r="B473" s="12" t="n"/>
       <c r="C473" s="12" t="n"/>
       <c r="D473" s="12" t="n"/>
-      <c r="E473" s="38" t="n"/>
+      <c r="E473" s="41" t="n"/>
       <c r="F473" s="16" t="n"/>
-      <c r="G473" s="36">
+      <c r="G473" s="39">
         <f>IF(OR(E473="",F473=""),"",ROUND(E473*F473,2))</f>
         <v/>
       </c>
@@ -8686,9 +8742,9 @@
       <c r="B474" s="12" t="n"/>
       <c r="C474" s="12" t="n"/>
       <c r="D474" s="12" t="n"/>
-      <c r="E474" s="38" t="n"/>
+      <c r="E474" s="41" t="n"/>
       <c r="F474" s="16" t="n"/>
-      <c r="G474" s="36">
+      <c r="G474" s="39">
         <f>IF(OR(E474="",F474=""),"",ROUND(E474*F474,2))</f>
         <v/>
       </c>
@@ -8700,9 +8756,9 @@
       <c r="B475" s="12" t="n"/>
       <c r="C475" s="12" t="n"/>
       <c r="D475" s="12" t="n"/>
-      <c r="E475" s="38" t="n"/>
+      <c r="E475" s="41" t="n"/>
       <c r="F475" s="16" t="n"/>
-      <c r="G475" s="36">
+      <c r="G475" s="39">
         <f>IF(OR(E475="",F475=""),"",ROUND(E475*F475,2))</f>
         <v/>
       </c>
@@ -8714,9 +8770,9 @@
       <c r="B476" s="12" t="n"/>
       <c r="C476" s="12" t="n"/>
       <c r="D476" s="12" t="n"/>
-      <c r="E476" s="38" t="n"/>
+      <c r="E476" s="41" t="n"/>
       <c r="F476" s="16" t="n"/>
-      <c r="G476" s="36">
+      <c r="G476" s="39">
         <f>IF(OR(E476="",F476=""),"",ROUND(E476*F476,2))</f>
         <v/>
       </c>
@@ -8728,9 +8784,9 @@
       <c r="B477" s="12" t="n"/>
       <c r="C477" s="12" t="n"/>
       <c r="D477" s="12" t="n"/>
-      <c r="E477" s="38" t="n"/>
+      <c r="E477" s="41" t="n"/>
       <c r="F477" s="16" t="n"/>
-      <c r="G477" s="36">
+      <c r="G477" s="39">
         <f>IF(OR(E477="",F477=""),"",ROUND(E477*F477,2))</f>
         <v/>
       </c>
@@ -8742,9 +8798,9 @@
       <c r="B478" s="12" t="n"/>
       <c r="C478" s="12" t="n"/>
       <c r="D478" s="12" t="n"/>
-      <c r="E478" s="38" t="n"/>
+      <c r="E478" s="41" t="n"/>
       <c r="F478" s="16" t="n"/>
-      <c r="G478" s="36">
+      <c r="G478" s="39">
         <f>IF(OR(E478="",F478=""),"",ROUND(E478*F478,2))</f>
         <v/>
       </c>
@@ -8756,9 +8812,9 @@
       <c r="B479" s="12" t="n"/>
       <c r="C479" s="12" t="n"/>
       <c r="D479" s="12" t="n"/>
-      <c r="E479" s="38" t="n"/>
+      <c r="E479" s="41" t="n"/>
       <c r="F479" s="16" t="n"/>
-      <c r="G479" s="36">
+      <c r="G479" s="39">
         <f>IF(OR(E479="",F479=""),"",ROUND(E479*F479,2))</f>
         <v/>
       </c>
@@ -8770,9 +8826,9 @@
       <c r="B480" s="12" t="n"/>
       <c r="C480" s="12" t="n"/>
       <c r="D480" s="12" t="n"/>
-      <c r="E480" s="38" t="n"/>
+      <c r="E480" s="41" t="n"/>
       <c r="F480" s="16" t="n"/>
-      <c r="G480" s="36">
+      <c r="G480" s="39">
         <f>IF(OR(E480="",F480=""),"",ROUND(E480*F480,2))</f>
         <v/>
       </c>
@@ -8784,9 +8840,9 @@
       <c r="B481" s="12" t="n"/>
       <c r="C481" s="12" t="n"/>
       <c r="D481" s="12" t="n"/>
-      <c r="E481" s="38" t="n"/>
+      <c r="E481" s="41" t="n"/>
       <c r="F481" s="16" t="n"/>
-      <c r="G481" s="36">
+      <c r="G481" s="39">
         <f>IF(OR(E481="",F481=""),"",ROUND(E481*F481,2))</f>
         <v/>
       </c>
@@ -8798,9 +8854,9 @@
       <c r="B482" s="12" t="n"/>
       <c r="C482" s="12" t="n"/>
       <c r="D482" s="12" t="n"/>
-      <c r="E482" s="38" t="n"/>
+      <c r="E482" s="41" t="n"/>
       <c r="F482" s="16" t="n"/>
-      <c r="G482" s="36">
+      <c r="G482" s="39">
         <f>IF(OR(E482="",F482=""),"",ROUND(E482*F482,2))</f>
         <v/>
       </c>
@@ -8812,9 +8868,9 @@
       <c r="B483" s="12" t="n"/>
       <c r="C483" s="12" t="n"/>
       <c r="D483" s="12" t="n"/>
-      <c r="E483" s="38" t="n"/>
+      <c r="E483" s="41" t="n"/>
       <c r="F483" s="16" t="n"/>
-      <c r="G483" s="36">
+      <c r="G483" s="39">
         <f>IF(OR(E483="",F483=""),"",ROUND(E483*F483,2))</f>
         <v/>
       </c>
@@ -8826,9 +8882,9 @@
       <c r="B484" s="12" t="n"/>
       <c r="C484" s="12" t="n"/>
       <c r="D484" s="12" t="n"/>
-      <c r="E484" s="38" t="n"/>
+      <c r="E484" s="41" t="n"/>
       <c r="F484" s="16" t="n"/>
-      <c r="G484" s="36">
+      <c r="G484" s="39">
         <f>IF(OR(E484="",F484=""),"",ROUND(E484*F484,2))</f>
         <v/>
       </c>
@@ -8840,9 +8896,9 @@
       <c r="B485" s="12" t="n"/>
       <c r="C485" s="12" t="n"/>
       <c r="D485" s="12" t="n"/>
-      <c r="E485" s="38" t="n"/>
+      <c r="E485" s="41" t="n"/>
       <c r="F485" s="16" t="n"/>
-      <c r="G485" s="36">
+      <c r="G485" s="39">
         <f>IF(OR(E485="",F485=""),"",ROUND(E485*F485,2))</f>
         <v/>
       </c>
@@ -8854,9 +8910,9 @@
       <c r="B486" s="12" t="n"/>
       <c r="C486" s="12" t="n"/>
       <c r="D486" s="12" t="n"/>
-      <c r="E486" s="38" t="n"/>
+      <c r="E486" s="41" t="n"/>
       <c r="F486" s="16" t="n"/>
-      <c r="G486" s="36">
+      <c r="G486" s="39">
         <f>IF(OR(E486="",F486=""),"",ROUND(E486*F486,2))</f>
         <v/>
       </c>
@@ -8868,9 +8924,9 @@
       <c r="B487" s="12" t="n"/>
       <c r="C487" s="12" t="n"/>
       <c r="D487" s="12" t="n"/>
-      <c r="E487" s="38" t="n"/>
+      <c r="E487" s="41" t="n"/>
       <c r="F487" s="16" t="n"/>
-      <c r="G487" s="36">
+      <c r="G487" s="39">
         <f>IF(OR(E487="",F487=""),"",ROUND(E487*F487,2))</f>
         <v/>
       </c>
@@ -8882,9 +8938,9 @@
       <c r="B488" s="12" t="n"/>
       <c r="C488" s="12" t="n"/>
       <c r="D488" s="12" t="n"/>
-      <c r="E488" s="38" t="n"/>
+      <c r="E488" s="41" t="n"/>
       <c r="F488" s="16" t="n"/>
-      <c r="G488" s="36">
+      <c r="G488" s="39">
         <f>IF(OR(E488="",F488=""),"",ROUND(E488*F488,2))</f>
         <v/>
       </c>
@@ -8896,9 +8952,9 @@
       <c r="B489" s="12" t="n"/>
       <c r="C489" s="12" t="n"/>
       <c r="D489" s="12" t="n"/>
-      <c r="E489" s="38" t="n"/>
+      <c r="E489" s="41" t="n"/>
       <c r="F489" s="16" t="n"/>
-      <c r="G489" s="36">
+      <c r="G489" s="39">
         <f>IF(OR(E489="",F489=""),"",ROUND(E489*F489,2))</f>
         <v/>
       </c>
@@ -8910,9 +8966,9 @@
       <c r="B490" s="12" t="n"/>
       <c r="C490" s="12" t="n"/>
       <c r="D490" s="12" t="n"/>
-      <c r="E490" s="38" t="n"/>
+      <c r="E490" s="41" t="n"/>
       <c r="F490" s="16" t="n"/>
-      <c r="G490" s="36">
+      <c r="G490" s="39">
         <f>IF(OR(E490="",F490=""),"",ROUND(E490*F490,2))</f>
         <v/>
       </c>
@@ -8924,9 +8980,9 @@
       <c r="B491" s="12" t="n"/>
       <c r="C491" s="12" t="n"/>
       <c r="D491" s="12" t="n"/>
-      <c r="E491" s="38" t="n"/>
+      <c r="E491" s="41" t="n"/>
       <c r="F491" s="16" t="n"/>
-      <c r="G491" s="36">
+      <c r="G491" s="39">
         <f>IF(OR(E491="",F491=""),"",ROUND(E491*F491,2))</f>
         <v/>
       </c>
@@ -8938,9 +8994,9 @@
       <c r="B492" s="12" t="n"/>
       <c r="C492" s="12" t="n"/>
       <c r="D492" s="12" t="n"/>
-      <c r="E492" s="38" t="n"/>
+      <c r="E492" s="41" t="n"/>
       <c r="F492" s="16" t="n"/>
-      <c r="G492" s="36">
+      <c r="G492" s="39">
         <f>IF(OR(E492="",F492=""),"",ROUND(E492*F492,2))</f>
         <v/>
       </c>
@@ -8952,9 +9008,9 @@
       <c r="B493" s="12" t="n"/>
       <c r="C493" s="12" t="n"/>
       <c r="D493" s="12" t="n"/>
-      <c r="E493" s="38" t="n"/>
+      <c r="E493" s="41" t="n"/>
       <c r="F493" s="16" t="n"/>
-      <c r="G493" s="36">
+      <c r="G493" s="39">
         <f>IF(OR(E493="",F493=""),"",ROUND(E493*F493,2))</f>
         <v/>
       </c>
@@ -8966,9 +9022,9 @@
       <c r="B494" s="12" t="n"/>
       <c r="C494" s="12" t="n"/>
       <c r="D494" s="12" t="n"/>
-      <c r="E494" s="38" t="n"/>
+      <c r="E494" s="41" t="n"/>
       <c r="F494" s="16" t="n"/>
-      <c r="G494" s="36">
+      <c r="G494" s="39">
         <f>IF(OR(E494="",F494=""),"",ROUND(E494*F494,2))</f>
         <v/>
       </c>
@@ -8980,9 +9036,9 @@
       <c r="B495" s="12" t="n"/>
       <c r="C495" s="12" t="n"/>
       <c r="D495" s="12" t="n"/>
-      <c r="E495" s="38" t="n"/>
+      <c r="E495" s="41" t="n"/>
       <c r="F495" s="16" t="n"/>
-      <c r="G495" s="36">
+      <c r="G495" s="39">
         <f>IF(OR(E495="",F495=""),"",ROUND(E495*F495,2))</f>
         <v/>
       </c>
@@ -8994,9 +9050,9 @@
       <c r="B496" s="12" t="n"/>
       <c r="C496" s="12" t="n"/>
       <c r="D496" s="12" t="n"/>
-      <c r="E496" s="38" t="n"/>
+      <c r="E496" s="41" t="n"/>
       <c r="F496" s="16" t="n"/>
-      <c r="G496" s="36">
+      <c r="G496" s="39">
         <f>IF(OR(E496="",F496=""),"",ROUND(E496*F496,2))</f>
         <v/>
       </c>
@@ -9008,9 +9064,9 @@
       <c r="B497" s="12" t="n"/>
       <c r="C497" s="12" t="n"/>
       <c r="D497" s="12" t="n"/>
-      <c r="E497" s="38" t="n"/>
+      <c r="E497" s="41" t="n"/>
       <c r="F497" s="16" t="n"/>
-      <c r="G497" s="36">
+      <c r="G497" s="39">
         <f>IF(OR(E497="",F497=""),"",ROUND(E497*F497,2))</f>
         <v/>
       </c>
@@ -9022,9 +9078,9 @@
       <c r="B498" s="12" t="n"/>
       <c r="C498" s="12" t="n"/>
       <c r="D498" s="12" t="n"/>
-      <c r="E498" s="38" t="n"/>
+      <c r="E498" s="41" t="n"/>
       <c r="F498" s="16" t="n"/>
-      <c r="G498" s="36">
+      <c r="G498" s="39">
         <f>IF(OR(E498="",F498=""),"",ROUND(E498*F498,2))</f>
         <v/>
       </c>
@@ -9036,9 +9092,9 @@
       <c r="B499" s="12" t="n"/>
       <c r="C499" s="12" t="n"/>
       <c r="D499" s="12" t="n"/>
-      <c r="E499" s="38" t="n"/>
+      <c r="E499" s="41" t="n"/>
       <c r="F499" s="16" t="n"/>
-      <c r="G499" s="36">
+      <c r="G499" s="39">
         <f>IF(OR(E499="",F499=""),"",ROUND(E499*F499,2))</f>
         <v/>
       </c>
@@ -9050,9 +9106,9 @@
       <c r="B500" s="12" t="n"/>
       <c r="C500" s="12" t="n"/>
       <c r="D500" s="12" t="n"/>
-      <c r="E500" s="38" t="n"/>
+      <c r="E500" s="41" t="n"/>
       <c r="F500" s="16" t="n"/>
-      <c r="G500" s="36">
+      <c r="G500" s="39">
         <f>IF(OR(E500="",F500=""),"",ROUND(E500*F500,2))</f>
         <v/>
       </c>
